--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -357,7 +357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B100"/>
+  <dimension ref="A1:B101"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -696,7 +696,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.4448103140732</v>
+        <v>139.4334860684302</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -704,7 +704,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.6768238777917</v>
+        <v>142.6604077042163</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -712,7 +712,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.9715761156826</v>
+        <v>143.9540188845062</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -720,7 +720,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.6545417617153</v>
+        <v>144.6367354849496</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -728,7 +728,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.5848042405071</v>
+        <v>144.5666802517152</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -736,7 +736,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.5097583970477</v>
+        <v>144.4913654366659</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -744,7 +744,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.4674830852561</v>
+        <v>144.4489819733338</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -752,7 +752,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.5064934102824</v>
+        <v>144.4880245639576</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -760,7 +760,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>145.1758180124893</v>
+        <v>145.1575396916396</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -768,7 +768,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0332160320341</v>
+        <v>148.0335274175785</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -776,7 +776,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4307134568302</v>
+        <v>148.430787161926</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -784,7 +784,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8534482002967</v>
+        <v>148.8534596980857</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -792,7 +792,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.8955202735038</v>
+        <v>148.8978057283692</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -800,7 +800,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2867331403682</v>
+        <v>149.2873162937499</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -808,7 +808,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4429599733844</v>
+        <v>150.4399241662431</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -816,7 +816,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.9522950166231</v>
+        <v>151.9446776558274</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -824,7 +824,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.3467866919482</v>
+        <v>152.338736809943</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -832,7 +832,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.6727228892421</v>
+        <v>152.6650761294098</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -840,7 +840,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.2382544081296</v>
+        <v>153.2334009168517</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -848,7 +848,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4243188147173</v>
+        <v>152.4230173449428</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -856,7 +856,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>153.0585107804387</v>
+        <v>153.0457223146508</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -864,7 +864,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.8955646037654</v>
+        <v>152.8782380834623</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -872,7 +872,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.976432397143</v>
+        <v>152.954318878511</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -880,7 +880,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.7200582958824</v>
+        <v>154.6934650528199</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -888,7 +888,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.6731036997524</v>
+        <v>155.6471583009525</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -896,7 +896,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.6899271281861</v>
+        <v>156.6619521082022</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -904,7 +904,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>158.3758278451848</v>
+        <v>158.3457785216803</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -912,7 +912,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.9225904343307</v>
+        <v>159.8989211568599</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -920,7 +920,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.650817843106</v>
+        <v>161.6362275004788</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -928,7 +928,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.7672719983022</v>
+        <v>159.780328676703</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -936,7 +936,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.5506702915182</v>
+        <v>159.5581221048682</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -944,7 +944,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>158.8313652065306</v>
+        <v>158.8641309209456</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -952,7 +952,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>156.9746165369212</v>
+        <v>157.0159201969365</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -960,7 +960,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.5284801768926</v>
+        <v>157.5669390325293</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -968,7 +968,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>157.8854697847946</v>
+        <v>157.9195569654382</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -976,7 +976,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>157.9491490237632</v>
+        <v>157.9802680270458</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -984,7 +984,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.2165150850974</v>
+        <v>159.2447833602011</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -992,7 +992,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.2821200713771</v>
+        <v>158.2921887800112</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1000,7 +1000,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.8803204698084</v>
+        <v>155.8660178002545</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1008,7 +1008,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>156.0355410268673</v>
+        <v>156.0202435790227</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1016,7 +1016,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.7402785289946</v>
+        <v>156.7325902460001</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1024,7 +1024,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.701661122244</v>
+        <v>156.6696997717868</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1032,7 +1032,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.4859365459153</v>
+        <v>156.4530439219965</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1040,7 +1040,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>156.3471775391082</v>
+        <v>156.3131473596949</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1048,7 +1048,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.2905300952211</v>
+        <v>157.4043526217732</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1056,7 +1056,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.4983319517572</v>
+        <v>158.5965671938587</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1064,7 +1064,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>158.9615562959408</v>
+        <v>159.0133418290683</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1072,7 +1072,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.5065438186793</v>
+        <v>159.5420226256106</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1080,7 +1080,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.141095275381</v>
+        <v>159.3569054374145</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1088,7 +1088,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>159.5525265114681</v>
+        <v>159.824058398476</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1096,7 +1096,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>158.8325237252104</v>
+        <v>159.3977530176476</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1104,7 +1104,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>158.1204268620277</v>
+        <v>159.0227676937303</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1112,7 +1112,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>158.4216056025721</v>
+        <v>159.4112808199156</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1120,7 +1120,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>158.2652444704347</v>
+        <v>159.5934212883183</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1128,7 +1128,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>158.0914819941886</v>
+        <v>159.7396892604685</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1136,7 +1136,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>157.9392042580763</v>
+        <v>159.687183220962</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1144,7 +1144,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>157.5115598941711</v>
+        <v>159.5550812706917</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1152,7 +1152,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>157.7335065728793</v>
+        <v>159.6335246116524</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1160,7 +1160,15 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>158.76</v>
+        <v>160.2522692247898</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B101">
+        <v>160.6009183954926</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -357,7 +357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B101"/>
+  <dimension ref="A1:B102"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -696,7 +696,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.4334860684302</v>
+        <v>139.4282483300218</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -704,7 +704,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.6604077042163</v>
+        <v>142.6528099717266</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -712,7 +712,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.9540188845062</v>
+        <v>143.9458855851097</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -720,7 +720,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.6367354849496</v>
+        <v>144.6284791388765</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -728,7 +728,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.5666802517152</v>
+        <v>144.5582770793031</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -736,7 +736,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.4913654366659</v>
+        <v>144.4828380193316</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -744,7 +744,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.4489819733338</v>
+        <v>144.4404046472913</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -752,7 +752,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.4880245639576</v>
+        <v>144.479462226389</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -760,7 +760,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>145.1575396916396</v>
+        <v>145.1490575903819</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -768,7 +768,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0335274175785</v>
+        <v>148.0336710664244</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -776,7 +776,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.430787161926</v>
+        <v>148.4308210058148</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -784,7 +784,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8534596980857</v>
+        <v>148.8534647954286</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -792,7 +792,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.8978057283692</v>
+        <v>148.8988603051413</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -800,7 +800,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2873162937499</v>
+        <v>149.2875897059945</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -808,7 +808,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4399241662431</v>
+        <v>150.438521679445</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -816,7 +816,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.9446776558274</v>
+        <v>151.94114648428</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -824,7 +824,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.338736809943</v>
+        <v>152.3350032656666</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -832,7 +832,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.6650761294098</v>
+        <v>152.6615247377906</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -840,7 +840,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.2334009168517</v>
+        <v>153.2311461640565</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -848,7 +848,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4230173449428</v>
+        <v>152.422416089479</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -856,7 +856,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>153.0457223146508</v>
+        <v>153.039818749383</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -864,7 +864,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.8782380834623</v>
+        <v>152.8702293344758</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -872,7 +872,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.954318878511</v>
+        <v>152.9440784217209</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -880,7 +880,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.6934650528199</v>
+        <v>154.6811407687885</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -888,7 +888,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.6471583009525</v>
+        <v>155.6351146410357</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -896,7 +896,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.6619521082022</v>
+        <v>156.6489510030797</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -904,7 +904,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>158.3457785216803</v>
+        <v>158.3317883409347</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -912,7 +912,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.8989211568599</v>
+        <v>159.8878422725998</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -920,7 +920,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.6362275004788</v>
+        <v>161.6293662745288</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -928,7 +928,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.780328676703</v>
+        <v>159.7862745231539</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -936,7 +936,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.5581221048682</v>
+        <v>159.5614889161681</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -944,7 +944,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>158.8641309209456</v>
+        <v>158.8792421401487</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -952,7 +952,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.0159201969365</v>
+        <v>157.0350102853525</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -960,7 +960,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.5669390325293</v>
+        <v>157.5847548764707</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -968,7 +968,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>157.9195569654382</v>
+        <v>157.9353952510507</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -976,7 +976,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>157.9802680270458</v>
+        <v>157.9948280140434</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -984,7 +984,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.2447833602011</v>
+        <v>159.2580497186091</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -992,7 +992,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.2921887800112</v>
+        <v>158.2970017142037</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1000,7 +1000,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.8660178002545</v>
+        <v>155.8594487376556</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1008,7 +1008,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>156.0202435790227</v>
+        <v>156.0132173009657</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1016,7 +1016,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.7325902460001</v>
+        <v>156.7291021985092</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1024,7 +1024,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.6696997717868</v>
+        <v>156.6548437549537</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1032,7 +1032,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.4530439219965</v>
+        <v>156.4377226391862</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1040,7 +1040,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>156.3131473596949</v>
+        <v>156.2972347660272</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1048,7 +1048,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.4043526217732</v>
+        <v>157.3951038888844</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1056,7 +1056,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.5965671938587</v>
+        <v>158.5988820089149</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1064,7 +1064,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.0133418290683</v>
+        <v>159.0404500540017</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1072,7 +1072,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.5420226256106</v>
+        <v>159.5501275473501</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1080,7 +1080,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.3569054374145</v>
+        <v>159.3771963112786</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1088,7 +1088,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>159.824058398476</v>
+        <v>159.8378139425831</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1096,7 +1096,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>159.3977530176476</v>
+        <v>159.4684029519856</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1104,7 +1104,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.0227676937303</v>
+        <v>159.13547777798</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1112,7 +1112,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>159.4112808199156</v>
+        <v>159.4802752227027</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1120,7 +1120,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>159.5934212883183</v>
+        <v>159.6046195278819</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1128,7 +1128,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>159.7396892604685</v>
+        <v>159.6658231494038</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1136,7 +1136,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>159.687183220962</v>
+        <v>159.4507222956628</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1144,7 +1144,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>159.5550812706917</v>
+        <v>159.124095541313</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1152,7 +1152,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>159.6335246116524</v>
+        <v>158.9439955431843</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1160,7 +1160,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>160.2522692247898</v>
+        <v>159.1240791643331</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1168,7 +1168,15 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>160.6009183954926</v>
+        <v>159.0955580446334</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B102">
+        <v>156.0413203135186</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -1072,7 +1072,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.5501275473501</v>
+        <v>159.5497728488797</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1080,7 +1080,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.3771963112786</v>
+        <v>159.3756644716003</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1088,7 +1088,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>159.8378139425831</v>
+        <v>159.8337195750469</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1096,7 +1096,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>159.4684029519856</v>
+        <v>159.4638235970512</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1104,7 +1104,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.13547777798</v>
+        <v>159.1291701471646</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1112,7 +1112,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>159.4802752227027</v>
+        <v>159.471722908069</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1120,7 +1120,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>159.6046195278819</v>
+        <v>159.5933540754615</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1128,7 +1128,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>159.6658231494038</v>
+        <v>159.6588424783127</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1136,7 +1136,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>159.4507222956628</v>
+        <v>159.4322120144163</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1144,7 +1144,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>159.124095541313</v>
+        <v>159.1036954175622</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1152,7 +1152,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>158.9439955431843</v>
+        <v>158.9069280274631</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1160,7 +1160,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>159.1240791643331</v>
+        <v>159.0832837256982</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1168,7 +1168,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>159.0955580446334</v>
+        <v>159.0846868285907</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1176,7 +1176,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>156.0413203135186</v>
+        <v>155.9467568481591</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -357,7 +357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B102"/>
+  <dimension ref="A1:B103"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -1072,7 +1072,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.5497728488797</v>
+        <v>159.5496268774027</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1080,7 +1080,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.3756644716003</v>
+        <v>159.3754714776136</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1088,7 +1088,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>159.8337195750469</v>
+        <v>159.8331483428509</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1096,7 +1096,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>159.4638235970512</v>
+        <v>159.463131297524</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1104,7 +1104,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.1291701471646</v>
+        <v>159.1286414408619</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1112,7 +1112,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>159.471722908069</v>
+        <v>159.4715369388451</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1120,7 +1120,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>159.5933540754615</v>
+        <v>159.5938678985513</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1128,7 +1128,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>159.6588424783127</v>
+        <v>159.6607279816927</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1136,7 +1136,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>159.4322120144163</v>
+        <v>159.4380600905707</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1144,7 +1144,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>159.1036954175622</v>
+        <v>159.1144665372801</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1152,7 +1152,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>158.9069280274631</v>
+        <v>158.9233598969007</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1160,7 +1160,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>159.0832837256982</v>
+        <v>159.1069932754959</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1168,7 +1168,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>159.0846868285907</v>
+        <v>159.9141052103334</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1176,7 +1176,15 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>155.9467568481591</v>
+        <v>159.3204679237588</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103" s="2">
+        <v>46276</v>
+      </c>
+      <c r="B103">
+        <v>159.400142316897</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -357,7 +357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B103"/>
+  <dimension ref="A1:B104"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -696,7 +696,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.4282483300218</v>
+        <v>139.4232659352207</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -704,7 +704,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.6528099717266</v>
+        <v>142.6455797928875</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -712,7 +712,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.9458855851097</v>
+        <v>143.9381413786734</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -720,7 +720,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.6284791388765</v>
+        <v>144.6206132775391</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -728,7 +728,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.5582770793031</v>
+        <v>144.55027162235</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -736,7 +736,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.4828380193316</v>
+        <v>144.4747144694096</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -744,7 +744,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.4404046472913</v>
+        <v>144.4322336887959</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -752,7 +752,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.479462226389</v>
+        <v>144.4713055636286</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -760,7 +760,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>145.1490575903819</v>
+        <v>145.1409726260754</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -768,7 +768,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0336710664244</v>
+        <v>148.0338074910877</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -776,7 +776,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4308210058148</v>
+        <v>148.4308530541309</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -784,7 +784,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8534647954286</v>
+        <v>148.8534695137901</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -792,7 +792,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.8988603051413</v>
+        <v>148.8998619955358</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -800,7 +800,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2875897059945</v>
+        <v>149.2878519403513</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -808,7 +808,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.438521679445</v>
+        <v>150.4371885558905</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -816,7 +816,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.94114648428</v>
+        <v>151.9377828277309</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -824,7 +824,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.3350032656666</v>
+        <v>152.3314457394651</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -832,7 +832,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.6615247377906</v>
+        <v>152.6581379605081</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -840,7 +840,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.2311461640565</v>
+        <v>153.228995534446</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -848,7 +848,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.422416089479</v>
+        <v>152.4218445585651</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -856,7 +856,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>153.039818749383</v>
+        <v>153.0342097977967</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -864,7 +864,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.8702293344758</v>
+        <v>152.8626142891461</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -872,7 +872,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.9440784217209</v>
+        <v>152.9343301618229</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -880,7 +880,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.6811407687885</v>
+        <v>154.6694034035157</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -888,7 +888,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.6351146410357</v>
+        <v>155.6236331265417</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -896,7 +896,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.6489510030797</v>
+        <v>156.6365478430624</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -904,7 +904,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>158.3317883409347</v>
+        <v>158.3184270141325</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -912,7 +912,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.8878422725998</v>
+        <v>159.877226972831</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -920,7 +920,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.6293662745288</v>
+        <v>161.6227733745599</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -928,7 +928,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.7862745231539</v>
+        <v>159.7918753826286</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -936,7 +936,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.5614889161681</v>
+        <v>159.5646444419313</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -944,7 +944,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>158.8792421401487</v>
+        <v>158.8935902639064</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -952,7 +952,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.0350102853525</v>
+        <v>157.0531605914263</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -960,7 +960,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.5847548764707</v>
+        <v>157.6017172785567</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -968,7 +968,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>157.9353952510507</v>
+        <v>157.9505025313811</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -976,7 +976,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>157.9948280140434</v>
+        <v>158.0087756723367</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -984,7 +984,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.2580497186091</v>
+        <v>159.2707816026206</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -992,7 +992,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.2970017142037</v>
+        <v>158.3016717171525</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1000,7 +1000,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.8594487376556</v>
+        <v>155.8532274313008</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1008,7 +1008,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>156.0132173009657</v>
+        <v>156.006562884901</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1016,7 +1016,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.7291021985092</v>
+        <v>156.7258245643609</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1024,7 +1024,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.6548437549537</v>
+        <v>156.6406695891844</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1032,7 +1032,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.4377226391862</v>
+        <v>156.4230856701351</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1040,7 +1040,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>156.2972347660272</v>
+        <v>156.2819966074485</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1048,7 +1048,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.3951038888844</v>
+        <v>157.3862381528138</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1056,7 +1056,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.5988820089149</v>
+        <v>158.6011076970484</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1064,7 +1064,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.0404500540017</v>
+        <v>159.0633612480295</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1072,7 +1072,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.5496268774027</v>
+        <v>159.5627229653279</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1080,7 +1080,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.3754714776136</v>
+        <v>159.4126463058357</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1088,7 +1088,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>159.8331483428509</v>
+        <v>159.9067896478244</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1096,7 +1096,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>159.463131297524</v>
+        <v>159.6198085568704</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1104,7 +1104,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.1286414408619</v>
+        <v>159.3530471581773</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1112,7 +1112,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>159.4715369388451</v>
+        <v>159.6886206473274</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1120,7 +1120,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>159.5938678985513</v>
+        <v>159.7976007965204</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1128,7 +1128,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>159.6607279816927</v>
+        <v>159.8493437158979</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1136,7 +1136,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>159.4380600905707</v>
+        <v>159.632467187729</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1144,7 +1144,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>159.1144665372801</v>
+        <v>159.2636582561268</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1152,7 +1152,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>158.9233598969007</v>
+        <v>159.0039722099297</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1160,7 +1160,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>159.1069932754959</v>
+        <v>159.0807845729236</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1168,7 +1168,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>159.9141052103334</v>
+        <v>159.996000032802</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1176,7 +1176,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>159.3204679237588</v>
+        <v>159.1379267752899</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1184,7 +1184,15 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>159.400142316897</v>
+        <v>159.1303826692029</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B104">
+        <v>158.9663811897176</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -696,7 +696,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.4232659352207</v>
+        <v>139.4185206595057</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -704,7 +704,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.6455797928875</v>
+        <v>142.6386911374355</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -712,7 +712,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.9381413786734</v>
+        <v>143.9307590216585</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -720,7 +720,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.6206132775391</v>
+        <v>144.6131108825587</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -728,7 +728,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.55027162235</v>
+        <v>144.542636341654</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -736,7 +736,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.4747144694096</v>
+        <v>144.4669668022741</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -744,7 +744,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.4322336887959</v>
+        <v>144.4244409301872</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -752,7 +752,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.4713055636286</v>
+        <v>144.4635264547441</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -760,7 +760,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>145.1409726260754</v>
+        <v>145.1332576116442</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -768,7 +768,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0338074910877</v>
+        <v>148.0339372217461</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -776,7 +776,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4308530541309</v>
+        <v>148.4308834445784</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -784,7 +784,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8534695137901</v>
+        <v>148.8534738887143</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -792,7 +792,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.8998619955358</v>
+        <v>148.9008146728819</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -800,7 +800,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2878519403513</v>
+        <v>149.2881036353953</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -808,7 +808,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4371885558905</v>
+        <v>150.4359197908356</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -816,7 +816,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.9377828277309</v>
+        <v>151.9345750776138</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -824,7 +824,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.3314457394651</v>
+        <v>152.3280521108463</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -832,7 +832,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.6581379605081</v>
+        <v>152.6549046677332</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -840,7 +840,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.228995534446</v>
+        <v>153.2269420076191</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -848,7 +848,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4218445585651</v>
+        <v>152.4213006009573</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -856,7 +856,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>153.0342097977967</v>
+        <v>153.0288740285057</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -864,7 +864,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.8626142891461</v>
+        <v>152.8553647624178</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -872,7 +872,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.9343301618229</v>
+        <v>152.9250396217891</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -880,7 +880,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.6694034035157</v>
+        <v>154.6582122537668</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -888,7 +888,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.6236331265417</v>
+        <v>155.6126756419453</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -896,7 +896,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.6365478430624</v>
+        <v>156.6247027790461</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -904,7 +904,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>158.3184270141325</v>
+        <v>158.3056537588778</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -912,7 +912,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.877226972831</v>
+        <v>159.8670478517792</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -920,7 +920,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.6227733745599</v>
+        <v>161.6164343124611</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -928,7 +928,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.7918753826286</v>
+        <v>159.7971594580991</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -936,7 +936,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.5646444419313</v>
+        <v>159.5676068710097</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -944,7 +944,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>158.8935902639064</v>
+        <v>158.9072311263351</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -952,7 +952,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.0531605914263</v>
+        <v>157.0704382005518</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -960,7 +960,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.6017172785567</v>
+        <v>157.6178853647698</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -968,7 +968,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>157.9505025313811</v>
+        <v>157.9649273363114</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -976,7 +976,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.0087756723367</v>
+        <v>158.0221476693171</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -984,7 +984,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.2707816026206</v>
+        <v>159.2830091968157</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -992,7 +992,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.3016717171525</v>
+        <v>158.30620270273</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1000,7 +1000,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.8532274313008</v>
+        <v>155.847327360502</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1008,7 +1008,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>156.006562884901</v>
+        <v>156.0002520369116</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1016,7 +1016,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.7258245643609</v>
+        <v>156.7227398049238</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1024,7 +1024,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.6406695891844</v>
+        <v>156.6271319027853</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1032,7 +1032,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.4230856701351</v>
+        <v>156.4090889109802</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1040,7 +1040,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>156.2819966074485</v>
+        <v>156.2673918984686</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1048,7 +1048,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.3862381528138</v>
+        <v>157.3777326985422</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1056,7 +1056,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6011076970484</v>
+        <v>158.603248976272</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1064,7 +1064,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.0633612480295</v>
+        <v>159.0667002214496</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1072,7 +1072,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.5627229653279</v>
+        <v>159.6286234141035</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1080,7 +1080,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.4126463058357</v>
+        <v>159.5329630739932</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1088,7 +1088,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>159.9067896478244</v>
+        <v>160.0027612279178</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1096,7 +1096,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>159.6198085568704</v>
+        <v>159.8006439701218</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1104,7 +1104,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.3530471581773</v>
+        <v>159.591765836054</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1112,7 +1112,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>159.6886206473274</v>
+        <v>159.9363391863685</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1120,7 +1120,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>159.7976007965204</v>
+        <v>160.0741663771831</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1128,7 +1128,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>159.8493437158979</v>
+        <v>160.1668750317399</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1136,7 +1136,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>159.632467187729</v>
+        <v>159.9789559094847</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1144,7 +1144,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>159.2636582561268</v>
+        <v>159.6802678729714</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1152,7 +1152,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>159.0039722099297</v>
+        <v>159.5554564758997</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1160,7 +1160,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>159.0807845729236</v>
+        <v>159.7267943705471</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1168,7 +1168,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>159.996000032802</v>
+        <v>160.8695194111716</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1176,7 +1176,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>159.1379267752899</v>
+        <v>160.889934618601</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1184,7 +1184,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>159.1303826692029</v>
+        <v>161.2293963845129</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1192,7 +1192,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>158.9663811897176</v>
+        <v>162.649913751442</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -696,7 +696,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.4185206595057</v>
+        <v>139.4139959720549</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -704,7 +704,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.6386911374355</v>
+        <v>142.6321203753656</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -712,7 +712,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.9307590216585</v>
+        <v>143.9237137536427</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -720,7 +720,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.6131108825587</v>
+        <v>144.6059473680248</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -728,7 +728,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.542636341654</v>
+        <v>144.5353461792859</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -736,7 +736,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.4669668022741</v>
+        <v>144.4595695565192</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -744,7 +744,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.4244409301872</v>
+        <v>144.4170007444447</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -752,7 +752,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.4635264547441</v>
+        <v>144.456099315353</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -760,7 +760,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>145.1332576116442</v>
+        <v>145.1258877802038</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -768,7 +768,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0339372217461</v>
+        <v>148.0340607380578</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -776,7 +776,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4308834445784</v>
+        <v>148.4309123012504</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -784,7 +784,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8534738887143</v>
+        <v>148.8534779517236</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -792,7 +792,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9008146728819</v>
+        <v>148.901721841952</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -800,7 +800,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2881036353953</v>
+        <v>149.2883453856147</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -808,7 +808,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4359197908356</v>
+        <v>150.4347108482263</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -816,7 +816,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.9345750776138</v>
+        <v>151.931512670559</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -824,7 +824,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.3280521108463</v>
+        <v>152.3248113435375</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -832,7 +832,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.6549046677332</v>
+        <v>152.6518147057551</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -840,7 +840,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.2269420076191</v>
+        <v>153.2249791777636</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -848,7 +848,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4213006009573</v>
+        <v>152.4207822681021</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -856,7 +856,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>153.0288740285057</v>
+        <v>153.0237920321351</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -864,7 +864,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.8553647624178</v>
+        <v>152.8484551837302</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -872,7 +872,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.9250396217891</v>
+        <v>152.9161754555202</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -880,7 +880,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.6582122537668</v>
+        <v>154.6475302728554</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -888,7 +888,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.6126756419453</v>
+        <v>155.6022074099695</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -896,7 +896,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.6247027790461</v>
+        <v>156.6133793820547</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -904,7 +904,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>158.3056537588778</v>
+        <v>158.2934311798257</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -912,7 +912,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.8670478517792</v>
+        <v>159.8572795104335</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -920,7 +920,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.6164343124611</v>
+        <v>161.6103355221138</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -928,7 +928,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.7971594580991</v>
+        <v>159.8021520326583</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -936,7 +936,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.5676068710097</v>
+        <v>159.5703924380024</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -944,7 +944,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>158.9072311263351</v>
+        <v>158.9202152906135</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -952,7 +952,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.0704382005518</v>
+        <v>157.0869040179014</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -960,7 +960,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.6178853647698</v>
+        <v>157.6333129914113</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -968,7 +968,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>157.9649273363114</v>
+        <v>157.9787140804991</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -976,7 +976,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.0221476693171</v>
+        <v>158.0349779187665</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -984,7 +984,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.2830091968157</v>
+        <v>159.2947606074276</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -992,7 +992,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.30620270273</v>
+        <v>158.3105987761815</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1000,7 +1000,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.847327360502</v>
+        <v>155.8417246024463</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1008,7 +1008,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>156.0002520369116</v>
+        <v>155.9942592238432</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1016,7 +1016,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.7227398049238</v>
+        <v>156.719832212461</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1024,7 +1024,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.6271319027853</v>
+        <v>156.6141892152743</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1032,7 +1032,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.4090889109802</v>
+        <v>156.3956918990992</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1040,7 +1040,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>156.2673918984686</v>
+        <v>156.2533828120961</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1048,7 +1048,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.3777326985422</v>
+        <v>157.3695665165978</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1056,7 +1056,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.603248976272</v>
+        <v>158.6053102729203</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1064,7 +1064,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.0667002214496</v>
+        <v>159.0699179904011</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1072,7 +1072,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.6286234141035</v>
+        <v>159.6329328764652</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1080,7 +1080,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.5329630739932</v>
+        <v>159.5901068334614</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1088,7 +1088,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.0027612279178</v>
+        <v>160.0505218236718</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1096,7 +1096,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>159.8006439701218</v>
+        <v>159.864587849626</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1104,7 +1104,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.591765836054</v>
+        <v>159.6736778309974</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1112,7 +1112,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>159.9363391863685</v>
+        <v>159.9641233984882</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1120,7 +1120,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>160.0741663771831</v>
+        <v>160.0743188956808</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1128,7 +1128,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>160.1668750317399</v>
+        <v>160.1289481070874</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1136,7 +1136,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>159.9789559094847</v>
+        <v>159.890691594428</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1144,7 +1144,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>159.6802678729714</v>
+        <v>159.5306923977139</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1152,7 +1152,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>159.5554564758997</v>
+        <v>159.2814984539298</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1160,7 +1160,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>159.7267943705471</v>
+        <v>159.3051109536941</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1168,7 +1168,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>160.8695194111716</v>
+        <v>160.0281760542622</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1176,7 +1176,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>160.889934618601</v>
+        <v>159.8670973466056</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1184,7 +1184,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>161.2293963845129</v>
+        <v>160.1827330869549</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1192,7 +1192,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>162.649913751442</v>
+        <v>161.0408542124751</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -30,8 +30,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -47,7 +55,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -55,13 +63,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -357,22 +383,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B104"/>
+  <dimension ref="A1:B105"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="2">
+      <c r="A2" s="3">
         <v>44743</v>
       </c>
       <c r="B2">
@@ -380,7 +406,7 @@
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="2">
+      <c r="A3" s="3">
         <v>44778</v>
       </c>
       <c r="B3">
@@ -388,7 +414,7 @@
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="2">
+      <c r="A4" s="3">
         <v>44806</v>
       </c>
       <c r="B4">
@@ -396,7 +422,7 @@
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="2">
+      <c r="A5" s="3">
         <v>44834</v>
       </c>
       <c r="B5">
@@ -404,7 +430,7 @@
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="2">
+      <c r="A6" s="3">
         <v>44869</v>
       </c>
       <c r="B6">
@@ -412,7 +438,7 @@
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="2">
+      <c r="A7" s="3">
         <v>44897</v>
       </c>
       <c r="B7">
@@ -420,7 +446,7 @@
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="2">
+      <c r="A8" s="3">
         <v>44932</v>
       </c>
       <c r="B8">
@@ -428,7 +454,7 @@
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="2">
+      <c r="A9" s="3">
         <v>44960</v>
       </c>
       <c r="B9">
@@ -436,7 +462,7 @@
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="2">
+      <c r="A10" s="3">
         <v>44988</v>
       </c>
       <c r="B10">
@@ -444,7 +470,7 @@
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="2">
+      <c r="A11" s="3">
         <v>45016</v>
       </c>
       <c r="B11">
@@ -452,7 +478,7 @@
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="2">
+      <c r="A12" s="3">
         <v>45051</v>
       </c>
       <c r="B12">
@@ -460,7 +486,7 @@
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="2">
+      <c r="A13" s="3">
         <v>45079</v>
       </c>
       <c r="B13">
@@ -468,7 +494,7 @@
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="2">
+      <c r="A14" s="3">
         <v>45107</v>
       </c>
       <c r="B14">
@@ -476,7 +502,7 @@
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="2">
+      <c r="A15" s="3">
         <v>45142</v>
       </c>
       <c r="B15">
@@ -484,7 +510,7 @@
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="2">
+      <c r="A16" s="3">
         <v>45170</v>
       </c>
       <c r="B16">
@@ -492,7 +518,7 @@
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="2">
+      <c r="A17" s="3">
         <v>45205</v>
       </c>
       <c r="B17">
@@ -500,7 +526,7 @@
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="2">
+      <c r="A18" s="3">
         <v>45233</v>
       </c>
       <c r="B18">
@@ -508,7 +534,7 @@
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="2">
+      <c r="A19" s="3">
         <v>45261</v>
       </c>
       <c r="B19">
@@ -516,7 +542,7 @@
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="2">
+      <c r="A20" s="3">
         <v>45296</v>
       </c>
       <c r="B20">
@@ -524,7 +550,7 @@
       </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="2">
+      <c r="A21" s="3">
         <v>45324</v>
       </c>
       <c r="B21">
@@ -532,7 +558,7 @@
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="2">
+      <c r="A22" s="3">
         <v>45352</v>
       </c>
       <c r="B22">
@@ -540,7 +566,7 @@
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="2">
+      <c r="A23" s="3">
         <v>45387</v>
       </c>
       <c r="B23">
@@ -548,7 +574,7 @@
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="2">
+      <c r="A24" s="3">
         <v>45415</v>
       </c>
       <c r="B24">
@@ -556,7 +582,7 @@
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="2">
+      <c r="A25" s="3">
         <v>45443</v>
       </c>
       <c r="B25">
@@ -564,7 +590,7 @@
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="2">
+      <c r="A26" s="3">
         <v>45478</v>
       </c>
       <c r="B26">
@@ -572,7 +598,7 @@
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="2">
+      <c r="A27" s="3">
         <v>45506</v>
       </c>
       <c r="B27">
@@ -580,7 +606,7 @@
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="2">
+      <c r="A28" s="3">
         <v>45541</v>
       </c>
       <c r="B28">
@@ -588,7 +614,7 @@
       </c>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="2">
+      <c r="A29" s="3">
         <v>45569</v>
       </c>
       <c r="B29">
@@ -596,7 +622,7 @@
       </c>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="2">
+      <c r="A30" s="3">
         <v>45597</v>
       </c>
       <c r="B30">
@@ -604,7 +630,7 @@
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="2">
+      <c r="A31" s="3">
         <v>45632</v>
       </c>
       <c r="B31">
@@ -612,7 +638,7 @@
       </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="2">
+      <c r="A32" s="3">
         <v>45660</v>
       </c>
       <c r="B32">
@@ -620,7 +646,7 @@
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="2">
+      <c r="A33" s="3">
         <v>45688</v>
       </c>
       <c r="B33">
@@ -628,7 +654,7 @@
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="2">
+      <c r="A34" s="3">
         <v>45716</v>
       </c>
       <c r="B34">
@@ -636,7 +662,7 @@
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="2">
+      <c r="A35" s="3">
         <v>45751</v>
       </c>
       <c r="B35">
@@ -644,7 +670,7 @@
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="2">
+      <c r="A36" s="3">
         <v>45779</v>
       </c>
       <c r="B36">
@@ -652,7 +678,7 @@
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="2">
+      <c r="A37" s="3">
         <v>45814</v>
       </c>
       <c r="B37">
@@ -660,7 +686,7 @@
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="2">
+      <c r="A38" s="3">
         <v>45821</v>
       </c>
       <c r="B38">
@@ -668,7 +694,7 @@
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="2">
+      <c r="A39" s="3">
         <v>45828</v>
       </c>
       <c r="B39">
@@ -676,7 +702,7 @@
       </c>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="2">
+      <c r="A40" s="3">
         <v>45835</v>
       </c>
       <c r="B40">
@@ -684,7 +710,7 @@
       </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="2">
+      <c r="A41" s="3">
         <v>45842</v>
       </c>
       <c r="B41">
@@ -692,507 +718,515 @@
       </c>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42" s="2">
+      <c r="A42" s="3">
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.4139959720549</v>
+        <v>139.4096768434906</v>
       </c>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" s="2">
+      <c r="A43" s="3">
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.6321203753656</v>
+        <v>142.6258460066152</v>
       </c>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" s="2">
+      <c r="A44" s="3">
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.9237137536427</v>
+        <v>143.9169830209669</v>
       </c>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" s="2">
+      <c r="A45" s="3">
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.6059473680248</v>
+        <v>144.5991003132127</v>
       </c>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" s="2">
+      <c r="A46" s="3">
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.5353461792859</v>
+        <v>144.5283782857256</v>
       </c>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47" s="2">
+      <c r="A47" s="3">
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.4595695565192</v>
+        <v>144.4524995162745</v>
       </c>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" s="2">
+      <c r="A48" s="3">
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.4170007444447</v>
+        <v>144.4098897654817</v>
       </c>
     </row>
     <row r="49" spans="1:2">
-      <c r="A49" s="2">
+      <c r="A49" s="3">
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.456099315353</v>
+        <v>144.4490008183514</v>
       </c>
     </row>
     <row r="50" spans="1:2">
-      <c r="A50" s="2">
+      <c r="A50" s="3">
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>145.1258877802038</v>
+        <v>145.1188405222828</v>
       </c>
     </row>
     <row r="51" spans="1:2">
-      <c r="A51" s="2">
+      <c r="A51" s="3">
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0340607380578</v>
+        <v>148.0341784750266</v>
       </c>
     </row>
     <row r="52" spans="1:2">
-      <c r="A52" s="2">
+      <c r="A52" s="3">
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4309123012504</v>
+        <v>148.4309397362585</v>
       </c>
     </row>
     <row r="53" spans="1:2">
-      <c r="A53" s="2">
+      <c r="A53" s="3">
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8534779517236</v>
+        <v>148.8534817308497</v>
       </c>
     </row>
     <row r="54" spans="1:2">
-      <c r="A54" s="2">
+      <c r="A54" s="3">
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.901721841952</v>
+        <v>148.9025866817092</v>
       </c>
     </row>
     <row r="55" spans="1:2">
-      <c r="A55" s="2">
+      <c r="A55" s="3">
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2883453856147</v>
+        <v>149.2885777446372</v>
       </c>
     </row>
     <row r="56" spans="1:2">
-      <c r="A56" s="2">
+      <c r="A56" s="3">
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4347108482263</v>
+        <v>150.4335576072465</v>
       </c>
     </row>
     <row r="57" spans="1:2">
-      <c r="A57" s="2">
+      <c r="A57" s="3">
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.931512670559</v>
+        <v>151.9285859737053</v>
       </c>
     </row>
     <row r="58" spans="1:2">
-      <c r="A58" s="2">
+      <c r="A58" s="3">
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.3248113435375</v>
+        <v>152.3217133673009</v>
       </c>
     </row>
     <row r="59" spans="1:2">
-      <c r="A59" s="2">
+      <c r="A59" s="3">
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.6518147057551</v>
+        <v>152.6488587928356</v>
       </c>
     </row>
     <row r="60" spans="1:2">
-      <c r="A60" s="2">
+      <c r="A60" s="3">
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.2249791777636</v>
+        <v>153.2231011881389</v>
       </c>
     </row>
     <row r="61" spans="1:2">
-      <c r="A61" s="2">
+      <c r="A61" s="3">
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4207822681021</v>
+        <v>152.4202877908174</v>
       </c>
     </row>
     <row r="62" spans="1:2">
-      <c r="A62" s="2">
+      <c r="A62" s="3">
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>153.0237920321351</v>
+        <v>153.0189461891477</v>
       </c>
     </row>
     <row r="63" spans="1:2">
-      <c r="A63" s="2">
+      <c r="A63" s="3">
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.8484551837302</v>
+        <v>152.8418623021497</v>
       </c>
     </row>
     <row r="64" spans="1:2">
-      <c r="A64" s="2">
+      <c r="A64" s="3">
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.9161754555202</v>
+        <v>152.9077091020358</v>
       </c>
     </row>
     <row r="65" spans="1:2">
-      <c r="A65" s="2">
+      <c r="A65" s="3">
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.6475302728554</v>
+        <v>154.6373236714886</v>
       </c>
     </row>
     <row r="66" spans="1:2">
-      <c r="A66" s="2">
+      <c r="A66" s="3">
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.6022074099695</v>
+        <v>155.5921966374831</v>
       </c>
     </row>
     <row r="67" spans="1:2">
-      <c r="A67" s="2">
+      <c r="A67" s="3">
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.6133793820547</v>
+        <v>156.6025442890269</v>
       </c>
     </row>
     <row r="68" spans="1:2">
-      <c r="A68" s="2">
+      <c r="A68" s="3">
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>158.2934311798257</v>
+        <v>158.2817249317994</v>
       </c>
     </row>
     <row r="69" spans="1:2">
-      <c r="A69" s="2">
+      <c r="A69" s="3">
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.8572795104335</v>
+        <v>159.8478983906173</v>
       </c>
     </row>
     <row r="70" spans="1:2">
-      <c r="A70" s="2">
+      <c r="A70" s="3">
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.6103355221138</v>
+        <v>161.6044643015769</v>
       </c>
     </row>
     <row r="71" spans="1:2">
-      <c r="A71" s="2">
+      <c r="A71" s="3">
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.8021520326583</v>
+        <v>159.8068758309717</v>
       </c>
     </row>
     <row r="72" spans="1:2">
-      <c r="A72" s="2">
+      <c r="A72" s="3">
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.5703924380024</v>
+        <v>159.5730156721039</v>
       </c>
     </row>
     <row r="73" spans="1:2">
-      <c r="A73" s="2">
+      <c r="A73" s="3">
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>158.9202152906135</v>
+        <v>158.9325886517641</v>
       </c>
     </row>
     <row r="74" spans="1:2">
-      <c r="A74" s="2">
+      <c r="A74" s="3">
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.0869040179014</v>
+        <v>157.1026134579831</v>
       </c>
     </row>
     <row r="75" spans="1:2">
-      <c r="A75" s="2">
+      <c r="A75" s="3">
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.6333129914113</v>
+        <v>157.6480493117472</v>
       </c>
     </row>
     <row r="76" spans="1:2">
-      <c r="A76" s="2">
+      <c r="A76" s="3">
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>157.9787140804991</v>
+        <v>157.9919034803422</v>
       </c>
     </row>
     <row r="77" spans="1:2">
-      <c r="A77" s="2">
+      <c r="A77" s="3">
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.0349779187665</v>
+        <v>158.0472978198711</v>
       </c>
     </row>
     <row r="78" spans="1:2">
-      <c r="A78" s="2">
+      <c r="A78" s="3">
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.2947606074276</v>
+        <v>159.3060620180586</v>
       </c>
     </row>
     <row r="79" spans="1:2">
-      <c r="A79" s="2">
+      <c r="A79" s="3">
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.3105987761815</v>
+        <v>158.314864153192</v>
       </c>
     </row>
     <row r="80" spans="1:2">
-      <c r="A80" s="2">
+      <c r="A80" s="3">
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.8417246024463</v>
+        <v>155.836397525019</v>
       </c>
     </row>
     <row r="81" spans="1:2">
-      <c r="A81" s="2">
+      <c r="A81" s="3">
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.9942592238432</v>
+        <v>155.9885613485779</v>
       </c>
     </row>
     <row r="82" spans="1:2">
-      <c r="A82" s="2">
+      <c r="A82" s="3">
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.719832212461</v>
+        <v>156.7170876832163</v>
       </c>
     </row>
     <row r="83" spans="1:2">
-      <c r="A83" s="2">
+      <c r="A83" s="3">
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.6141892152743</v>
+        <v>156.601803534232</v>
       </c>
     </row>
     <row r="84" spans="1:2">
-      <c r="A84" s="2">
+      <c r="A84" s="3">
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.3956918990992</v>
+        <v>156.3828574529044</v>
       </c>
     </row>
     <row r="85" spans="1:2">
-      <c r="A85" s="2">
+      <c r="A85" s="3">
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>156.2533828120961</v>
+        <v>156.2399343929229</v>
       </c>
     </row>
     <row r="86" spans="1:2">
-      <c r="A86" s="2">
+      <c r="A86" s="3">
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.3695665165978</v>
+        <v>157.3617201525039</v>
       </c>
     </row>
     <row r="87" spans="1:2">
-      <c r="A87" s="2">
+      <c r="A87" s="3">
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6053102729203</v>
+        <v>158.6072957388863</v>
       </c>
     </row>
     <row r="88" spans="1:2">
-      <c r="A88" s="2">
+      <c r="A88" s="3">
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.0699179904011</v>
+        <v>159.0730206019171</v>
       </c>
     </row>
     <row r="89" spans="1:2">
-      <c r="A89" s="2">
+      <c r="A89" s="3">
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.6329328764652</v>
+        <v>159.6370918126125</v>
       </c>
     </row>
     <row r="90" spans="1:2">
-      <c r="A90" s="2">
+      <c r="A90" s="3">
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.5901068334614</v>
+        <v>159.5905208637731</v>
       </c>
     </row>
     <row r="91" spans="1:2">
-      <c r="A91" s="2">
+      <c r="A91" s="3">
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.0505218236718</v>
+        <v>160.153482737259</v>
       </c>
     </row>
     <row r="92" spans="1:2">
-      <c r="A92" s="2">
+      <c r="A92" s="3">
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>159.864587849626</v>
+        <v>159.9930506585352</v>
       </c>
     </row>
     <row r="93" spans="1:2">
-      <c r="A93" s="2">
+      <c r="A93" s="3">
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.6736778309974</v>
+        <v>159.8061146908759</v>
       </c>
     </row>
     <row r="94" spans="1:2">
-      <c r="A94" s="2">
+      <c r="A94" s="3">
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>159.9641233984882</v>
+        <v>160.0529573912211</v>
       </c>
     </row>
     <row r="95" spans="1:2">
-      <c r="A95" s="2">
+      <c r="A95" s="3">
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>160.0743188956808</v>
+        <v>160.1254910598625</v>
       </c>
     </row>
     <row r="96" spans="1:2">
-      <c r="A96" s="2">
+      <c r="A96" s="3">
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>160.1289481070874</v>
+        <v>160.1352314654277</v>
       </c>
     </row>
     <row r="97" spans="1:2">
-      <c r="A97" s="2">
+      <c r="A97" s="3">
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>159.890691594428</v>
+        <v>159.8484570425276</v>
       </c>
     </row>
     <row r="98" spans="1:2">
-      <c r="A98" s="2">
+      <c r="A98" s="3">
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>159.5306923977139</v>
+        <v>159.4607816581416</v>
       </c>
     </row>
     <row r="99" spans="1:2">
-      <c r="A99" s="2">
+      <c r="A99" s="3">
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>159.2814984539298</v>
+        <v>159.1727528310382</v>
       </c>
     </row>
     <row r="100" spans="1:2">
-      <c r="A100" s="2">
+      <c r="A100" s="3">
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>159.3051109536941</v>
+        <v>159.0431168314598</v>
       </c>
     </row>
     <row r="101" spans="1:2">
-      <c r="A101" s="2">
+      <c r="A101" s="3">
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>160.0281760542622</v>
+        <v>159.4994226134742</v>
       </c>
     </row>
     <row r="102" spans="1:2">
-      <c r="A102" s="2">
+      <c r="A102" s="3">
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>159.8670973466056</v>
+        <v>160.0090731716102</v>
       </c>
     </row>
     <row r="103" spans="1:2">
-      <c r="A103" s="2">
+      <c r="A103" s="3">
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>160.1827330869549</v>
+        <v>160.3085353884741</v>
       </c>
     </row>
     <row r="104" spans="1:2">
-      <c r="A104" s="2">
+      <c r="A104" s="3">
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>161.0408542124751</v>
+        <v>161.0685483522819</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B105">
+        <v>158.5244585880601</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B105"/>
+  <dimension ref="A1:B106"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.4096768434906</v>
+        <v>139.4055495792279</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.6258460066152</v>
+        <v>142.6198484264612</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.9169830209669</v>
+        <v>143.9105462364532</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.5991003132127</v>
+        <v>144.5925492297284</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.5283782857256</v>
+        <v>144.5217117821737</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.4524995162745</v>
+        <v>144.4457354693472</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.4098897654817</v>
+        <v>144.4030866445395</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.4490008183514</v>
+        <v>144.4422096506907</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>145.1188405222828</v>
+        <v>145.1120951564684</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0341784750266</v>
+        <v>148.034290828069</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4309397362585</v>
+        <v>148.4309658511345</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8534817308497</v>
+        <v>148.8534852510836</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9025866817092</v>
+        <v>148.9034120822478</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2885777446372</v>
+        <v>149.288801228269</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4335576072465</v>
+        <v>150.4324563159991</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.9285859737053</v>
+        <v>151.9257861847418</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.3217133673009</v>
+        <v>152.3187489748285</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.6488587928356</v>
+        <v>152.6460284280448</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.2231011881389</v>
+        <v>153.2213026737265</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4202877908174</v>
+        <v>152.4198155591186</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>153.0189461891477</v>
+        <v>153.0143204688418</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.8418623021497</v>
+        <v>152.8355649303483</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.9077091020358</v>
+        <v>152.8996144842886</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.6373236714886</v>
+        <v>154.6275615694681</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.5921966374831</v>
+        <v>155.5826142050653</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.6025442890269</v>
+        <v>156.5921668910523</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>158.2817249317994</v>
+        <v>158.2705034212671</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.8478983906173</v>
+        <v>159.8388826229453</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.6044643015769</v>
+        <v>161.5988087569497</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.8068758309717</v>
+        <v>159.8113513291212</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.5730156721039</v>
+        <v>159.5754896096128</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>158.9325886517641</v>
+        <v>158.9443929591696</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.1026134579831</v>
+        <v>157.1176170446713</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.6480493117472</v>
+        <v>157.6621392720873</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>157.9919034803422</v>
+        <v>158.0045329226738</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.0472978198711</v>
+        <v>158.0591364740242</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.3060620180586</v>
+        <v>159.3169378349396</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.314864153192</v>
+        <v>158.3190030970584</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.836397525019</v>
+        <v>155.8313265217951</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.9885613485779</v>
+        <v>155.9831374696002</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.7170876832163</v>
+        <v>156.7144935227766</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.601803534232</v>
+        <v>156.5899400005622</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.3828574529044</v>
+        <v>156.3705513524673</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>156.2399343929229</v>
+        <v>156.2270142992485</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.3617201525039</v>
+        <v>157.3541755709647</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6072957388863</v>
+        <v>158.6092092685588</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.0730206019171</v>
+        <v>159.0760137515897</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.6370918126125</v>
+        <v>159.6411073554434</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.5905208637731</v>
+        <v>159.5909388348083</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.153482737259</v>
+        <v>160.1541985545095</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>159.9930506585352</v>
+        <v>160.1328406321477</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.8061146908759</v>
+        <v>159.9812784630596</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.0529573912211</v>
+        <v>160.2007982866214</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>160.1254910598625</v>
+        <v>160.2470553505478</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>160.1352314654277</v>
+        <v>160.2204079772922</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>159.8484570425276</v>
+        <v>159.8711371228848</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>159.4607816581416</v>
+        <v>159.4205839287291</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>159.1727528310382</v>
+        <v>159.1191040327615</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>159.0431168314598</v>
+        <v>158.9743478563277</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>159.4994226134742</v>
+        <v>159.2264464941501</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>160.0090731716102</v>
+        <v>160.235311801848</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>160.3085353884741</v>
+        <v>160.5228216408453</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>161.0685483522819</v>
+        <v>161.2164739202119</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,15 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>158.5244585880601</v>
+        <v>160.3224552043648</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106" s="3">
+        <v>46297</v>
+      </c>
+      <c r="B106">
+        <v>162.3289468601464</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B106"/>
+  <dimension ref="A1:B107"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.4055495792279</v>
+        <v>139.4016016745333</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.6198484264612</v>
+        <v>142.6141097212448</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.9105462364532</v>
+        <v>143.9043845698225</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.5925492297284</v>
+        <v>144.5862753580266</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.5217117821737</v>
+        <v>144.5153275528709</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.4457354693472</v>
+        <v>144.4392579959185</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.4030866445395</v>
+        <v>144.3965718373706</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.4422096506907</v>
+        <v>144.4357063008948</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>145.1120951564684</v>
+        <v>145.1056327286316</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.034290828069</v>
+        <v>148.0343981574089</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4309658511345</v>
+        <v>148.4309907380421</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8534852510836</v>
+        <v>148.8534885347611</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9034120822478</v>
+        <v>148.9042006768274</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.288801228269</v>
+        <v>149.2890163173376</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4324563159991</v>
+        <v>150.4314035512339</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.9257861847418</v>
+        <v>151.9231052445277</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.3187489748285</v>
+        <v>152.3159097315228</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.6460284280448</v>
+        <v>152.6433158112387</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.2213026737265</v>
+        <v>153.2195787108897</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4198155591186</v>
+        <v>152.4193641047086</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>153.0143204688418</v>
+        <v>153.0099002547607</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.8355649303483</v>
+        <v>152.8295437216124</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.8996144842886</v>
+        <v>152.8918677460559</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.6275615694681</v>
+        <v>154.618215690889</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.5826142050653</v>
+        <v>155.5734333941535</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.5921668910523</v>
+        <v>156.5822190583459</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>158.2705034212671</v>
+        <v>158.2597375413547</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.8388826229453</v>
+        <v>159.830211887786</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.5988087569497</v>
+        <v>161.5933577485342</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.8113513291212</v>
+        <v>159.8155970211323</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.5754896096128</v>
+        <v>159.5778259760496</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>158.9443929591696</v>
+        <v>158.9556662709355</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.1176170446713</v>
+        <v>157.1319609348691</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.6621392720873</v>
+        <v>157.6756240471875</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.0045329226738</v>
+        <v>158.0166367913519</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.0591364740242</v>
+        <v>158.0705208813725</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.3169378349396</v>
+        <v>159.3274108218334</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.3190030970584</v>
+        <v>158.3230198701937</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.8313265217951</v>
+        <v>155.8264937826581</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.9831374696002</v>
+        <v>155.9779685580335</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.7144935227766</v>
+        <v>156.7120382785648</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.5899400005622</v>
+        <v>156.5785665756181</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.3705513524673</v>
+        <v>156.35874205585</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>156.2270142992485</v>
+        <v>156.2145925711577</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.3541755709647</v>
+        <v>157.3469160332907</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6092092685588</v>
+        <v>158.6110545152218</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.0760137515897</v>
+        <v>159.0789028028566</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.6411073554434</v>
+        <v>159.6449862570765</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.5909388348083</v>
+        <v>159.59135912324</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1541985545095</v>
+        <v>160.1549148498565</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.1328406321477</v>
+        <v>160.1293984845383</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.9812784630596</v>
+        <v>159.975322129632</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.2007982866214</v>
+        <v>160.3233100336962</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>160.2470553505478</v>
+        <v>160.3749456764161</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>160.2204079772922</v>
+        <v>160.3459010333222</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>159.8711371228848</v>
+        <v>159.9770553962673</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>159.4205839287291</v>
+        <v>159.49666982402</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>159.1191040327615</v>
+        <v>159.1307951366097</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>158.9743478563277</v>
+        <v>158.9131720044288</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>159.2264464941501</v>
+        <v>159.0747888842635</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>160.235311801848</v>
+        <v>159.9017680738047</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>160.5228216408453</v>
+        <v>160.0747953147248</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>161.2164739202119</v>
+        <v>160.6660621293998</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>160.3224552043648</v>
+        <v>159.8183925654801</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,15 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>162.3289468601464</v>
+        <v>160.68842467705</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107" s="3">
+        <v>46304</v>
+      </c>
+      <c r="B107">
+        <v>159.1498043682565</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>160.3749456764161</v>
+        <v>160.3936579011628</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>160.3459010333222</v>
+        <v>160.3971506680866</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>159.9770553962673</v>
+        <v>160.1367963378719</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>159.49666982402</v>
+        <v>159.7603672780962</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>159.1307951366097</v>
+        <v>159.5374610295297</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>158.9131720044288</v>
+        <v>159.4910527959944</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>159.0747888842635</v>
+        <v>159.8967716115584</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>159.9017680738047</v>
+        <v>160.9607539312859</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>160.0747953147248</v>
+        <v>161.5333522056596</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>160.6660621293998</v>
+        <v>162.5583622437526</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>159.8183925654801</v>
+        <v>163.6609026787775</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>160.68842467705</v>
+        <v>166.4734026787775</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>159.1498043682565</v>
+        <v>169.2859026787775</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.4016016745333</v>
+        <v>139.3978216880662</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.6141097212448</v>
+        <v>142.60861348995</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.9043845698225</v>
+        <v>143.898480764337</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.5862753580266</v>
+        <v>144.5802614890738</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.5153275528709</v>
+        <v>144.5092080631006</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.4392579959185</v>
+        <v>144.4330492833934</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.3965718373706</v>
+        <v>144.3903274177691</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.4357063008948</v>
+        <v>144.4294728728861</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>145.1056327286316</v>
+        <v>145.0994358356716</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0343981574089</v>
+        <v>148.0345007919002</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4309907380421</v>
+        <v>148.4310144808254</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8534885347611</v>
+        <v>148.8534916018916</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9042006768274</v>
+        <v>148.9049548697416</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2890163173376</v>
+        <v>149.2892234603363</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4314035512339</v>
+        <v>150.4303961832265</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.9231052445277</v>
+        <v>151.9205357604851</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.3159097315228</v>
+        <v>152.3131878963319</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.6433158112387</v>
+        <v>152.6407137726313</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.2195787108897</v>
+        <v>153.2179247730678</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4193641047086</v>
+        <v>152.4189320857272</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>153.0099002547607</v>
+        <v>153.005672192561</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.8295437216124</v>
+        <v>152.8237809750356</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.8918677460559</v>
+        <v>152.884447021436</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.618215690889</v>
+        <v>154.6092600966685</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.5734333941535</v>
+        <v>155.5646296466274</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.5822190583459</v>
+        <v>156.5726748970901</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>158.2597375413547</v>
+        <v>158.2494004362114</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.830211887786</v>
+        <v>159.8218672882953</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.5933577485342</v>
+        <v>161.5881008396707</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.8155970211323</v>
+        <v>159.8196296490038</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.5778259760496</v>
+        <v>159.5800353427581</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>158.9556662709355</v>
+        <v>158.9664433501801</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.1319609348691</v>
+        <v>157.1456873768134</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.6756240471875</v>
+        <v>157.6885414233377</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.0166367913519</v>
+        <v>158.0282467570654</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.0705208813725</v>
+        <v>158.0814761189559</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.3274108218334</v>
+        <v>159.3375022249023</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.3230198701937</v>
+        <v>158.3269186969858</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.8264937826581</v>
+        <v>155.8218830946231</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.9779685580335</v>
+        <v>155.9730372864883</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.7120382785648</v>
+        <v>156.7097115952193</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.5785665756181</v>
+        <v>156.5676537646268</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.35874205585</v>
+        <v>156.3474004467125</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>156.2145925711577</v>
+        <v>156.2026414217805</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.3469160332907</v>
+        <v>157.3399259867041</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6110545152218</v>
+        <v>158.6128349067627</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.0789028028566</v>
+        <v>159.0816928060624</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.6449862570765</v>
+        <v>159.6487349054529</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.59135912324</v>
+        <v>159.5917803514219</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1549148498565</v>
+        <v>160.1556297503328</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.1293984845383</v>
+        <v>160.126112983269</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.975322129632</v>
+        <v>159.9696118184889</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.3233100336962</v>
+        <v>160.4297499032135</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>160.3936579011628</v>
+        <v>160.520019185977</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>160.3971506680866</v>
+        <v>160.5481094036306</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>160.1367963378719</v>
+        <v>160.3612736341543</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>159.7603672780962</v>
+        <v>160.0440157306162</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>159.5374610295297</v>
+        <v>159.8817035630116</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>159.4910527959944</v>
+        <v>159.9088657889118</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>159.8967716115584</v>
+        <v>160.4131492108406</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>160.9607539312859</v>
+        <v>161.5004071568036</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>161.5333522056596</v>
+        <v>162.2850724188941</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>162.5583622437526</v>
+        <v>163.5100825962621</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>163.6609026787775</v>
+        <v>165.324153825468</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>166.4734026787775</v>
+        <v>167.956426787739</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>169.2859026787775</v>
+        <v>170.768926787739</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B107"/>
+  <dimension ref="A1:B108"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.3978216880662</v>
+        <v>139.3941991312104</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.60861348995</v>
+        <v>142.603344687897</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.898480764337</v>
+        <v>143.8928189759179</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.5802614890738</v>
+        <v>144.5744918076104</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.5092080631006</v>
+        <v>144.5033371992504</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.4330492833934</v>
+        <v>144.4270929637049</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.3903274177691</v>
+        <v>144.3843369137267</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.4294728728861</v>
+        <v>144.4234929224012</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>145.0994358356716</v>
+        <v>145.0934884703653</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0345007919002</v>
+        <v>148.0345990323625</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4310144808254</v>
+        <v>148.4310371559216</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8534916018916</v>
+        <v>148.8534944704409</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9049548697416</v>
+        <v>148.9056768606405</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2892234603363</v>
+        <v>149.2894230758756</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4303961832265</v>
+        <v>150.4294313450549</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.9205357604851</v>
+        <v>151.9180709392521</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.3131878963319</v>
+        <v>152.3105763520932</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.6407137726313</v>
+        <v>152.6382157106538</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.2179247730678</v>
+        <v>153.2163366916819</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4189320857272</v>
+        <v>152.41851827343</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>153.005672192561</v>
+        <v>153.0016240570527</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.8237809750356</v>
+        <v>152.818260464842</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.884447021436</v>
+        <v>152.8773322323504</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.6092600966685</v>
+        <v>154.6006709492038</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.5646296466274</v>
+        <v>155.5561803524652</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.5726748970901</v>
+        <v>156.5635105339856</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>158.2494004362114</v>
+        <v>158.2394672911144</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.8218672882953</v>
+        <v>159.8138312345797</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.5881008396707</v>
+        <v>161.5830282484478</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.8196296490038</v>
+        <v>159.8234644018728</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.5800353427581</v>
+        <v>159.5821272620026</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>158.9664433501801</v>
+        <v>158.9767560116767</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.1456873768134</v>
+        <v>157.1588351122737</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.6885414233377</v>
+        <v>157.7009261362288</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.0282467570654</v>
+        <v>158.0393920349619</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.0814761189559</v>
+        <v>158.0920255021745</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.3375022249023</v>
+        <v>159.3472318880013</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.3269186969858</v>
+        <v>158.3307037356617</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.8218830946231</v>
+        <v>155.8174796683639</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.9730372864883</v>
+        <v>155.96832784501</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.7097115952193</v>
+        <v>156.7075040893494</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.5676537646268</v>
+        <v>156.5571743716584</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.3474004467125</v>
+        <v>156.3364996093514</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>156.2026414217805</v>
+        <v>156.1911350492482</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.3399259867041</v>
+        <v>157.3331909642986</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6128349067627</v>
+        <v>158.6145536605979</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.0816928060624</v>
+        <v>159.0843885170264</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.6487349054529</v>
+        <v>159.6523593416341</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.5917803514219</v>
+        <v>159.5922013515902</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1556297503328</v>
+        <v>160.1563416773838</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.126112983269</v>
+        <v>160.1229738673058</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.9696118184889</v>
+        <v>159.9641327213473</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.4297499032135</v>
+        <v>160.4250920411132</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>160.520019185977</v>
+        <v>160.6673215829362</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>160.5481094036306</v>
+        <v>160.7018584040761</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>160.3612736341543</v>
+        <v>160.5282491446354</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.0440157306162</v>
+        <v>160.2390547865163</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>159.8817035630116</v>
+        <v>160.1150554703284</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>159.9088657889118</v>
+        <v>160.1637104909785</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>160.4131492108406</v>
+        <v>160.6977114063021</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>161.5004071568036</v>
+        <v>161.7546384507791</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>162.2850724188941</v>
+        <v>162.4930816541737</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>163.5100825962621</v>
+        <v>163.7252305308762</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>165.324153825468</v>
+        <v>165.5494787450296</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>167.956426787739</v>
+        <v>167.8214120627377</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,15 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>170.768926787739</v>
+        <v>170.4346945388154</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108" s="3">
+        <v>46311</v>
+      </c>
+      <c r="B108">
+        <v>168.7264736830914</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.3941991312104</v>
+        <v>139.390724370943</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.603344687897</v>
+        <v>142.5982894894187</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.8928189759179</v>
+        <v>143.8873846315929</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.5744918076104</v>
+        <v>144.5689517540231</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.5033371992504</v>
+        <v>144.4977001278795</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.4270929637049</v>
+        <v>144.4213739699659</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.3843369137267</v>
+        <v>144.378585163078</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.4234929224012</v>
+        <v>144.4177513128663</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>145.0934884703653</v>
+        <v>145.0877758844357</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0345990323625</v>
+        <v>148.0346931545011</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4310371559216</v>
+        <v>148.431058833156</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8534944704409</v>
+        <v>148.8534971565755</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9056768606405</v>
+        <v>148.9063686658208</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2894230758756</v>
+        <v>149.289615554949</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4294313450549</v>
+        <v>150.4285064056472</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.9180709392521</v>
+        <v>151.915704527319</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.3105763520932</v>
+        <v>152.3080685440841</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.6382157106538</v>
+        <v>152.6358155369878</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.2163366916819</v>
+        <v>153.2148106215523</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.41851827343</v>
+        <v>152.4181215405153</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>153.0016240570527</v>
+        <v>152.9977446356531</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.818260464842</v>
+        <v>152.812967290438</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.8773322323504</v>
+        <v>152.8705049101777</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.6006709492038</v>
+        <v>154.5924263047706</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.5561803524652</v>
+        <v>155.5480646617539</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.5635105339856</v>
+        <v>156.5547039249464</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>158.2394672911144</v>
+        <v>158.2299151451722</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.8138312345797</v>
+        <v>159.8060873380701</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.5830282484478</v>
+        <v>161.5781308023582</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.8234644018728</v>
+        <v>159.8271150889852</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.5821272620026</v>
+        <v>159.5841103838789</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>158.9767560116767</v>
+        <v>158.9866334259097</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.1588351122737</v>
+        <v>157.1714397304384</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.7009261362288</v>
+        <v>157.7128101696266</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.0393920349619</v>
+        <v>158.0500996140748</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.0920255021745</v>
+        <v>158.102190731182</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.3472318880013</v>
+        <v>159.3566183589368</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.3307037356617</v>
+        <v>158.3343790572904</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.8174796683639</v>
+        <v>155.813269986684</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.96832784501</v>
+        <v>155.9638257801906</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.7075040893494</v>
+        <v>156.7054072407502</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.5571743716584</v>
+        <v>156.5471032820739</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.3364996093514</v>
+        <v>156.3260146278431</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>156.1911350492482</v>
+        <v>156.1800494671311</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.3331909642986</v>
+        <v>157.3266974945535</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6145536605979</v>
+        <v>158.6162137977693</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.0843885170264</v>
+        <v>159.0869944149406</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.6523593416341</v>
+        <v>159.655865277337</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.5922013515902</v>
+        <v>159.5926211355689</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1563416773838</v>
+        <v>160.1570493042994</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.1229738673058</v>
+        <v>160.1199717388215</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.9641327213473</v>
+        <v>159.9588711850003</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.4250920411132</v>
+        <v>160.4206191838855</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>160.6673215829362</v>
+        <v>160.7830688189394</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>160.7018584040761</v>
+        <v>160.8237567705021</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>160.5282491446354</v>
+        <v>160.6643732797419</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.2390547865163</v>
+        <v>160.4098597311932</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.1150554703284</v>
+        <v>160.3259850318935</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>160.1637104909785</v>
+        <v>160.4022230709066</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>160.6977114063021</v>
+        <v>160.9701560429082</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>161.7546384507791</v>
+        <v>162.0077447137426</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>162.4930816541737</v>
+        <v>162.7058104767083</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>163.7252305308762</v>
+        <v>163.9389684763225</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>165.5494787450296</v>
+        <v>165.7846880621353</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>167.8214120627377</v>
+        <v>167.8251336619496</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>170.4346945388154</v>
+        <v>169.9949171854136</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>168.7264736830914</v>
+        <v>169.0559787879221</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.390724370943</v>
+        <v>139.3873885443472</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.5982894894187</v>
+        <v>142.5934351668856</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.8873846315929</v>
+        <v>143.8821643046176</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.5689517540231</v>
+        <v>144.5636279023056</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.4977001278795</v>
+        <v>144.4922831712102</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.4213739699659</v>
+        <v>144.4158784098389</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.378585163078</v>
+        <v>144.373058185986</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.4177513128663</v>
+        <v>144.4122340880874</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>145.0877758844357</v>
+        <v>145.0822844673986</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0346931545011</v>
+        <v>148.0347834114695</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.431058833156</v>
+        <v>148.4310795764373</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8534971565755</v>
+        <v>148.8534996748721</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9063686658208</v>
+        <v>148.9070321369156</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.289615554949</v>
+        <v>149.2898012630235</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4285064056472</v>
+        <v>150.4276189460722</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.915704527319</v>
+        <v>151.9134307585679</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.3080685440841</v>
+        <v>152.3056584256767</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.6358155369878</v>
+        <v>152.6335076278324</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.2148106215523</v>
+        <v>153.2133430102349</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4181215405153</v>
+        <v>152.4177408508675</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.9977446356531</v>
+        <v>152.9940236259492</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.812967290438</v>
+        <v>152.8078877443225</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.8705049101777</v>
+        <v>152.8639480382433</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.5924263047706</v>
+        <v>154.5845059299396</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.5480646617539</v>
+        <v>155.5402633178873</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.5547039249464</v>
+        <v>156.5462346848849</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>158.2299151451722</v>
+        <v>158.2207227239082</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.8060873380701</v>
+        <v>159.7986203152284</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.5781308023582</v>
+        <v>161.5733998958915</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.8271150889852</v>
+        <v>159.8305942903589</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.5841103838789</v>
+        <v>159.5859925577886</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>158.9866334259097</v>
+        <v>158.9961023864911</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.1714397304384</v>
+        <v>157.1835339800789</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.7128101696266</v>
+        <v>157.7242230199964</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.0500996140748</v>
+        <v>158.0603944619975</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.102190731182</v>
+        <v>158.1119920236723</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.3566183589368</v>
+        <v>159.3656789872712</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.3343790572904</v>
+        <v>158.3379486304448</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.813269986684</v>
+        <v>155.8092416717842</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.9638257801906</v>
+        <v>155.9595178541403</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.7054072407502</v>
+        <v>156.7034132976451</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.5471032820739</v>
+        <v>156.5374172689666</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.3260146278431</v>
+        <v>156.3159224063995</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>156.1800494671311</v>
+        <v>156.1693623513803</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.3266974945535</v>
+        <v>157.3204330194147</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6162137977693</v>
+        <v>158.6178181561934</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.0869944149406</v>
+        <v>159.0895147194839</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.655865277337</v>
+        <v>159.6592581123658</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.5926211355689</v>
+        <v>159.5930388690719</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1570493042994</v>
+        <v>160.1577515200655</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.1199717388215</v>
+        <v>160.1170979755302</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.9588711850003</v>
+        <v>159.9538146018226</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.4206191838855</v>
+        <v>160.4163206344938</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>160.7830688189394</v>
+        <v>160.874265163332</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>160.8237567705021</v>
+        <v>160.9188664082331</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>160.6643732797419</v>
+        <v>160.7707312108539</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.4098597311932</v>
+        <v>160.5435639459421</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.3259850318935</v>
+        <v>160.4912499445491</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>160.4022230709066</v>
+        <v>160.5879650214949</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>160.9701560429082</v>
+        <v>161.1771961634852</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>162.0077447137426</v>
+        <v>162.192404211403</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>162.7058104767083</v>
+        <v>162.8562619260922</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>163.9389684763225</v>
+        <v>164.0838136238205</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>165.7846880621353</v>
+        <v>165.9225818902496</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>167.8251336619496</v>
+        <v>167.7935177503736</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>169.9949171854136</v>
+        <v>169.6884663789619</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>169.0559787879221</v>
+        <v>169.0828128939182</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.3873885443472</v>
+        <v>139.3811016470931</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.5934351668856</v>
+        <v>142.5842831004387</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.8821643046176</v>
+        <v>143.8723170767055</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.5636279023056</v>
+        <v>144.5535801320392</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.4922831712102</v>
+        <v>144.4820600199356</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.4158784098389</v>
+        <v>144.4055072335612</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.373058185986</v>
+        <v>144.3626278799402</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.4122340880874</v>
+        <v>144.4018222061611</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>145.0822844673986</v>
+        <v>145.0719157542377</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0347834114695</v>
+        <v>148.034953243022</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4310795764373</v>
+        <v>148.4311184907811</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8534996748721</v>
+        <v>148.853504259385</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9070321369156</v>
+        <v>148.9082807568449</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2898012630235</v>
+        <v>149.2901537118013</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4276189460722</v>
+        <v>150.4259477283504</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.9134307585679</v>
+        <v>151.909140249465</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.3056584256767</v>
+        <v>152.3011093279179</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.6335076278324</v>
+        <v>152.6291481753305</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.2133430102349</v>
+        <v>153.2105702574121</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4177408508675</v>
+        <v>152.4170238596759</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.9940236259492</v>
+        <v>152.9870196516481</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.8078877443225</v>
+        <v>152.7983199858724</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.8639480382433</v>
+        <v>152.8515840172256</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.5845059299396</v>
+        <v>154.5695646486095</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.5402633178873</v>
+        <v>155.5255337369924</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.5462346848849</v>
+        <v>156.5302341719928</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>158.2207227239082</v>
+        <v>158.2033395056165</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.7986203152284</v>
+        <v>159.7844607625855</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.5733998958915</v>
+        <v>161.5644058802658</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.8305942903589</v>
+        <v>159.8370831831147</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.5859925577886</v>
+        <v>159.5894819745992</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>158.9961023864911</v>
+        <v>159.0139116241976</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.1835339800789</v>
+        <v>157.2063097916022</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.7242230199964</v>
+        <v>157.745742104927</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.0603944619975</v>
+        <v>158.0798368057431</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.1119920236723</v>
+        <v>158.1305769695845</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.3656789872712</v>
+        <v>159.3828866555414</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.3379486304448</v>
+        <v>158.3447858315276</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.8092416717842</v>
+        <v>155.801684642553</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.9595178541403</v>
+        <v>155.9514368154411</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.7034132976451</v>
+        <v>156.699706476642</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.5374172689666</v>
+        <v>156.5191159862578</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.3159224063995</v>
+        <v>156.29683201208</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>156.1693623513803</v>
+        <v>156.1491017180109</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.3204330194147</v>
+        <v>157.3085449495575</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6178181561934</v>
+        <v>158.6208700464864</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.0895147194839</v>
+        <v>159.0943142263096</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.6592581123658</v>
+        <v>159.6657246220954</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.5930388690719</v>
+        <v>159.593865489083</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1577515200655</v>
+        <v>160.1591361725082</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.1170979755302</v>
+        <v>160.111704478086</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.9538146018226</v>
+        <v>159.9442705186758</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.4163206344938</v>
+        <v>160.408207601955</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>160.874265163332</v>
+        <v>161.0723621495939</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>160.9188664082331</v>
+        <v>161.1114651142923</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>160.7707312108539</v>
+        <v>160.9688809817071</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.5435639459421</v>
+        <v>160.7471915343046</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.4912499445491</v>
+        <v>160.7125830510299</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>160.5879650214949</v>
+        <v>160.7906072794115</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>161.1771961634852</v>
+        <v>161.3343053003883</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>162.192404211403</v>
+        <v>162.2580043159115</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>162.8562619260922</v>
+        <v>162.8013703112961</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>164.0838136238205</v>
+        <v>163.8880934715282</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>165.9225818902496</v>
+        <v>165.3672867474529</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>167.7935177503736</v>
+        <v>166.8382819175902</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>169.6884663789619</v>
+        <v>168.3631225428601</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>169.0828128939182</v>
+        <v>167.7119835753039</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.3811016470931</v>
+        <v>139.3781360645118</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.5842831004387</v>
+        <v>142.5799644893485</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.8723170767055</v>
+        <v>143.8676681203606</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.5535801320392</v>
+        <v>144.5488341157157</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.4820600199356</v>
+        <v>144.4772313159458</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.4055072335612</v>
+        <v>144.4006087575585</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.3626278799402</v>
+        <v>144.3577015484811</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.4018222061611</v>
+        <v>144.3969045855854</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>145.0719157542377</v>
+        <v>145.067016017164</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.034953243022</v>
+        <v>148.0350332301677</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4311184907811</v>
+        <v>148.4311367652115</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.853504259385</v>
+        <v>148.8535063483358</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9082807568449</v>
+        <v>148.9088689242981</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2901537118013</v>
+        <v>149.2903210723669</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4259477283504</v>
+        <v>150.4251600166228</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.909140249465</v>
+        <v>151.9071140209406</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.3011093279179</v>
+        <v>152.2989603883208</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.6291481753305</v>
+        <v>152.6270873403017</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.2105702574121</v>
+        <v>153.2092592439593</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4170238596759</v>
+        <v>152.4166858656288</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.9870196516481</v>
+        <v>152.9837198717024</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.7983199858724</v>
+        <v>152.7938093392563</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.8515840172256</v>
+        <v>152.8457489161418</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.5695646486095</v>
+        <v>154.5625104506074</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.5255337369924</v>
+        <v>155.5185736971024</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.5302341719928</v>
+        <v>156.5226691371809</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>158.2033395056165</v>
+        <v>158.1951133180679</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.7844607625855</v>
+        <v>159.7777424387998</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.5644058802658</v>
+        <v>161.5601280528322</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.8370831831147</v>
+        <v>159.8401129934515</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.5894819745992</v>
+        <v>159.5911016532715</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.0139116241976</v>
+        <v>159.0222955931374</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.2063097916022</v>
+        <v>157.2170449804041</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.745742104927</v>
+        <v>157.7558968844085</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.0798368057431</v>
+        <v>158.0890256821633</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.1305769695845</v>
+        <v>158.1393946764714</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.3828866555414</v>
+        <v>159.3910631770347</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.3447858315276</v>
+        <v>158.3480608033365</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.801684642553</v>
+        <v>155.7981358880978</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.9514368154411</v>
+        <v>155.9476422607791</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.699706476642</v>
+        <v>156.6979812424232</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.5191159862578</v>
+        <v>156.5104622382865</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.29683201208</v>
+        <v>156.287795380466</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>156.1491017180109</v>
+        <v>156.1394906839529</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.3085449495575</v>
+        <v>157.302900171725</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6208700464864</v>
+        <v>158.6223224461958</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.0943142263096</v>
+        <v>159.0966007123477</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.6657246220954</v>
+        <v>159.6688076880049</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.593865489083</v>
+        <v>159.5942732954577</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1591361725082</v>
+        <v>160.1598172106828</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.111704478086</v>
+        <v>160.1091707247484</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.9442705186758</v>
+        <v>159.9397622065653</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.408207601955</v>
+        <v>160.4043754450242</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.0723621495939</v>
+        <v>161.1574555009543</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.1114651142923</v>
+        <v>161.1835374033394</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>160.9688809817071</v>
+        <v>161.0338221420558</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.7471915343046</v>
+        <v>160.783127302436</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.7125830510299</v>
+        <v>160.7291284892044</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>160.7906072794115</v>
+        <v>160.7616839549522</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>161.3343053003883</v>
+        <v>161.2339825798852</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>162.2580043159115</v>
+        <v>162.0793858052526</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>162.8013703112961</v>
+        <v>162.5789436955155</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>163.8880934715282</v>
+        <v>163.5144020394167</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>165.3672867474529</v>
+        <v>164.6367975957044</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>166.8382819175902</v>
+        <v>165.9601360201654</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>168.3631225428601</v>
+        <v>167.1868030918611</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>167.7119835753039</v>
+        <v>166.3400803699537</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B108"/>
+  <dimension ref="A1:B109"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.3781360645118</v>
+        <v>139.37528027994</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.5799644893485</v>
+        <v>142.5758048611452</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.8676681203606</v>
+        <v>143.8631889059979</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.5488341157157</v>
+        <v>144.5442599441406</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.4772313159458</v>
+        <v>144.4725775430983</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.4006087575585</v>
+        <v>144.39588782791</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.3577015484811</v>
+        <v>144.3529538168686</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.3969045855854</v>
+        <v>144.3921652544828</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>145.067016017164</v>
+        <v>145.0622924059836</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0350332301677</v>
+        <v>148.0351101805899</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4311367652115</v>
+        <v>148.4311543133159</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535063483358</v>
+        <v>148.8535083151771</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9088689242981</v>
+        <v>148.9094348191471</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2903210723669</v>
+        <v>149.2904829047817</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4251600166228</v>
+        <v>150.4244018466133</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.9071140209406</v>
+        <v>151.9051613897682</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2989603883208</v>
+        <v>152.2968891456759</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.6270873403017</v>
+        <v>152.6251001212096</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.2092592439593</v>
+        <v>153.20799490438</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4166858656288</v>
+        <v>152.416360516496</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.9837198717024</v>
+        <v>152.9805447393684</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.7938093392563</v>
+        <v>152.7894672792037</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.8457489161418</v>
+        <v>152.8401281531857</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.5625104506074</v>
+        <v>154.5557136955978</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.5185736971024</v>
+        <v>155.5118641747105</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.5226691371809</v>
+        <v>156.5153737172655</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>158.1951133180679</v>
+        <v>158.1871758446875</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.7777424387998</v>
+        <v>159.7712492610774</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.5601280528322</v>
+        <v>161.555987262625</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.8401129934515</v>
+        <v>159.8430117463055</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.5911016532715</v>
+        <v>159.592645382211</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.0222955931374</v>
+        <v>159.0303588407453</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.2170449804041</v>
+        <v>157.2273774653475</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.7558968844085</v>
+        <v>157.7656779236777</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.0890256821633</v>
+        <v>158.0978848673013</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.1393946764714</v>
+        <v>158.1479167437309</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.3910631770347</v>
+        <v>159.3989729647669</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.3480608033365</v>
+        <v>158.3512447075552</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7981358880978</v>
+        <v>155.7947282493477</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.9476422607791</v>
+        <v>155.9439987789892</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6979812424232</v>
+        <v>156.6963340814112</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.5104622382865</v>
+        <v>156.5021163483828</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.287795380466</v>
+        <v>156.279074344731</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>156.1394906839529</v>
+        <v>156.1302028673</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.302900171725</v>
+        <v>157.2974419055396</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6223224461958</v>
+        <v>158.6237288236966</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.0966007123477</v>
+        <v>159.0988162006416</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.6688076880049</v>
+        <v>159.6717964668853</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.5942732954577</v>
+        <v>159.5946768615877</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1598172106828</v>
+        <v>160.1604899990949</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.1091707247484</v>
+        <v>160.1067371838529</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.9397622065653</v>
+        <v>159.9354170764799</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.4043754450242</v>
+        <v>160.4006821250239</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.1574555009543</v>
+        <v>161.1520958794071</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.1835374033394</v>
+        <v>161.2639470316331</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.0338221420558</v>
+        <v>161.1198614237517</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.783127302436</v>
+        <v>160.8624681136048</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.7291284892044</v>
+        <v>160.7836064025257</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>160.7616839549522</v>
+        <v>160.8153847997033</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>161.2339825798852</v>
+        <v>161.2476040466067</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>162.0793858052526</v>
+        <v>162.0217068205059</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>162.5789436955155</v>
+        <v>162.4882834340561</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>163.5144020394167</v>
+        <v>163.335095588732</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>164.6367975957044</v>
+        <v>164.2928561173972</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>165.9601360201654</v>
+        <v>165.4187889328587</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>167.1868030918611</v>
+        <v>166.4254743472666</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,15 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>166.3400803699537</v>
+        <v>165.5370569928371</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109" s="3">
+        <v>46318</v>
+      </c>
+      <c r="B109">
+        <v>163.1708069928371</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.37528027994</v>
+        <v>139.3725283071106</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.5758048611452</v>
+        <v>142.5717955976276</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.8631889059979</v>
+        <v>143.8588703087217</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.5442599441406</v>
+        <v>144.5398484583554</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.4725775430983</v>
+        <v>144.4680893728877</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.39588782791</v>
+        <v>144.3913349718661</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.3529538168686</v>
+        <v>144.3483751537432</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.3921652544828</v>
+        <v>144.387594697752</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>145.0622924059836</v>
+        <v>145.0577356045175</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0351101805899</v>
+        <v>148.0351842637225</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4311543133159</v>
+        <v>148.4311711772421</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535083151771</v>
+        <v>148.8535101688488</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9094348191471</v>
+        <v>148.9099796815174</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2904829047817</v>
+        <v>149.290639472834</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4244018466133</v>
+        <v>150.4236715903073</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.9051613897682</v>
+        <v>151.903278424376</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2968891456759</v>
+        <v>152.2948914688011</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.6251001212096</v>
+        <v>152.6231826535978</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.20799490438</v>
+        <v>153.2067747954434</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.416360516496</v>
+        <v>152.4160471156285</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.9805447393684</v>
+        <v>152.9774873393454</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.7894672792037</v>
+        <v>152.7852845566735</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.8401281531857</v>
+        <v>152.8347101654888</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.5557136955978</v>
+        <v>154.5491605910134</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.5118641747105</v>
+        <v>155.5053919494767</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.5153737172655</v>
+        <v>156.5083338418313</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>158.1871758446875</v>
+        <v>158.1795122780967</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.7712492610774</v>
+        <v>159.7649702988231</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.555987262625</v>
+        <v>161.5519771990404</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.8430117463055</v>
+        <v>159.8457875552255</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.592645382211</v>
+        <v>159.5941181303548</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.0303588407453</v>
+        <v>159.0381193170138</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.2273774653475</v>
+        <v>157.2373293635169</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.7656779236777</v>
+        <v>157.7751053353056</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.0978848673013</v>
+        <v>158.1064316139812</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.1479167437309</v>
+        <v>158.1561575788822</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.3989729647669</v>
+        <v>159.406628588951</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.3512447075552</v>
+        <v>158.3543408977798</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7947282493477</v>
+        <v>155.7914535485272</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.9439987789892</v>
+        <v>155.9404976172052</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6963340814112</v>
+        <v>156.6947600278785</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.5021163483828</v>
+        <v>156.4940622764708</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.279074344731</v>
+        <v>156.2706527986764</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>156.1302028673</v>
+        <v>156.1212224250886</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.2974419055396</v>
+        <v>157.2921611745616</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6237288236966</v>
+        <v>158.6250912715631</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.0988162006416</v>
+        <v>159.1009638396498</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.6717964668853</v>
+        <v>159.6746950437098</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.5946768615877</v>
+        <v>159.5950758523418</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1604899990949</v>
+        <v>160.1611541243479</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.1067371838529</v>
+        <v>160.1043981134919</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.9354170764799</v>
+        <v>159.9312264812158</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.4006821250239</v>
+        <v>160.3971202934677</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.1520958794071</v>
+        <v>161.1469201769617</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.2639470316331</v>
+        <v>161.3816697229904</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.1198614237517</v>
+        <v>161.24802028547</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.8624681136048</v>
+        <v>160.9828196796217</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.7836064025257</v>
+        <v>160.8891758769168</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>160.8153847997033</v>
+        <v>160.9287250168692</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>161.2476040466067</v>
+        <v>161.3377924767377</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>162.0217068205059</v>
+        <v>162.060058386607</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>162.4882834340561</v>
+        <v>162.5060847710714</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>163.335095588732</v>
+        <v>163.2945975061181</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>164.2928561173972</v>
+        <v>164.1529510706201</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>165.4187889328587</v>
+        <v>165.1351314034551</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>166.4254743472666</v>
+        <v>166.0064037381586</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>165.5370569928371</v>
+        <v>165.175808318844</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>163.1708069928371</v>
+        <v>162.8095583188441</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.24802028547</v>
+        <v>161.247178930248</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.9828196796217</v>
+        <v>160.981749974026</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.8891758769168</v>
+        <v>160.8843984886799</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>160.9287250168692</v>
+        <v>160.9231941044847</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>161.3377924767377</v>
+        <v>161.3287682375994</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>162.060058386607</v>
+        <v>162.0473120667259</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>162.5060847710714</v>
+        <v>162.4905328768322</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>163.2945975061181</v>
+        <v>163.2978747806547</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>164.1529510706201</v>
+        <v>164.1489915178092</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>165.1351314034551</v>
+        <v>165.1287849874248</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>166.0064037381586</v>
+        <v>166.000650430492</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>165.175808318844</v>
+        <v>165.1673450752138</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>162.8095583188441</v>
+        <v>162.8010950752139</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.247178930248</v>
+        <v>161.2478074999975</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.981749974026</v>
+        <v>160.9827670129071</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.8843984886799</v>
+        <v>160.8892410766454</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>160.9231941044847</v>
+        <v>160.9279193575258</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>161.3287682375994</v>
+        <v>161.3379720217852</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>162.0473120667259</v>
+        <v>162.0607531580508</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>162.4905328768322</v>
+        <v>162.4810845256634</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>163.2978747806547</v>
+        <v>163.2921926084899</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>164.1489915178092</v>
+        <v>164.1597279384877</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>165.1287849874248</v>
+        <v>165.1325204078335</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>166.000650430492</v>
+        <v>166.0081611680839</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>165.1673450752138</v>
+        <v>165.1790094377079</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>162.8010950752139</v>
+        <v>162.8127594377079</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.3725283071106</v>
+        <v>139.3698745871107</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.5717955976276</v>
+        <v>142.5679286922923</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.8588703087217</v>
+        <v>143.854703845829</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.5398484583554</v>
+        <v>144.5355911383277</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.4680893728877</v>
+        <v>144.4637581279237</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.3913349718661</v>
+        <v>144.386941378203</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.3483751537432</v>
+        <v>144.3439566935362</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.387594697752</v>
+        <v>144.3831840649692</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>145.0577356045175</v>
+        <v>145.0533369413542</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0351842637225</v>
+        <v>148.0352556366437</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4311711772421</v>
+        <v>148.4311873959585</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535101688488</v>
+        <v>148.8535119175007</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9099796815174</v>
+        <v>148.9105046612469</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.290639472834</v>
+        <v>149.2907910242423</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4236715903073</v>
+        <v>150.4229677369347</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.903278424376</v>
+        <v>151.9014614678548</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2948914688011</v>
+        <v>152.2929635137482</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.6231826535978</v>
+        <v>152.6213313380855</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.2067747954434</v>
+        <v>153.2055966411255</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4160471156285</v>
+        <v>152.4157450166318</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.9774873393454</v>
+        <v>152.9745412574586</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.7852845566735</v>
+        <v>152.7812525850595</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.8347101654888</v>
+        <v>152.8294842048589</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.5491605910134</v>
+        <v>154.5428383089382</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.5053919494767</v>
+        <v>155.4991447105661</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.5083338418313</v>
+        <v>156.5015363963679</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>158.1795122780967</v>
+        <v>158.1721087971423</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.7649702988231</v>
+        <v>159.7588953025947</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.5519771990404</v>
+        <v>161.5480919197498</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.8457875552255</v>
+        <v>159.8484478899777</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.5941181303548</v>
+        <v>159.5955244560758</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.0381193170138</v>
+        <v>159.0455936641646</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.2373293635169</v>
+        <v>157.246921210045</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.7751053353056</v>
+        <v>157.7841978243768</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.1064316139812</v>
+        <v>158.1146820045218</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.1561575788822</v>
+        <v>158.1641306843555</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.406628588951</v>
+        <v>159.4140418628989</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.3543408977798</v>
+        <v>158.3573526001</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7914535485272</v>
+        <v>155.7883042228187</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.9404976172052</v>
+        <v>155.937130679858</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6947600278785</v>
+        <v>156.6932545165316</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.4940622764708</v>
+        <v>156.4862850707019</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.2706527986764</v>
+        <v>156.2625157035659</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>156.1212224250886</v>
+        <v>156.1125345191491</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.2921611745616</v>
+        <v>157.2870495608553</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6250912715631</v>
+        <v>158.6264117621247</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1009638396498</v>
+        <v>159.103046602795</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.6746950437098</v>
+        <v>159.6775072847548</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.5950758523418</v>
+        <v>159.5954699948343</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1611541243479</v>
+        <v>160.1618092595419</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.1043981134919</v>
+        <v>160.1021481966485</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.9312264812158</v>
+        <v>159.9271823701019</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.3971202934677</v>
+        <v>160.3936831071845</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.1469201769617</v>
+        <v>161.141919206015</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.3816697229904</v>
+        <v>161.4793098277011</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.2478074999975</v>
+        <v>161.3542000934357</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.9827670129071</v>
+        <v>161.0829584144043</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.8892410766454</v>
+        <v>160.9791408297868</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>160.9279193575258</v>
+        <v>161.023683980999</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>161.3379720217852</v>
+        <v>161.4159343446781</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>162.0607531580508</v>
+        <v>162.0971722181183</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>162.4810845256634</v>
+        <v>162.4803833105383</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>163.2921926084899</v>
+        <v>163.2405886943104</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>164.1597279384877</v>
+        <v>164.039364215927</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>165.1325204078335</v>
+        <v>164.8908497411612</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>166.0081611680839</v>
+        <v>165.6630014968951</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>165.1790094377079</v>
+        <v>164.8964233832073</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>162.8127594377079</v>
+        <v>162.6718433452216</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.3698745871107</v>
+        <v>139.3673139509193</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.5679286922923</v>
+        <v>142.5641966970222</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.854703845829</v>
+        <v>143.8506816213198</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.5355911383277</v>
+        <v>144.5314800482421</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.4637581279237</v>
+        <v>144.459575726146</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.386941378203</v>
+        <v>144.3826988405152</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.3439566935362</v>
+        <v>144.3396901793822</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.3831840649692</v>
+        <v>144.3789251133938</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>145.0533369413542</v>
+        <v>145.0490883350955</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0352556366437</v>
+        <v>148.0353244451802</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4311873959585</v>
+        <v>148.4312030055462</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535119175007</v>
+        <v>148.8535135685736</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9105046612469</v>
+        <v>148.9110108259473</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2907910242423</v>
+        <v>149.2909377918153</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4229677369347</v>
+        <v>150.4222888826206</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.9014614678548</v>
+        <v>151.8997071144252</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2929635137482</v>
+        <v>152.2911016993117</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.6213313380855</v>
+        <v>152.6195428180878</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.2055966411255</v>
+        <v>153.2044583185796</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4157450166318</v>
+        <v>152.4154536189139</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.9745412574586</v>
+        <v>152.9717005361675</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.7812525850595</v>
+        <v>152.7773633820941</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.8294842048589</v>
+        <v>152.8244402674729</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.5428383089382</v>
+        <v>154.5367349035052</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.4991447105661</v>
+        <v>155.4931109801591</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.5015363963679</v>
+        <v>156.4949691430095</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>158.1721087971423</v>
+        <v>158.1649524869631</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.7588953025947</v>
+        <v>159.753014653285</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.5480919197498</v>
+        <v>161.544325825536</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.8484478899777</v>
+        <v>159.8509996382289</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.5955244560758</v>
+        <v>159.5968685477674</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.0455936641646</v>
+        <v>159.0527973330267</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.246921210045</v>
+        <v>157.2561720963494</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.7841978243768</v>
+        <v>157.7929728086198</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.1146820045218</v>
+        <v>158.1226510472318</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.1641306843555</v>
+        <v>158.1718487259662</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.4140418628989</v>
+        <v>159.4212238971686</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.3573526001</v>
+        <v>158.3602829147946</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7883042228187</v>
+        <v>155.7852732680265</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.937130679858</v>
+        <v>155.9338904686024</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6932545165316</v>
+        <v>156.6918133437926</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.4862850707019</v>
+        <v>156.4787707773145</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.2625157035659</v>
+        <v>156.2546490020273</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>156.1125345191491</v>
+        <v>156.1041252389548</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.2870495608553</v>
+        <v>157.2820991629691</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6264117621247</v>
+        <v>158.6276921555173</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.103046602795</v>
+        <v>159.1050672996292</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.6775072847548</v>
+        <v>159.6802368506278</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.5954699948343</v>
+        <v>159.5958590698132</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1618092595419</v>
+        <v>160.1624551521163</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.1021481966485</v>
+        <v>160.0999825030466</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.9271823701019</v>
+        <v>159.9232772387611</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.3936831071845</v>
+        <v>160.3903641859845</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.141919206015</v>
+        <v>161.137084372668</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.4793098277011</v>
+        <v>161.6125011019196</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.3542000934357</v>
+        <v>161.5023047504835</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>161.0829584144043</v>
+        <v>161.2171890129848</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.9791408297868</v>
+        <v>161.1151310175751</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>161.023683980999</v>
+        <v>161.1749188895768</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>161.4159343446781</v>
+        <v>161.5633150406926</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>162.0971722181183</v>
+        <v>162.1903771619195</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>162.4803833105383</v>
+        <v>162.5713408761163</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>163.2405886943104</v>
+        <v>163.2929862098234</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>164.039364215927</v>
+        <v>164.029422016709</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>164.8908497411612</v>
+        <v>164.8233770601916</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>165.6630014968951</v>
+        <v>165.5291281182833</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>164.8964233832073</v>
+        <v>164.8595862337958</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>162.6718433452216</v>
+        <v>163.2702901714014</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.5023047504835</v>
+        <v>161.502118522627</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>161.2171890129848</v>
+        <v>161.2171421160689</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>161.1151310175751</v>
+        <v>161.1151821259865</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>161.1749188895768</v>
+        <v>161.1742189319097</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>161.5633150406926</v>
+        <v>161.5634583494607</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>162.1903771619195</v>
+        <v>162.1909524879214</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>162.5713408761163</v>
+        <v>162.5501253109143</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>163.2929862098234</v>
+        <v>163.2909640531266</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>164.029422016709</v>
+        <v>164.034975337809</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>164.8233770601916</v>
+        <v>164.8212551677431</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>165.5291281182833</v>
+        <v>165.5305255512341</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>164.8595862337958</v>
+        <v>164.8620355713183</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>163.2702901714014</v>
+        <v>163.2771588628168</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.3673139509193</v>
+        <v>139.3648415858163</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.5641966970222</v>
+        <v>142.5605926742531</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.8506816213198</v>
+        <v>143.8467962760603</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.5314800482421</v>
+        <v>144.5275077873126</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.459575726146</v>
+        <v>144.455534630674</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.3826988405152</v>
+        <v>144.3785997062394</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.3396901793822</v>
+        <v>144.3355679118014</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.3789251133938</v>
+        <v>144.3748101567358</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>145.0490883350955</v>
+        <v>145.04498224508</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0353244451802</v>
+        <v>148.0353908248954</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4312030055462</v>
+        <v>148.4312180394609</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535135685736</v>
+        <v>148.853515128872</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9110108259473</v>
+        <v>148.9114991682176</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2909377918153</v>
+        <v>149.291079994519</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4222888826206</v>
+        <v>150.421633721112</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.8997071144252</v>
+        <v>151.898012188279</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2911016993117</v>
+        <v>152.2893026849973</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.6195428180878</v>
+        <v>152.6178139597396</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.2044583185796</v>
+        <v>153.2033578454932</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4154536189139</v>
+        <v>152.4151723636998</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.9717005361675</v>
+        <v>152.9689596347225</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.7773633820941</v>
+        <v>152.7736095177436</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.8244402674729</v>
+        <v>152.8195690307052</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.5367349035052</v>
+        <v>154.5308392366103</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.4931109801591</v>
+        <v>155.4872800445135</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.4949691430095</v>
+        <v>156.4886206489732</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>158.1649524869631</v>
+        <v>158.1580312666189</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.753014653285</v>
+        <v>159.7473193156259</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.544325825536</v>
+        <v>161.5406736370069</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.8509996382289</v>
+        <v>159.853449160356</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.5968685477674</v>
+        <v>159.5981542597911</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.0527973330267</v>
+        <v>159.0597446872608</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.2561720963494</v>
+        <v>157.2650997941942</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.7929728086198</v>
+        <v>157.8014465265272</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.1226510472318</v>
+        <v>158.1303527636297</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.1718487259662</v>
+        <v>158.1793235954331</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.4212238971686</v>
+        <v>159.4281851493579</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.3602829147946</v>
+        <v>158.3631348187937</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7852732680265</v>
+        <v>155.7823541882837</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.9338904686024</v>
+        <v>155.9307700286664</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6918133437926</v>
+        <v>156.6904326334155</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.4787707773145</v>
+        <v>156.4715063592448</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.2546490020273</v>
+        <v>156.2470395400614</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>156.1041252389548</v>
+        <v>156.0959815313348</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.2820991629691</v>
+        <v>157.2773025575724</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6276921555173</v>
+        <v>158.6289342071521</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1050672996292</v>
+        <v>159.1070285862563</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.6802368506278</v>
+        <v>159.6828872085573</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.5958590698132</v>
+        <v>159.5962429042431</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1624551521163</v>
+        <v>160.1630916133776</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.0999825030466</v>
+        <v>160.0978964549973</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.9232772387611</v>
+        <v>159.9195040838298</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.3903641859845</v>
+        <v>160.3871575744726</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.137084372668</v>
+        <v>161.1324076302328</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.6125011019196</v>
+        <v>161.7335320940927</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.502118522627</v>
+        <v>161.6402776433604</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>161.2171421160689</v>
+        <v>161.3513263916442</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>161.1151821259865</v>
+        <v>161.2634782699802</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>161.1742189319097</v>
+        <v>161.3463407142984</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>161.5634583494607</v>
+        <v>161.7259623817211</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>162.1909524879214</v>
+        <v>162.3381791618457</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>162.5501253109143</v>
+        <v>162.7073578956239</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>163.2909640531266</v>
+        <v>163.4614699273948</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>164.034975337809</v>
+        <v>164.2457316426916</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>164.8212551677431</v>
+        <v>165.0274278291205</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>165.5305255512341</v>
+        <v>165.7357908180872</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>164.8620355713183</v>
+        <v>165.2257071568684</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>163.2771588628168</v>
+        <v>164.467127379944</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B109"/>
+  <dimension ref="A1:B110"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.3648415858163</v>
+        <v>139.360144021456</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.5605926742531</v>
+        <v>142.5537430949986</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.8467962760603</v>
+        <v>143.8394092064386</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.5275077873126</v>
+        <v>144.5199525634266</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.455534630674</v>
+        <v>144.4478486704176</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.3785997062394</v>
+        <v>144.3708035359042</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.3355679118014</v>
+        <v>144.3277278325913</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.3748101567358</v>
+        <v>144.3669839929326</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>145.04498224508</v>
+        <v>145.037169892568</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0353908248954</v>
+        <v>148.0355167940285</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4312180394609</v>
+        <v>148.4312465023409</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.853515128872</v>
+        <v>148.8535180015547</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9114991682176</v>
+        <v>148.9124260189543</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.291079994519</v>
+        <v>149.2913515177766</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.421633721112</v>
+        <v>150.420389690484</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.898012188279</v>
+        <v>151.8947889519732</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2893026849973</v>
+        <v>152.2858807811126</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.6178139597396</v>
+        <v>152.6145236991349</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.2033578454932</v>
+        <v>153.2012631537259</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4151723636998</v>
+        <v>152.4146382336631</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.9689596347225</v>
+        <v>152.963757001429</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.7736095177436</v>
+        <v>152.7664805696805</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.8195690307052</v>
+        <v>152.8103104389307</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.5308392366103</v>
+        <v>154.5196302097898</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.4872800445135</v>
+        <v>155.476187155443</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.4886206489732</v>
+        <v>156.4765378509749</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>158.1580312666189</v>
+        <v>158.1448495535982</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.7473193156259</v>
+        <v>159.7364511014738</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.5406736370069</v>
+        <v>161.5336913308842</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.853449160356</v>
+        <v>159.8580646188472</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.5981542597911</v>
+        <v>159.600564480033</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.0597446872608</v>
+        <v>159.0729230223257</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.2650997941942</v>
+        <v>157.2820507714929</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.8014465265272</v>
+        <v>157.8175497965582</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.1303527636297</v>
+        <v>158.145005835974</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.1793235954331</v>
+        <v>158.1935878522696</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.4281851493579</v>
+        <v>159.4414841443023</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.3631348187937</v>
+        <v>158.3686147042789</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7823541882837</v>
+        <v>155.7768279468554</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.9307700286664</v>
+        <v>155.9248630784435</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6904326334155</v>
+        <v>156.6878385511431</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.4715063592448</v>
+        <v>156.4576791495945</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.2470395400614</v>
+        <v>156.2325438176983</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>156.0959815313348</v>
+        <v>156.0804425288472</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.2773025575724</v>
+        <v>157.2681432141412</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6289342071521</v>
+        <v>158.6313098242238</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1070285862563</v>
+        <v>159.1107828437356</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.6828872085573</v>
+        <v>159.687963271305</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.5962429042431</v>
+        <v>159.5969943528724</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1630916133776</v>
+        <v>160.1643357535638</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.0978964549973</v>
+        <v>160.0939465670537</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.9195040838298</v>
+        <v>159.9123279534562</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.3871575744726</v>
+        <v>160.3810593791916</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.1324076302328</v>
+        <v>161.1234987176215</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.7335320940927</v>
+        <v>161.8271596436101</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.6402776433604</v>
+        <v>161.8599949368001</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>161.3513263916442</v>
+        <v>161.6043693718484</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>161.2634782699802</v>
+        <v>161.5157524233784</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>161.3463407142984</v>
+        <v>161.6188389953227</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>161.7259623817211</v>
+        <v>161.9945933120395</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>162.3381791618457</v>
+        <v>162.5925287712655</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>162.7073578956239</v>
+        <v>162.9744569825457</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>163.4614699273948</v>
+        <v>163.7415266394923</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>164.2457316426916</v>
+        <v>164.5595256885122</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>165.0274278291205</v>
+        <v>165.3486941488299</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>165.7357908180872</v>
+        <v>166.0536611255699</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>165.2257071568684</v>
+        <v>165.7780037817382</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,15 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>164.467127379944</v>
+        <v>165.824100048126</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110" s="3">
+        <v>46325</v>
+      </c>
+      <c r="B110">
+        <v>168.227100048126</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.360144021456</v>
+        <v>139.3648415858163</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.5537430949986</v>
+        <v>142.5605926742531</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.8394092064386</v>
+        <v>143.8467962760603</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.5199525634266</v>
+        <v>144.5275077873126</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.4478486704176</v>
+        <v>144.455534630674</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.3708035359042</v>
+        <v>144.3785997062394</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.3277278325913</v>
+        <v>144.3355679118014</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.3669839929326</v>
+        <v>144.3748101567358</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>145.037169892568</v>
+        <v>145.04498224508</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0355167940285</v>
+        <v>148.0353908248954</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4312465023409</v>
+        <v>148.4312180394609</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535180015547</v>
+        <v>148.853515128872</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9124260189543</v>
+        <v>148.9114991682176</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2913515177766</v>
+        <v>149.291079994519</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.420389690484</v>
+        <v>150.421633721112</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.8947889519732</v>
+        <v>151.898012188279</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2858807811126</v>
+        <v>152.2893026849973</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.6145236991349</v>
+        <v>152.6178139597396</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.2012631537259</v>
+        <v>153.2033578454932</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4146382336631</v>
+        <v>152.4151723636998</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.963757001429</v>
+        <v>152.9689596347225</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.7664805696805</v>
+        <v>152.7736095177436</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.8103104389307</v>
+        <v>152.8195690307052</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.5196302097898</v>
+        <v>154.5308392366103</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.476187155443</v>
+        <v>155.4872800445135</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.4765378509749</v>
+        <v>156.4886206489732</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>158.1448495535982</v>
+        <v>158.1580312666189</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.7364511014738</v>
+        <v>159.7473193156259</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.5336913308842</v>
+        <v>161.5406736370069</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.8580646188472</v>
+        <v>159.853449160356</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.600564480033</v>
+        <v>159.5981542597911</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.0729230223257</v>
+        <v>159.0597446872608</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.2820507714929</v>
+        <v>157.2650997941942</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.8175497965582</v>
+        <v>157.8014465265272</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.145005835974</v>
+        <v>158.1303527636297</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.1935878522696</v>
+        <v>158.1793235954331</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.4414841443023</v>
+        <v>159.4281851493579</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.3686147042789</v>
+        <v>158.3631348187937</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7768279468554</v>
+        <v>155.7823541882837</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.9248630784435</v>
+        <v>155.9307700286664</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6878385511431</v>
+        <v>156.6904326334155</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.4576791495945</v>
+        <v>156.4715063592448</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.2325438176983</v>
+        <v>156.2470395400614</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>156.0804425288472</v>
+        <v>156.0959815313348</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.2681432141412</v>
+        <v>157.2773025575724</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6313098242238</v>
+        <v>158.6289342071521</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1107828437356</v>
+        <v>159.1070285862563</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.687963271305</v>
+        <v>159.6828872085573</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.5969943528724</v>
+        <v>159.5962429042431</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1643357535638</v>
+        <v>160.1630916133776</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.0939465670537</v>
+        <v>160.0978964549973</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.9123279534562</v>
+        <v>159.9195040838298</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.3810593791916</v>
+        <v>160.3871575744726</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.1234987176215</v>
+        <v>161.1324076302328</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.8271596436101</v>
+        <v>161.606730885325</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.8599949368001</v>
+        <v>161.6304304022484</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>161.6043693718484</v>
+        <v>161.3871191675342</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>161.5157524233784</v>
+        <v>161.2984062408642</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>161.6188389953227</v>
+        <v>161.3804902903054</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>161.9945933120395</v>
+        <v>161.789720046239</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>162.5925287712655</v>
+        <v>162.4191360229689</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>162.9744569825457</v>
+        <v>162.7797954091139</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>163.7415266394923</v>
+        <v>163.4846836053649</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>164.5595256885122</v>
+        <v>164.2205643025424</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>165.3486941488299</v>
+        <v>164.9911644651348</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>166.0536611255699</v>
+        <v>165.6833397710101</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>165.7780037817382</v>
+        <v>165.1484422295912</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>165.824100048126</v>
+        <v>164.2939648436673</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>168.227100048126</v>
+        <v>166.6969648436673</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>161.3871191675342</v>
+        <v>161.387158321371</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>161.2984062408642</v>
+        <v>161.2984130677268</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>161.3804902903054</v>
+        <v>161.380346677397</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>161.789720046239</v>
+        <v>161.7662107853121</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>162.4191360229689</v>
+        <v>162.3782852079013</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>162.7797954091139</v>
+        <v>162.7502051695167</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>163.4846836053649</v>
+        <v>163.4633182564334</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>164.2205643025424</v>
+        <v>164.2030909658936</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>164.9911644651348</v>
+        <v>164.9867299328916</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>165.6833397710101</v>
+        <v>165.6726880821191</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>165.1484422295912</v>
+        <v>165.1403817944312</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>164.2939648436673</v>
+        <v>164.2835446790599</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>166.6969648436673</v>
+        <v>166.6865446790599</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.3648415858163</v>
+        <v>139.3624530052061</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.5605926742531</v>
+        <v>142.5571101539737</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.8467962760603</v>
+        <v>143.8430409429384</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.5275077873126</v>
+        <v>144.5236674454784</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.455534630674</v>
+        <v>144.4516278046368</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.3785997062394</v>
+        <v>144.3746368307432</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.3355679118014</v>
+        <v>144.3315827024834</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.3748101567358</v>
+        <v>144.3708320190146</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>145.04498224508</v>
+        <v>145.0410116269576</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0353908248954</v>
+        <v>148.0354549019763</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4312180394609</v>
+        <v>148.4312325287658</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.853515128872</v>
+        <v>148.8535166046273</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9114991682176</v>
+        <v>148.9119706121129</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.291079994519</v>
+        <v>149.2912178384577</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.421633721112</v>
+        <v>150.4210010354507</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.898012188279</v>
+        <v>151.8963737245211</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2893026849973</v>
+        <v>152.2875633511668</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.6178139597396</v>
+        <v>152.6161418337738</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.2033578454932</v>
+        <v>153.2022933686737</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4151723636998</v>
+        <v>152.4149007304537</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.9689596347225</v>
+        <v>152.9663133934133</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.7736095177436</v>
+        <v>152.7699840673894</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.8195690307052</v>
+        <v>152.8148617962668</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.5308392366103</v>
+        <v>154.5251409109839</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.4872800445135</v>
+        <v>155.4816418917244</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.4886206489732</v>
+        <v>156.4824802218465</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>158.1580312666189</v>
+        <v>158.1513338234707</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.7473193156259</v>
+        <v>159.7418007956106</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.5406736370069</v>
+        <v>161.5371303730483</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.853449160356</v>
+        <v>159.8558023382478</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.5981542597911</v>
+        <v>159.5993851443826</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.0597446872608</v>
+        <v>159.0664490968807</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.2650997941942</v>
+        <v>157.2737208672356</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.8014465265272</v>
+        <v>157.8096341348357</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.1303527636297</v>
+        <v>158.1378002674005</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.1793235954331</v>
+        <v>158.1865664675133</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.4281851493579</v>
+        <v>159.4349354699139</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.3631348187937</v>
+        <v>158.3659111687096</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7823541882837</v>
+        <v>155.7795409510632</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.9307700286664</v>
+        <v>155.9277629008424</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6904326334155</v>
+        <v>156.6891088058871</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.4715063592448</v>
+        <v>156.4644796225213</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.2470395400614</v>
+        <v>156.2396749962926</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>156.0959815313348</v>
+        <v>156.0880911363684</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.2773025575724</v>
+        <v>157.2726527643934</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6289342071521</v>
+        <v>158.6301395746418</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1070285862563</v>
+        <v>159.1089329750536</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.6828872085573</v>
+        <v>159.6854616439584</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.5962429042431</v>
+        <v>159.5966213649056</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1630916133776</v>
+        <v>160.1637185094677</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.0978964549973</v>
+        <v>160.0958857967671</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.9195040838298</v>
+        <v>159.9158563620801</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.3871575744726</v>
+        <v>160.384057707549</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.1324076302328</v>
+        <v>161.1278814369697</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.606730885325</v>
+        <v>161.6011454773694</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.6304304022484</v>
+        <v>161.7525787880713</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>161.387158321371</v>
+        <v>161.5474514523512</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>161.2984130677268</v>
+        <v>161.4718202720484</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>161.380346677397</v>
+        <v>161.5748613583475</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>161.7662107853121</v>
+        <v>161.9597507948907</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>162.3782852079013</v>
+        <v>162.560449050581</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>162.7502051695167</v>
+        <v>162.927195624335</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>163.4633182564334</v>
+        <v>163.634788130561</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>164.2030909658936</v>
+        <v>164.3793201032236</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>164.9867299328916</v>
+        <v>165.1603119739945</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>165.6726880821191</v>
+        <v>165.8330310659726</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>165.1403817944312</v>
+        <v>165.4200588622236</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>164.2835446790599</v>
+        <v>165.0504924428838</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>166.6865446790599</v>
+        <v>167.4534924428837</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.3624530052061</v>
+        <v>139.3579107214048</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.5571101539737</v>
+        <v>142.5504858500271</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.8430409429384</v>
+        <v>143.8358950661362</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.5236674454784</v>
+        <v>144.5163570964569</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.4516278046368</v>
+        <v>144.4441910728181</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.3746368307432</v>
+        <v>144.3670935726728</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.3315827024834</v>
+        <v>144.323997015078</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.3708320190146</v>
+        <v>144.3632598022531</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>145.0410116269576</v>
+        <v>145.0334508736436</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0354549019763</v>
+        <v>148.0355766107932</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4312325287658</v>
+        <v>148.4312599870706</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535166046273</v>
+        <v>148.8535193249027</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9119706121129</v>
+        <v>148.9128661925598</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2912178384577</v>
+        <v>149.2914812154924</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4210010354507</v>
+        <v>150.4197986261146</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.8963737245211</v>
+        <v>151.8932552776295</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2875633511668</v>
+        <v>152.2842522448475</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.6161418337738</v>
+        <v>152.6129569881392</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.2022933686737</v>
+        <v>153.2002655757027</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4149007304537</v>
+        <v>152.4143844199417</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.9663133934133</v>
+        <v>152.9612859679116</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.7699840673894</v>
+        <v>152.7630929885245</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.8148617962668</v>
+        <v>152.805907360217</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.5251409109839</v>
+        <v>154.5142980420195</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.4816418917244</v>
+        <v>155.4709070638981</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.4824802218465</v>
+        <v>156.4707841542957</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>158.1513338234707</v>
+        <v>158.1385685076237</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.7418007956106</v>
+        <v>159.7312627079023</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.5371303730483</v>
+        <v>161.5303520676221</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.8558023382478</v>
+        <v>159.8602410530773</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.5993851443826</v>
+        <v>159.601695296782</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.0664490968807</v>
+        <v>159.079178090175</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.2737208672356</v>
+        <v>157.2901039460027</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.8096341348357</v>
+        <v>157.825206760612</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.1378002674005</v>
+        <v>158.1519809755094</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.1865664675133</v>
+        <v>158.2003976429332</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.4349354699139</v>
+        <v>159.447839931846</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.3659111687096</v>
+        <v>158.3712480520903</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7795409510632</v>
+        <v>155.7742099529599</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.9277629008424</v>
+        <v>155.9220649686401</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6891088058871</v>
+        <v>156.6866188041924</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.4644796225213</v>
+        <v>156.4510942388556</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.2396749962926</v>
+        <v>156.2256351611434</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>156.0880911363684</v>
+        <v>156.0730248647632</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.2726527643934</v>
+        <v>157.2637677191248</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6301395746418</v>
+        <v>158.6324464367165</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1089329750536</v>
+        <v>159.1125804437996</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.6854616439584</v>
+        <v>159.6903950443351</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.5966213649056</v>
+        <v>159.5973617987247</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1637185094677</v>
+        <v>160.1649432991368</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.0958857967671</v>
+        <v>160.0920750742124</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.9158563620801</v>
+        <v>159.9089131275956</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.384057707549</v>
+        <v>160.378157714164</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.1278814369697</v>
+        <v>161.1192528283582</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.6011454773694</v>
+        <v>161.8211599489243</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.7525787880713</v>
+        <v>161.9622239177216</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>161.5474514523512</v>
+        <v>161.7409827207015</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>161.4718202720484</v>
+        <v>161.6630394438746</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>161.5748613583475</v>
+        <v>161.7685062694517</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>161.9597507948907</v>
+        <v>162.1474758794361</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>162.560449050581</v>
+        <v>162.7445109734603</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>162.927195624335</v>
+        <v>163.1287422867237</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>163.634788130561</v>
+        <v>163.8886503498453</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>164.3793201032236</v>
+        <v>164.7121873084129</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>165.1603119739945</v>
+        <v>165.5099194251152</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>165.8330310659726</v>
+        <v>166.2132708314019</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>165.4200588622236</v>
+        <v>166.0298019675645</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>165.0504924428838</v>
+        <v>166.3069752411875</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>167.4534924428837</v>
+        <v>168.7099752411875</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.3579107214048</v>
+        <v>139.360144021456</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.5504858500271</v>
+        <v>142.5537430949986</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.8358950661362</v>
+        <v>143.8394092064386</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.5163570964569</v>
+        <v>144.5199525634266</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.4441910728181</v>
+        <v>144.4478486704176</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.3670935726728</v>
+        <v>144.3708035359042</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.323997015078</v>
+        <v>144.3277278325913</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.3632598022531</v>
+        <v>144.3669839929326</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>145.0334508736436</v>
+        <v>145.037169892568</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0355766107932</v>
+        <v>148.0355167940285</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4312599870706</v>
+        <v>148.4312465023409</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535193249027</v>
+        <v>148.8535180015547</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9128661925598</v>
+        <v>148.9124260189543</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2914812154924</v>
+        <v>149.2913515177766</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4197986261146</v>
+        <v>150.420389690484</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.8932552776295</v>
+        <v>151.8947889519732</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2842522448475</v>
+        <v>152.2858807811126</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.6129569881392</v>
+        <v>152.6145236991349</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.2002655757027</v>
+        <v>153.2012631537259</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4143844199417</v>
+        <v>152.4146382336631</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.9612859679116</v>
+        <v>152.963757001429</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.7630929885245</v>
+        <v>152.7664805696805</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.805907360217</v>
+        <v>152.8103104389307</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.5142980420195</v>
+        <v>154.5196302097898</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.4709070638981</v>
+        <v>155.476187155443</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.4707841542957</v>
+        <v>156.4765378509749</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>158.1385685076237</v>
+        <v>158.1448495535982</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.7312627079023</v>
+        <v>159.7364511014738</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.5303520676221</v>
+        <v>161.5336913308842</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.8602410530773</v>
+        <v>159.8580646188472</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.601695296782</v>
+        <v>159.600564480033</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.079178090175</v>
+        <v>159.0729230223257</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.2901039460027</v>
+        <v>157.2820507714929</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.825206760612</v>
+        <v>157.8175497965582</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.1519809755094</v>
+        <v>158.145005835974</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.2003976429332</v>
+        <v>158.1935878522696</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.447839931846</v>
+        <v>159.4414841443023</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.3712480520903</v>
+        <v>158.3686147042789</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7742099529599</v>
+        <v>155.7768279468554</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.9220649686401</v>
+        <v>155.9248630784435</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6866188041924</v>
+        <v>156.6878385511431</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.4510942388556</v>
+        <v>156.4576791495945</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.2256351611434</v>
+        <v>156.2325438176983</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>156.0730248647632</v>
+        <v>156.0804425288472</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.2637677191248</v>
+        <v>157.2681432141412</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6324464367165</v>
+        <v>158.6313098242238</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1125804437996</v>
+        <v>159.1107828437356</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.6903950443351</v>
+        <v>159.687963271305</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.5973617987247</v>
+        <v>159.5969943528724</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1649432991368</v>
+        <v>160.1643357535638</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.0920750742124</v>
+        <v>160.0939465670537</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.9089131275956</v>
+        <v>159.9123279534562</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.378157714164</v>
+        <v>160.3810593791916</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.1192528283582</v>
+        <v>161.1234987176215</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.8211599489243</v>
+        <v>161.5957362449481</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.9622239177216</v>
+        <v>161.8419470816352</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>161.7409827207015</v>
+        <v>161.6698162294613</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>161.6630394438746</v>
+        <v>161.6024357644253</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>161.7685062694517</v>
+        <v>161.7199897120023</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>162.1474758794361</v>
+        <v>162.0977471345577</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>162.7445109734603</v>
+        <v>162.682946320776</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>163.1287422867237</v>
+        <v>163.0402003422591</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>163.8886503498453</v>
+        <v>163.7361368464481</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>164.7121873084129</v>
+        <v>164.4699289807407</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>165.5099194251152</v>
+        <v>165.2325704200263</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>166.2132708314019</v>
+        <v>165.8817943916306</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>166.0298019675645</v>
+        <v>165.547819261497</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>166.3069752411875</v>
+        <v>165.4031671269966</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>168.7099752411875</v>
+        <v>168.460066684041</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.360144021456</v>
+        <v>139.3557494442404</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.5537430949986</v>
+        <v>142.5473331340629</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.8394092064386</v>
+        <v>143.832492903675</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.5199525634266</v>
+        <v>144.5128753817656</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.4478486704176</v>
+        <v>144.4406492457084</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.3708035359042</v>
+        <v>144.3635010871817</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.3277278325913</v>
+        <v>144.3203843605724</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.3669839929326</v>
+        <v>144.3596535677436</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>145.037169892568</v>
+        <v>145.0298487889205</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0355167940285</v>
+        <v>148.0356344547928</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4312465023409</v>
+        <v>148.4312730080123</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535180015547</v>
+        <v>148.8535205794983</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9124260189543</v>
+        <v>148.9132918839592</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2913515177766</v>
+        <v>149.2916071042587</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.420389690484</v>
+        <v>150.4192268512084</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.8947889519732</v>
+        <v>151.8917702725844</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2858807811126</v>
+        <v>152.2826751844216</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.6145236991349</v>
+        <v>152.6114392930135</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.2012631537259</v>
+        <v>153.1992991106226</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4146382336631</v>
+        <v>152.4141388654156</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.963757001429</v>
+        <v>152.9588960958389</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.7664805696805</v>
+        <v>152.7598156787515</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.8103104389307</v>
+        <v>152.8016454464876</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.5196302097898</v>
+        <v>154.5091358930479</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.476187155443</v>
+        <v>155.4657933936529</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.4765378509749</v>
+        <v>156.4652103300392</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>158.1448495535982</v>
+        <v>158.132481341384</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.7364511014738</v>
+        <v>159.7262285231793</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.5336913308842</v>
+        <v>161.5271083831688</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.8580646188472</v>
+        <v>159.8623363307067</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.600564480033</v>
+        <v>159.6027803988056</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.0729230223257</v>
+        <v>159.0852251614552</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.2820507714929</v>
+        <v>157.2978938947502</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.8175497965582</v>
+        <v>157.832617433958</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.145005835974</v>
+        <v>158.1587364799726</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.1935878522696</v>
+        <v>158.2070051597747</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.4414841443023</v>
+        <v>159.4540111015199</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.3686147042789</v>
+        <v>158.3738137294977</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7768279468554</v>
+        <v>155.7716821009129</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.9248630784435</v>
+        <v>155.9193633576685</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6878385511431</v>
+        <v>156.685446723299</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.4576791495945</v>
+        <v>156.4447148496895</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.2325438176983</v>
+        <v>156.2189388401232</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>156.0804425288472</v>
+        <v>156.0658279323343</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.2681432141412</v>
+        <v>157.2595204463152</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6313098242238</v>
+        <v>158.6335508130434</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1107828437356</v>
+        <v>159.1143279083945</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.687963271305</v>
+        <v>159.6927597656218</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.5969943528724</v>
+        <v>159.5977236584147</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1643357535638</v>
+        <v>160.1655411341174</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.0939465670537</v>
+        <v>160.0902678739195</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.9123279534562</v>
+        <v>159.9056065134621</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.3810593791916</v>
+        <v>160.3753481423371</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.1234987176215</v>
+        <v>161.1151375247923</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.5957362449481</v>
+        <v>161.8153433252576</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.8419470816352</v>
+        <v>161.8687069576104</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>161.6698162294613</v>
+        <v>161.6412632003687</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>161.6024357644253</v>
+        <v>161.5549476552077</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>161.7199897120023</v>
+        <v>161.6410713697144</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>162.0977471345577</v>
+        <v>161.9952644986104</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>162.682946320776</v>
+        <v>162.5630606820626</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>163.0402003422591</v>
+        <v>162.9477691461928</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>163.7361368464481</v>
+        <v>163.6799415956609</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>164.4699289807407</v>
+        <v>164.446478375052</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>165.2325704200263</v>
+        <v>165.2068168584906</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>165.8817943916306</v>
+        <v>165.8616051662677</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>165.547819261497</v>
+        <v>165.6785056445715</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>165.4031671269966</v>
+        <v>165.7721368179869</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>168.460066684041</v>
+        <v>167.2106119957382</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.3557494442404</v>
+        <v>139.3536567614821</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.5473331340629</v>
+        <v>142.5442799958235</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.832492903675</v>
+        <v>143.8291974528467</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.5128753817656</v>
+        <v>144.5095021087766</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.4406492457084</v>
+        <v>144.4372177817861</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.3635010871817</v>
+        <v>144.3600205900146</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.3203843605724</v>
+        <v>144.3168843464475</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.3596535677436</v>
+        <v>144.3561597762949</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>145.0298487889205</v>
+        <v>145.0263582142891</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0356344547928</v>
+        <v>148.035690421914</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4312730080123</v>
+        <v>148.4312855885483</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535205794983</v>
+        <v>148.8535217697861</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9132918839592</v>
+        <v>148.9137037956548</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2916071042587</v>
+        <v>149.291729347071</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4192268512084</v>
+        <v>150.4186734380835</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.8917702725844</v>
+        <v>151.8903316592704</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2826751844216</v>
+        <v>152.2811472006009</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.6114392930135</v>
+        <v>152.6099683536659</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.1992991106226</v>
+        <v>153.198362327763</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4141388654156</v>
+        <v>152.4139011733601</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.9588960958389</v>
+        <v>152.9565834584207</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.7598156787515</v>
+        <v>152.7566433550438</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.8016454464876</v>
+        <v>152.7975180309693</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.5091358930479</v>
+        <v>154.5041357797894</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.4657933936529</v>
+        <v>155.4608384275925</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.4652103300392</v>
+        <v>156.4598081127902</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>158.132481341384</v>
+        <v>158.126579270958</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.7262285231793</v>
+        <v>159.721341858997</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.5271083831688</v>
+        <v>161.5239563044085</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.8623363307067</v>
+        <v>159.8643548116354</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.6027803988056</v>
+        <v>159.6038223846228</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.0852251614552</v>
+        <v>159.0910743933662</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.2978938947502</v>
+        <v>157.305433260839</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.832617433958</v>
+        <v>157.8397934470555</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.1587364799726</v>
+        <v>158.1652824849203</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.2070051597747</v>
+        <v>158.2134191903575</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.4540111015199</v>
+        <v>159.4600054649623</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.3738137294977</v>
+        <v>158.3763141486409</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7716821009129</v>
+        <v>155.7692398471334</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.9193633576685</v>
+        <v>155.9167533794691</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.685446723299</v>
+        <v>156.6843196704183</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.4447148496895</v>
+        <v>156.4385315524829</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.2189388401232</v>
+        <v>156.2124452761884</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>156.0658279323343</v>
+        <v>156.0588421071346</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.2595204463152</v>
+        <v>157.2553958926209</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6335508130434</v>
+        <v>158.634624279358</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1143279083945</v>
+        <v>159.1160272596518</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.6927597656218</v>
+        <v>159.6950600955436</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.5977236584147</v>
+        <v>159.5980799096775</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1655411341174</v>
+        <v>160.1661292758436</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.0902678739195</v>
+        <v>160.0885217490004</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.9056065134621</v>
+        <v>159.90240307176</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.3753481423371</v>
+        <v>160.3726263753495</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.1151375247923</v>
+        <v>161.1111469327594</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.8153433252576</v>
+        <v>161.8097016238706</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.8687069576104</v>
+        <v>161.6244311616667</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>161.6412632003687</v>
+        <v>161.3531659206279</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>161.5549476552077</v>
+        <v>161.2365024185805</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>161.6410713697144</v>
+        <v>161.2781852063579</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>161.9952644986104</v>
+        <v>161.5873961688065</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>162.5630606820626</v>
+        <v>162.1077358306978</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>162.9477691461928</v>
+        <v>162.4656309857599</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>163.6799415956609</v>
+        <v>163.1419466889214</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>164.446478375052</v>
+        <v>163.7991323961697</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>165.2068168584906</v>
+        <v>164.4624370759045</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>165.8616051662677</v>
+        <v>165.026755236342</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>165.6785056445715</v>
+        <v>164.7681955174712</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>165.7721368179869</v>
+        <v>164.4136181307252</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>167.2106119957382</v>
+        <v>163.6532653377016</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B110"/>
+  <dimension ref="A1:B111"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.8097016238706</v>
+        <v>161.5804868837901</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.6244311616667</v>
+        <v>161.5048574415155</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>161.3531659206279</v>
+        <v>161.077733317375</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>161.2365024185805</v>
+        <v>160.921782236856</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>161.2781852063579</v>
+        <v>160.9627306498521</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>161.5873961688065</v>
+        <v>161.1995832938085</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>162.1077358306978</v>
+        <v>161.6247118866366</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>162.4656309857599</v>
+        <v>161.9219762615483</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>163.1419466889214</v>
+        <v>162.4761067777917</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>163.7991323961697</v>
+        <v>162.9413995831059</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>164.4624370759045</v>
+        <v>163.428586914343</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>165.026755236342</v>
+        <v>163.8357391552236</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>164.7681955174712</v>
+        <v>163.3351852251618</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>164.4136181307252</v>
+        <v>162.1745723862047</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,15 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>163.6532653377016</v>
+        <v>161.7024290953913</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111" s="3">
+        <v>46332</v>
+      </c>
+      <c r="B111">
+        <v>159.2994290953913</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.3536567614821</v>
+        <v>139.3516294588391</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.5442799958235</v>
+        <v>142.5413217918147</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.8291974528467</v>
+        <v>143.8260037724372</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.5095021087766</v>
+        <v>144.5062322921935</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.4372177817861</v>
+        <v>144.4338916051104</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.3600205900146</v>
+        <v>144.3566469282976</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.3168843464475</v>
+        <v>144.313491788729</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.3561597762949</v>
+        <v>144.3527732528763</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>145.0263582142891</v>
+        <v>145.0229740556621</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.035690421914</v>
+        <v>148.035744601936</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4312855885483</v>
+        <v>148.4312977505228</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535217697861</v>
+        <v>148.8535228998641</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9137037956548</v>
+        <v>148.9141025854744</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.291729347071</v>
+        <v>149.2918480979168</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4186734380835</v>
+        <v>150.4181375175204</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.8903316592704</v>
+        <v>151.8889372998678</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2811472006009</v>
+        <v>152.2796660407632</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.6099683536659</v>
+        <v>152.608542046559</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.198362327763</v>
+        <v>153.1974538826467</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4139011733601</v>
+        <v>152.4136709720604</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.9565834584207</v>
+        <v>152.9543443777301</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.7566433550438</v>
+        <v>152.7535710637763</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.7975180309693</v>
+        <v>152.7935188592839</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.5041357797894</v>
+        <v>154.4992902099669</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.4608384275925</v>
+        <v>155.4560349166989</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.4598081127902</v>
+        <v>156.4545697334588</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>158.126579270958</v>
+        <v>158.120854031612</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.721341858997</v>
+        <v>159.7165964026963</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.5239563044085</v>
+        <v>161.5208920705454</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.8643548116354</v>
+        <v>159.8663005540187</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.6038223846228</v>
+        <v>159.6048236652078</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.0910743933662</v>
+        <v>159.0967352951555</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.305433260839</v>
+        <v>157.3127338937394</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.8397934470555</v>
+        <v>157.8467457133394</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.1652824849203</v>
+        <v>158.1716285165257</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.2134191903575</v>
+        <v>158.2196480265075</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.4600054649623</v>
+        <v>159.4658304069384</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.3763141486409</v>
+        <v>158.378751620511</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7692398471334</v>
+        <v>155.7668789464249</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.9167533794691</v>
+        <v>155.9142304873682</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6843196704183</v>
+        <v>156.6832351936228</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.4385315524829</v>
+        <v>156.4325354830773</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.2124452761884</v>
+        <v>156.2061454545814</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>156.0588421071346</v>
+        <v>156.0520583109397</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.2553958926209</v>
+        <v>157.2513888621726</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.634624279358</v>
+        <v>158.6356680917991</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1160272596518</v>
+        <v>159.1176804155147</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.6950600955436</v>
+        <v>159.6972985606865</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.5980799096775</v>
+        <v>159.5984305489196</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1661292758436</v>
+        <v>160.1667077666819</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.0885217490004</v>
+        <v>160.0868336911829</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.90240307176</v>
+        <v>159.8992980698369</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.3726263753495</v>
+        <v>160.3699883853629</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.1111469327594</v>
+        <v>161.1072755215932</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.5804868837901</v>
+        <v>161.8042271662141</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.5048574415155</v>
+        <v>161.6208451154959</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>161.077733317375</v>
+        <v>161.1517351173641</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.921782236856</v>
+        <v>161.0117970025192</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>160.9627306498521</v>
+        <v>161.0743901598943</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>161.1995832938085</v>
+        <v>161.3589936480202</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>161.6247118866366</v>
+        <v>161.8370487899967</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>161.9219762615483</v>
+        <v>162.2011597353213</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>162.4761067777917</v>
+        <v>162.8552907686603</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>162.9413995831059</v>
+        <v>163.4654439902601</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>163.428586914343</v>
+        <v>163.9438333401802</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>163.8357391552236</v>
+        <v>164.4401953761461</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>163.3351852251618</v>
+        <v>164.136088164691</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>162.1745723862047</v>
+        <v>163.5358792129999</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>161.7024290953913</v>
+        <v>161.9980064039298</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>159.2994290953913</v>
+        <v>159.5950064039298</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.8042271662141</v>
+        <v>161.5757059203003</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.6208451154959</v>
+        <v>161.5015533160936</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>161.1517351173641</v>
+        <v>160.8916006419917</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>161.0117970025192</v>
+        <v>160.7143954863245</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>161.0743901598943</v>
+        <v>160.7729996287071</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>161.3589936480202</v>
+        <v>160.9760978884108</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>161.8370487899967</v>
+        <v>161.3516749375958</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>162.2011597353213</v>
+        <v>161.6363464742296</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>162.8552907686603</v>
+        <v>162.156252644854</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>163.4654439902601</v>
+        <v>162.561375142571</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>163.9438333401802</v>
+        <v>162.9898697929416</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>164.4401953761461</v>
+        <v>163.3514691544372</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>164.136088164691</v>
+        <v>162.8279885385057</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>163.5358792129999</v>
+        <v>161.5621111405806</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>161.9980064039298</v>
+        <v>160.8350183920625</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>159.5950064039298</v>
+        <v>158.4320183920625</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.3516294588391</v>
+        <v>139.349664519743</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.5413217918147</v>
+        <v>142.5384541627847</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.8260037724372</v>
+        <v>143.8229072215471</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.5062322921935</v>
+        <v>144.5030612474882</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.4338916051104</v>
+        <v>144.4306659461195</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.3566469282976</v>
+        <v>144.3533752603139</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.313491788729</v>
+        <v>144.3102018165459</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.3527732528763</v>
+        <v>144.3494891350292</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>145.0229740556621</v>
+        <v>145.0196915242772</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.035744601936</v>
+        <v>148.035797079008</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4312977505228</v>
+        <v>148.4313095143662</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535228998641</v>
+        <v>148.8535239735152</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9141025854744</v>
+        <v>148.9144888700646</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2918480979168</v>
+        <v>149.2919635023758</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4181375175204</v>
+        <v>150.4176182742341</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.8889372998678</v>
+        <v>151.8875851857616</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2796660407632</v>
+        <v>152.2782295878831</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.608542046559</v>
+        <v>152.6071583745723</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.1974538826467</v>
+        <v>153.1965725106516</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4136709720604</v>
+        <v>152.4134479128712</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.9543443777301</v>
+        <v>152.9521754053285</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.7535710637763</v>
+        <v>152.7505941574556</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.7935188592839</v>
+        <v>152.7896420581135</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.4992902099669</v>
+        <v>154.4945921450584</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.4560349166989</v>
+        <v>155.4513760452245</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.4545697334588</v>
+        <v>156.4494878827641</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>158.120854031612</v>
+        <v>158.1152978402732</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.7165964026963</v>
+        <v>159.7119861917157</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.5208920705454</v>
+        <v>161.5179121195194</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.8663005540187</v>
+        <v>159.8681773395926</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.6048236652078</v>
+        <v>159.6057864802521</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.0967352951555</v>
+        <v>159.1022167787704</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.3127338937394</v>
+        <v>157.3198069103554</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.8467457133394</v>
+        <v>157.8534844833429</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.1716285165257</v>
+        <v>158.1777835363295</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.2196480265075</v>
+        <v>158.2256994983004</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.4658304069384</v>
+        <v>159.471492913474</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.378751620511</v>
+        <v>158.3811283590112</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7668789464249</v>
+        <v>155.7645954280151</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.9142304873682</v>
+        <v>155.9117904284671</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6832351936228</v>
+        <v>156.68219101129</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.4325354830773</v>
+        <v>156.4267183012154</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.2061454545814</v>
+        <v>156.2000308836706</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>156.0520583109397</v>
+        <v>156.0454679739395</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.2513888621726</v>
+        <v>157.2474944454316</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6356680917991</v>
+        <v>158.6366834409053</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1176804155147</v>
+        <v>159.1192891961003</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.6972985606865</v>
+        <v>159.6994775617115</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.5984305489196</v>
+        <v>159.5987755885168</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1667077666819</v>
+        <v>160.1672766702307</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.0868336911829</v>
+        <v>160.0852008845673</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.8992980698369</v>
+        <v>159.89628705882</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.3699883853629</v>
+        <v>160.3674303856987</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.1072755215932</v>
+        <v>161.1035180796538</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.5757059203003</v>
+        <v>161.798912710978</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.5015533160936</v>
+        <v>161.6173489935113</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.8916006419917</v>
+        <v>160.9665827972111</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.7143954863245</v>
+        <v>160.8050184092132</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>160.7729996287071</v>
+        <v>160.8892626380947</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>160.9760978884108</v>
+        <v>161.1552962191645</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>161.3516749375958</v>
+        <v>161.6029029986546</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>161.6363464742296</v>
+        <v>161.961855444557</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>162.156252644854</v>
+        <v>162.595993503318</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>162.561375142571</v>
+        <v>163.1661848833822</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>162.9898697929416</v>
+        <v>163.4802675817786</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>163.3514691544372</v>
+        <v>163.9181779015006</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>162.8279885385057</v>
+        <v>163.5799032877305</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>161.5621111405806</v>
+        <v>162.8094605869833</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>160.8350183920625</v>
+        <v>160.8980668305935</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>158.4320183920625</v>
+        <v>158.4950668305935</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.798912710978</v>
+        <v>161.5710650867257</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.6173489935113</v>
+        <v>161.4983321618068</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.9665827972111</v>
+        <v>160.7321593266992</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.8050184092132</v>
+        <v>160.5353183378216</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>160.8892626380947</v>
+        <v>160.6079345293527</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>161.1552962191645</v>
+        <v>160.7847046486498</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>161.6029029986546</v>
+        <v>161.12304639629</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>161.961855444557</v>
+        <v>161.3879853584111</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>162.595993503318</v>
+        <v>161.8787164209818</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>163.1661848833822</v>
+        <v>162.2354505811248</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>163.4802675817786</v>
+        <v>162.615076433881</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>163.9181779015006</v>
+        <v>162.939639931303</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>163.5799032877305</v>
+        <v>162.4045451211987</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>162.8094605869833</v>
+        <v>161.0897041721289</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>160.8980668305935</v>
+        <v>160.2406252998374</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>158.4950668305935</v>
+        <v>154.5771528155403</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.349664519743</v>
+        <v>139.347759110375</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.5384541627847</v>
+        <v>142.5356730123059</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.8229072215471</v>
+        <v>143.8199034371259</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.5030612474882</v>
+        <v>144.4999845685701</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.4306659461195</v>
+        <v>144.4275363188727</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.3533752603139</v>
+        <v>144.3502010323816</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.3102018165459</v>
+        <v>144.3070098488579</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.3494891350292</v>
+        <v>144.3463028496325</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>145.0196915242772</v>
+        <v>145.0165061141817</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.035797079008</v>
+        <v>148.0358479320839</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4313095143662</v>
+        <v>148.4313208992066</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535239735152</v>
+        <v>148.8535249942357</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9144888700646</v>
+        <v>148.9148632280613</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2919635023758</v>
+        <v>149.2920756981744</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4176182742341</v>
+        <v>150.4171149427603</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.8875851857616</v>
+        <v>151.886273427938</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2782295878831</v>
+        <v>152.2768358504945</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.6071583745723</v>
+        <v>152.6058154577523</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.1965725106516</v>
+        <v>153.1957170211787</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4134479128712</v>
+        <v>152.4132316684546</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.9521754053285</v>
+        <v>152.9500733046696</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.7505941574556</v>
+        <v>152.7477082714798</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.7896420581135</v>
+        <v>152.785882106674</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.4945921450584</v>
+        <v>154.4900349665433</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.4513760452245</v>
+        <v>155.4468553989167</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.4494878827641</v>
+        <v>156.4445556778783</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>158.1152978402732</v>
+        <v>158.1099033611866</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.7119861917157</v>
+        <v>159.7075055900538</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.5179121195194</v>
+        <v>161.5150130754085</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.8681773395926</v>
+        <v>159.8699886965175</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.6057864802521</v>
+        <v>159.6067129127899</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.1022167787704</v>
+        <v>159.1075272048514</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.3198069103554</v>
+        <v>157.3266627505586</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.8534844833429</v>
+        <v>157.8600193940175</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.1777835363295</v>
+        <v>158.1837559821358</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.2256994983004</v>
+        <v>158.2315810053369</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.471492913474</v>
+        <v>159.4769995978556</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.3811283590112</v>
+        <v>158.3834464849775</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7645954280151</v>
+        <v>155.762385573857</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.9117904284671</v>
+        <v>155.9094292204417</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.68219101129</v>
+        <v>156.6811849978499</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.4267183012154</v>
+        <v>156.4210721525804</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.2000308836706</v>
+        <v>156.1940935578096</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>156.0454679739395</v>
+        <v>156.039063000005</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.2474944454316</v>
+        <v>157.2437079999565</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6366834409053</v>
+        <v>158.6376714557143</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1192891961003</v>
+        <v>159.1208553296288</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.6994775617115</v>
+        <v>159.7015993807194</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.5987755885168</v>
+        <v>159.5991150544667</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1672766702307</v>
+        <v>160.1678360680251</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.0852008845673</v>
+        <v>160.0836206906279</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.89628705882</v>
+        <v>159.8933658527584</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.3674303856987</v>
+        <v>160.3649488131649</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.1035180796538</v>
+        <v>161.0998696918945</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.5710650867257</v>
+        <v>161.7937514238284</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.4983321618068</v>
+        <v>161.6139396808991</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.7321593266992</v>
+        <v>160.8073884627452</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.5353183378216</v>
+        <v>160.6266228566772</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>160.6079345293527</v>
+        <v>160.7309381619514</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>160.7847046486498</v>
+        <v>160.9895315739312</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>161.12304639629</v>
+        <v>161.4068692212826</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>161.3879853584111</v>
+        <v>161.7601343002285</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>161.8787164209818</v>
+        <v>162.376747165633</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>162.2354505811248</v>
+        <v>162.9147688914273</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>162.615076433881</v>
+        <v>163.2136127414154</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>162.939639931303</v>
+        <v>163.4770117322792</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>162.4045451211987</v>
+        <v>163.1168335320648</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>161.0897041721289</v>
+        <v>162.2413354653182</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>160.2406252998374</v>
+        <v>160.1916986712073</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>154.5771528155403</v>
+        <v>155.7650745012281</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.7937514238284</v>
+        <v>161.5665583710707</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.6139396808991</v>
+        <v>161.4951910952578</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.8073884627452</v>
+        <v>160.6259628177298</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.6266228566772</v>
+        <v>160.4155534850854</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>160.7309381619514</v>
+        <v>160.5020613988133</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>160.9895315739312</v>
+        <v>160.6724462825269</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>161.4068692212826</v>
+        <v>160.9791137343609</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>161.7601343002285</v>
+        <v>161.2276196765972</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>162.376747165633</v>
+        <v>161.6970112379498</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>162.9147688914273</v>
+        <v>162.0228119846905</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>163.2136127414154</v>
+        <v>162.367227896578</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>163.4770117322792</v>
+        <v>162.6714866284761</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>163.1168335320648</v>
+        <v>162.1439400974348</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>162.2413354653182</v>
+        <v>160.8553788495852</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>160.1916986712073</v>
+        <v>160.0133059027542</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>155.7650745012281</v>
+        <v>155.554766482291</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.347759110375</v>
+        <v>139.3441163787119</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.5356730123059</v>
+        <v>142.530354960068</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.8199034371259</v>
+        <v>143.8141579836426</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.4999845685701</v>
+        <v>144.4940979554557</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.4275363188727</v>
+        <v>144.421548511191</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.3502010323816</v>
+        <v>144.3441279973875</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.3070098488579</v>
+        <v>144.3009029264255</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.3463028496325</v>
+        <v>144.340206805074</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>145.0165061141817</v>
+        <v>145.0104099265389</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0358479320839</v>
+        <v>148.0359450584148</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4313208992066</v>
+        <v>148.4313426024815</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535249942357</v>
+        <v>148.8535268895856</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9148632280613</v>
+        <v>148.9155783057961</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2920756981744</v>
+        <v>149.2922909784602</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4171149427603</v>
+        <v>150.4161531803686</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.886273427938</v>
+        <v>151.8837639712824</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2768358504945</v>
+        <v>152.2741691299507</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.6058154577523</v>
+        <v>152.6032449056464</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.1957170211787</v>
+        <v>153.1940792659976</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4132316684546</v>
+        <v>152.4128184116448</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.9500733046696</v>
+        <v>152.9460577372592</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.7477082714798</v>
+        <v>152.742193391539</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.785882106674</v>
+        <v>152.7786922787442</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.4900349665433</v>
+        <v>154.4813187125204</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.4468553989167</v>
+        <v>155.4382049605599</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.4445556778783</v>
+        <v>156.435114626004</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>158.1099033611866</v>
+        <v>158.0995722471331</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.7075055900538</v>
+        <v>159.6989121749374</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.5150130754085</v>
+        <v>161.5094450656582</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.8699886965175</v>
+        <v>159.873428091051</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.6067129127899</v>
+        <v>159.6084642569716</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.1075272048514</v>
+        <v>159.1176658176358</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.3266627505586</v>
+        <v>157.3397615750636</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.8600193940175</v>
+        <v>157.8725133834163</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.1837559821358</v>
+        <v>158.1951845056925</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.2315810053369</v>
+        <v>158.2428617417682</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.4769995978556</v>
+        <v>159.4875702320828</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.3834464849775</v>
+        <v>158.3879149409236</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.762385573857</v>
+        <v>155.7581731334351</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.9094292204417</v>
+        <v>155.9049286562293</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6811849978499</v>
+        <v>156.6792796796726</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.4210721525804</v>
+        <v>156.4102637620077</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.1940935578096</v>
+        <v>156.1827208471156</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>156.039063000005</v>
+        <v>156.0267789360069</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.2437079999565</v>
+        <v>157.2364416835607</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6376714557143</v>
+        <v>158.6395697136686</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1208553296288</v>
+        <v>159.1238661416888</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.7015993807194</v>
+        <v>159.7056800492059</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.5991150544667</v>
+        <v>159.5997774255436</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1678360680251</v>
+        <v>160.1689267453947</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.0836206906279</v>
+        <v>160.0806083930093</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.8933658527584</v>
+        <v>159.8877773136102</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.3649488131649</v>
+        <v>160.3602017186213</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.0998696918945</v>
+        <v>161.0928817798345</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.5665583710707</v>
+        <v>161.7838628866356</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.4951910952578</v>
+        <v>161.607369651508</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.6259628177298</v>
+        <v>160.6008750424159</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.4155534850854</v>
+        <v>160.3881802031851</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>160.5020613988133</v>
+        <v>160.5116474885259</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>160.6724462825269</v>
+        <v>160.7378071136786</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>160.9791137343609</v>
+        <v>161.0948565125206</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>161.2276196765972</v>
+        <v>161.425897032437</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>161.6970112379498</v>
+        <v>162.0066188593906</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>162.0228119846905</v>
+        <v>162.4939710422102</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>162.367227896578</v>
+        <v>162.7735391614572</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>162.6714866284761</v>
+        <v>162.9099203432718</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>162.1439400974348</v>
+        <v>162.5717651207952</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>160.8553788495852</v>
+        <v>161.6965868541164</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>160.0133059027542</v>
+        <v>159.8550613787435</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>155.554766482291</v>
+        <v>156.4703902674056</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.3441163787119</v>
+        <v>139.3459105660351</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.530354960068</v>
+        <v>142.5329744872656</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.8141579836426</v>
+        <v>143.816988313493</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.4940979554557</v>
+        <v>144.496998107415</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.421548511191</v>
+        <v>144.4244985002905</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.3441279973875</v>
+        <v>144.3471199577608</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.3009029264255</v>
+        <v>144.3039115732266</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.340206805074</v>
+        <v>144.3432100917105</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>145.0104099265389</v>
+        <v>145.0134135816787</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0359450584148</v>
+        <v>148.035897235316</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4313426024815</v>
+        <v>148.4313319229717</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535268895856</v>
+        <v>148.8535259652603</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9155783057961</v>
+        <v>148.915226202971</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2922909784602</v>
+        <v>149.292184815697</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4161531803686</v>
+        <v>150.4166268037121</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.8837639712824</v>
+        <v>151.8850002482236</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2741691299507</v>
+        <v>152.2754829535302</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.6032449056464</v>
+        <v>152.6045115248614</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.1940792659976</v>
+        <v>153.1948862923229</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4128184116448</v>
+        <v>152.413021931176</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.9460577372592</v>
+        <v>152.9480350350953</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.742193391539</v>
+        <v>152.744909302982</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.7786922787442</v>
+        <v>152.7822338107083</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.4813187125204</v>
+        <v>154.4856124451086</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.4382049605599</v>
+        <v>155.442466935988</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.435114626004</v>
+        <v>156.4397666319178</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>158.0995722471331</v>
+        <v>158.1046636744473</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.6989121749374</v>
+        <v>159.7031492665659</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.5094450656582</v>
+        <v>161.5121917367432</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.873428091051</v>
+        <v>159.8717379200165</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.6084642569716</v>
+        <v>159.6076049023754</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.1176658176358</v>
+        <v>159.1126744245542</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.3397615750636</v>
+        <v>157.3333112277656</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.8725133834163</v>
+        <v>157.8663595137367</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.1951845056925</v>
+        <v>158.189553805436</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.2428617417682</v>
+        <v>158.2372995455508</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.4875702320828</v>
+        <v>159.4823567246747</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.3879149409236</v>
+        <v>158.3857080301285</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7581731334351</v>
+        <v>155.7602458989449</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.9049286562293</v>
+        <v>155.9071431304943</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6792796796726</v>
+        <v>156.6802151709199</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.4102637620077</v>
+        <v>156.4155896340725</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.1827208471156</v>
+        <v>156.1883259232933</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>156.0267789360069</v>
+        <v>156.0328357347321</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.2364416835607</v>
+        <v>157.2400251326801</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6395697136686</v>
+        <v>158.6386332075712</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1238661416888</v>
+        <v>159.1223804579486</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.7056800492059</v>
+        <v>159.7036661881444</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.5997774255436</v>
+        <v>159.5994489843475</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1689267453947</v>
+        <v>160.1683860566775</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.0806083930093</v>
+        <v>160.082090634586</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.8877773136102</v>
+        <v>159.8905305095693</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.3602017186213</v>
+        <v>160.3625403119053</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.0928817798345</v>
+        <v>161.0963257192726</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.7838628866356</v>
+        <v>161.5621800969266</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.607369651508</v>
+        <v>161.4921273508695</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.6008750424159</v>
+        <v>160.4901681281042</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.3881802031851</v>
+        <v>160.2629874070323</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>160.5116474885259</v>
+        <v>160.3661301069397</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>160.7378071136786</v>
+        <v>160.5244756687049</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>161.0948565125206</v>
+        <v>160.7955978957482</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>161.425897032437</v>
+        <v>161.0268273757392</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>162.0066188593906</v>
+        <v>161.4721410219981</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>162.4939710422102</v>
+        <v>161.7618184542306</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>162.7735391614572</v>
+        <v>162.0678367317758</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>162.9099203432718</v>
+        <v>162.3457332080589</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>162.5717651207952</v>
+        <v>161.8147870916688</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>161.6965868541164</v>
+        <v>160.5201427264477</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>159.8550613787435</v>
+        <v>159.6420496376719</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>156.4703902674056</v>
+        <v>155.7663337120403</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.3459105660351</v>
+        <v>139.3423741857338</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.5329744872656</v>
+        <v>142.5278110123755</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.816988313493</v>
+        <v>143.8114088021543</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.496998107415</v>
+        <v>144.4912804265589</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.4244985002905</v>
+        <v>144.4186825989425</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.3471199577608</v>
+        <v>144.3412213422507</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.3039115732266</v>
+        <v>144.2979800767039</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.3432100917105</v>
+        <v>144.3372891646152</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>145.0134135816787</v>
+        <v>145.0074913748032</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.035897235316</v>
+        <v>148.0359914669763</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4313319229717</v>
+        <v>148.4313529535317</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535259652603</v>
+        <v>148.8535277699902</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.915226202971</v>
+        <v>148.9159200174262</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.292184815697</v>
+        <v>149.2923943035507</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4166268037121</v>
+        <v>150.415693435562</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.8850002482236</v>
+        <v>151.8825630172961</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2754829535302</v>
+        <v>152.2728927130848</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.6045115248614</v>
+        <v>152.6020140237562</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.1948862923229</v>
+        <v>153.193294943467</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.413021931176</v>
+        <v>152.4126208373801</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.9480350350953</v>
+        <v>152.9441387198301</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.744909302982</v>
+        <v>152.7395569015589</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.7822338107083</v>
+        <v>152.7752529003896</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.4856124451086</v>
+        <v>154.4771482358936</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.442466935988</v>
+        <v>155.434064098339</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.4397666319178</v>
+        <v>156.4305938836456</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>158.1046636744473</v>
+        <v>158.0946229067921</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.7031492665659</v>
+        <v>159.6947895351852</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.5121917367432</v>
+        <v>161.5067701778175</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.8717379200165</v>
+        <v>159.875062093246</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.6076049023754</v>
+        <v>159.6092926636963</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.1126744245542</v>
+        <v>159.1225083271847</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.3333112277656</v>
+        <v>157.3460224873343</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.8663595137367</v>
+        <v>157.878489054134</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.189553805436</v>
+        <v>158.200655161786</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.2372995455508</v>
+        <v>158.2482738662174</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.4823567246747</v>
+        <v>159.4926457524018</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.3857080301285</v>
+        <v>158.3900690823141</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7602458989449</v>
+        <v>155.7561642063775</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.9071431304943</v>
+        <v>155.9027825082513</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6802151709199</v>
+        <v>156.6783767943031</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.4155896340725</v>
+        <v>156.4050879429554</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.1883259232933</v>
+        <v>156.1772715882653</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>156.0328357347321</v>
+        <v>156.0208857468689</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.2400251326801</v>
+        <v>157.2329537104876</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6386332075712</v>
+        <v>158.640481940338</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1223804579486</v>
+        <v>159.125313865063</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.7036661881444</v>
+        <v>159.7076429299478</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.5994489843475</v>
+        <v>159.6001004337007</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1683860566775</v>
+        <v>160.1694582538226</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.082090634586</v>
+        <v>160.0791717825134</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.8905305095693</v>
+        <v>159.885102759718</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.3625403119053</v>
+        <v>160.357930049032</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.0963257192726</v>
+        <v>161.0895337313172</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.5621800969266</v>
+        <v>161.7791237633196</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.4921273508695</v>
+        <v>161.6042033174843</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.4901681281042</v>
+        <v>160.4728049798707</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.2629874070323</v>
+        <v>160.2439328475176</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>160.3661301069397</v>
+        <v>160.3707679146185</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>160.5244756687049</v>
+        <v>160.5706693736381</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>160.7955978957482</v>
+        <v>160.8840701218786</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>161.0268273757392</v>
+        <v>161.1937887103724</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>161.4721410219981</v>
+        <v>161.7473248847052</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>161.7618184542306</v>
+        <v>162.1996301846203</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>162.0678367317758</v>
+        <v>162.4638863689853</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>162.3457332080589</v>
+        <v>162.6111833977383</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>161.8147870916688</v>
+        <v>162.292174884826</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>160.5201427264477</v>
+        <v>161.2429847350433</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>159.6420496376719</v>
+        <v>159.3742444866268</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>155.7663337120403</v>
+        <v>156.2794453720474</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B111"/>
+  <dimension ref="A1:B112"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.3423741857338</v>
+        <v>139.3406817593913</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.5278110123755</v>
+        <v>142.525339420237</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.8114088021543</v>
+        <v>143.8087373295515</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.4912804265589</v>
+        <v>144.4885420414328</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.4186825989425</v>
+        <v>144.4158972215765</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.3412213422507</v>
+        <v>144.3383963972523</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.2979800767039</v>
+        <v>144.295139407544</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.3372891646152</v>
+        <v>144.3344535600911</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>145.0074913748032</v>
+        <v>145.0046543630207</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0359914669763</v>
+        <v>148.0360365227803</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4313529535317</v>
+        <v>148.4313629909705</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535277699902</v>
+        <v>148.8535286090534</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9159200174262</v>
+        <v>148.9162517908228</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2923943035507</v>
+        <v>149.2924949020314</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.415693435562</v>
+        <v>150.415246968833</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.8825630172961</v>
+        <v>151.8813958952596</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2728927130848</v>
+        <v>152.2716521296115</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.6020140237562</v>
+        <v>152.6008173902464</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.193294943467</v>
+        <v>153.1925323812489</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4126208373801</v>
+        <v>152.4124289515949</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.9441387198301</v>
+        <v>152.9422754473474</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.7395569015589</v>
+        <v>152.736996406179</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.7752529003896</v>
+        <v>152.7719113264653</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.4771482358936</v>
+        <v>154.4730957941263</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.434064098339</v>
+        <v>155.43003927431</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.4305938836456</v>
+        <v>156.4261989472217</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>158.0946229067921</v>
+        <v>158.0898098170667</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.6947895351852</v>
+        <v>159.6907768165584</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.5067701778175</v>
+        <v>161.5041643330519</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.875062093246</v>
+        <v>159.8766426282516</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.6092926636963</v>
+        <v>159.6100916985476</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.1225083271847</v>
+        <v>159.1272084913369</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.3460224873343</v>
+        <v>157.3521021597729</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.878489054134</v>
+        <v>157.8842941215892</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.200655161786</v>
+        <v>158.2059724608917</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.2482738662174</v>
+        <v>158.2535418631684</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.4926457524018</v>
+        <v>159.4975886312281</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.3900690823141</v>
+        <v>158.3921722413747</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7561642063775</v>
+        <v>155.7542162308965</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.9027825082513</v>
+        <v>155.9007015943088</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6783767943031</v>
+        <v>156.677504896477</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.4050879429554</v>
+        <v>156.4000559469667</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.1772715882653</v>
+        <v>156.171971771325</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>156.0208857468689</v>
+        <v>156.0151496704676</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.2329537104876</v>
+        <v>157.2295574753322</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.640481940338</v>
+        <v>158.6413708061129</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.125313865063</v>
+        <v>159.1267250403521</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.7076429299478</v>
+        <v>159.7095567028915</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.6001004337007</v>
+        <v>159.6004180713818</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1694582538226</v>
+        <v>160.1699807101745</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.0791717825134</v>
+        <v>160.0777787494523</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.885102759718</v>
+        <v>159.8825035385737</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.357930049032</v>
+        <v>160.3557224854549</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.0895337313172</v>
+        <v>161.0862776551311</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.7791237633196</v>
+        <v>161.7745140162152</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.6042033174843</v>
+        <v>161.6011125487521</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.4728049798707</v>
+        <v>160.4748002311179</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.2439328475176</v>
+        <v>160.2013036807135</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>160.3707679146185</v>
+        <v>160.3075467504013</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>160.5706693736381</v>
+        <v>160.5057977490337</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>160.8840701218786</v>
+        <v>160.8102434412126</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>161.1937887103724</v>
+        <v>161.0912878956507</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>161.7473248847052</v>
+        <v>161.6119954550785</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>162.1996301846203</v>
+        <v>162.0395473943667</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>162.4638863689853</v>
+        <v>162.2933985353313</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>162.6111833977383</v>
+        <v>162.4399925669481</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>162.292174884826</v>
+        <v>162.1670109734112</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>161.2429847350433</v>
+        <v>161.1913819772471</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>159.3742444866268</v>
+        <v>159.5094779836968</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,15 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>156.2794453720474</v>
+        <v>156.5365669338504</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112" s="3">
+        <v>46339</v>
+      </c>
+      <c r="B112">
+        <v>157.8460019078754</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.3406817593913</v>
+        <v>139.3423741857338</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.525339420237</v>
+        <v>142.5278110123755</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.8087373295515</v>
+        <v>143.8114088021543</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.4885420414328</v>
+        <v>144.4912804265589</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.4158972215765</v>
+        <v>144.4186825989425</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.3383963972523</v>
+        <v>144.3412213422507</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.295139407544</v>
+        <v>144.2979800767039</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.3344535600911</v>
+        <v>144.3372891646152</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>145.0046543630207</v>
+        <v>145.0074913748032</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0360365227803</v>
+        <v>148.0359914669763</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4313629909705</v>
+        <v>148.4313529535317</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535286090534</v>
+        <v>148.8535277699902</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9162517908228</v>
+        <v>148.9159200174262</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2924949020314</v>
+        <v>149.2923943035507</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.415246968833</v>
+        <v>150.415693435562</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.8813958952596</v>
+        <v>151.8825630172961</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2716521296115</v>
+        <v>152.2728927130848</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.6008173902464</v>
+        <v>152.6020140237562</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.1925323812489</v>
+        <v>153.193294943467</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4124289515949</v>
+        <v>152.4126208373801</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.9422754473474</v>
+        <v>152.9441387198301</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.736996406179</v>
+        <v>152.7395569015589</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.7719113264653</v>
+        <v>152.7752529003896</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.4730957941263</v>
+        <v>154.4771482358936</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.43003927431</v>
+        <v>155.434064098339</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.4261989472217</v>
+        <v>156.4305938836456</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>158.0898098170667</v>
+        <v>158.0946229067921</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.6907768165584</v>
+        <v>159.6947895351852</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.5041643330519</v>
+        <v>161.5067701778175</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.8766426282516</v>
+        <v>159.875062093246</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.6100916985476</v>
+        <v>159.6092926636963</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.1272084913369</v>
+        <v>159.1225083271847</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.3521021597729</v>
+        <v>157.3460224873343</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.8842941215892</v>
+        <v>157.878489054134</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.2059724608917</v>
+        <v>158.200655161786</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.2535418631684</v>
+        <v>158.2482738662174</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.4975886312281</v>
+        <v>159.4926457524018</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.3921722413747</v>
+        <v>158.3900690823141</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7542162308965</v>
+        <v>155.7561642063775</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.9007015943088</v>
+        <v>155.9027825082513</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.677504896477</v>
+        <v>156.6783767943031</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.4000559469667</v>
+        <v>156.4050879429554</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.171971771325</v>
+        <v>156.1772715882653</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>156.0151496704676</v>
+        <v>156.0208857468689</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.2295574753322</v>
+        <v>157.2329537104876</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6413708061129</v>
+        <v>158.640481940338</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1267250403521</v>
+        <v>159.125313865063</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.7095567028915</v>
+        <v>159.7076429299478</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.6004180713818</v>
+        <v>159.6001004337007</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1699807101745</v>
+        <v>160.1694582538226</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.0777787494523</v>
+        <v>160.0791717825134</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.8825035385737</v>
+        <v>159.885102759718</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.3557224854549</v>
+        <v>160.357930049032</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.0862776551311</v>
+        <v>161.0895337313172</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.7745140162152</v>
+        <v>161.5537877102295</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.6011125487521</v>
+        <v>161.4862213275815</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.4748002311179</v>
+        <v>160.4933169395236</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.2013036807135</v>
+        <v>160.179994394385</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>160.3075467504013</v>
+        <v>160.2448985089919</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>160.5057977490337</v>
+        <v>160.4282756766949</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>160.8102434412126</v>
+        <v>160.7630891365596</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>161.0912878956507</v>
+        <v>160.9787039648749</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>161.6119954550785</v>
+        <v>161.3981504629867</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>162.0395473943667</v>
+        <v>161.7027195758381</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>162.2933985353313</v>
+        <v>162.0079876918264</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>162.4399925669481</v>
+        <v>162.2838153048996</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>162.1670109734112</v>
+        <v>161.5699821334011</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>161.1913819772471</v>
+        <v>160.4112248698326</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>159.5094779836968</v>
+        <v>159.675366720151</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>156.5365669338504</v>
+        <v>157.0087421757949</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>157.8460019078754</v>
+        <v>159.2992421757949</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.3423741857338</v>
+        <v>139.3390369974373</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.5278110123755</v>
+        <v>142.5229371404664</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.8114088021543</v>
+        <v>143.8061403179651</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.4912804265589</v>
+        <v>144.4858795133284</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.4186825989425</v>
+        <v>144.4131890332177</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.3412213422507</v>
+        <v>144.3356497664067</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.2979800767039</v>
+        <v>144.2923775027655</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.3372891646152</v>
+        <v>144.3316965812537</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>145.0074913748032</v>
+        <v>145.0018955237859</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0359914669763</v>
+        <v>148.0360802840644</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4313529535317</v>
+        <v>148.4313727287684</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535277699902</v>
+        <v>148.8535294091721</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9159200174262</v>
+        <v>148.9165740530165</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2923943035507</v>
+        <v>149.2925928793176</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.415693435562</v>
+        <v>150.4148132138277</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.8825630172961</v>
+        <v>151.880261196833</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2728927130848</v>
+        <v>152.2704458931225</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.6020140237562</v>
+        <v>152.599653597614</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.193294943467</v>
+        <v>153.1917906873509</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4126208373801</v>
+        <v>152.4122425120811</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.9441387198301</v>
+        <v>152.9404655291136</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.7395569015589</v>
+        <v>152.7345086725254</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.7752529003896</v>
+        <v>152.7686634507964</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.4771482358936</v>
+        <v>154.4691564562895</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.434064098339</v>
+        <v>155.4261256922545</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.4305938836456</v>
+        <v>156.4219246563691</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>158.0946229067921</v>
+        <v>158.0851274552558</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.6947895351852</v>
+        <v>159.6868697217173</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.5067701778175</v>
+        <v>161.5016249266532</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.875062093246</v>
+        <v>159.8781722297057</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.6092926636963</v>
+        <v>159.6108628352196</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.1225083271847</v>
+        <v>159.1317724722751</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.3460224873343</v>
+        <v>157.3580083231576</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.878489054134</v>
+        <v>157.8899357577086</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.200655161786</v>
+        <v>158.2111427250267</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.2482738662174</v>
+        <v>158.2586713698626</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.4926457524018</v>
+        <v>159.5024039451527</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.3900690823141</v>
+        <v>158.3942261308089</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7561642063775</v>
+        <v>155.7523264906702</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.9027825082513</v>
+        <v>155.8986830048259</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6783767943031</v>
+        <v>156.676662470657</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.4050879429554</v>
+        <v>156.395161882966</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.1772715882653</v>
+        <v>156.1668153621615</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>156.0208857468689</v>
+        <v>156.0095645469281</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.2329537104876</v>
+        <v>157.226249431044</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.640481940338</v>
+        <v>158.6422371845803</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.125313865063</v>
+        <v>159.1281010120873</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.7076429299478</v>
+        <v>159.7114231523283</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.6001004337007</v>
+        <v>159.6007304068979</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1694582538226</v>
+        <v>160.1704942496064</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.0791717825134</v>
+        <v>160.0764273605009</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.885102759718</v>
+        <v>159.8799765232667</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.357930049032</v>
+        <v>160.3535763654007</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.0895337313172</v>
+        <v>161.0831098415963</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.5537877102295</v>
+        <v>161.7700284700534</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.4862213275815</v>
+        <v>161.5980948141653</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.4933169395236</v>
+        <v>160.4767169116795</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.179994394385</v>
+        <v>160.167035369552</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>160.2448985089919</v>
+        <v>160.256020605646</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>160.4282756766949</v>
+        <v>160.4521863311602</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>160.7630891365596</v>
+        <v>160.7501444838249</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>160.9787039648749</v>
+        <v>160.9956111094804</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>161.3981504629867</v>
+        <v>161.4931884637834</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>161.7027195758381</v>
+        <v>161.8982785394013</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>162.0079876918264</v>
+        <v>162.1418898146459</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>162.2838153048996</v>
+        <v>162.2868550811129</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>161.5699821334011</v>
+        <v>162.0541096457406</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>160.4112248698326</v>
+        <v>161.1443722724775</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>159.675366720151</v>
+        <v>159.6164419859208</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>157.0087421757949</v>
+        <v>157.1013628790889</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>159.2992421757949</v>
+        <v>157.9025749887685</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.3390369974373</v>
+        <v>139.3406817593913</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.5229371404664</v>
+        <v>142.525339420237</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.8061403179651</v>
+        <v>143.8087373295515</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.4858795133284</v>
+        <v>144.4885420414328</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.4131890332177</v>
+        <v>144.4158972215765</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.3356497664067</v>
+        <v>144.3383963972523</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.2923775027655</v>
+        <v>144.295139407544</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.3316965812537</v>
+        <v>144.3344535600911</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>145.0018955237859</v>
+        <v>145.0046543630207</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0360802840644</v>
+        <v>148.0360365227803</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4313727287684</v>
+        <v>148.4313629909705</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535294091721</v>
+        <v>148.8535286090534</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9165740530165</v>
+        <v>148.9162517908228</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2925928793176</v>
+        <v>149.2924949020314</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4148132138277</v>
+        <v>150.415246968833</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.880261196833</v>
+        <v>151.8813958952596</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2704458931225</v>
+        <v>152.2716521296115</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.599653597614</v>
+        <v>152.6008173902464</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.1917906873509</v>
+        <v>153.1925323812489</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4122425120811</v>
+        <v>152.4124289515949</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.9404655291136</v>
+        <v>152.9422754473474</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.7345086725254</v>
+        <v>152.736996406179</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.7686634507964</v>
+        <v>152.7719113264653</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.4691564562895</v>
+        <v>154.4730957941263</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.4261256922545</v>
+        <v>155.43003927431</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.4219246563691</v>
+        <v>156.4261989472217</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>158.0851274552558</v>
+        <v>158.0898098170667</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.6868697217173</v>
+        <v>159.6907768165584</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.5016249266532</v>
+        <v>161.5041643330519</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.8781722297057</v>
+        <v>159.8766426282516</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.6108628352196</v>
+        <v>159.6100916985476</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.1317724722751</v>
+        <v>159.1272084913369</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.3580083231576</v>
+        <v>157.3521021597729</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.8899357577086</v>
+        <v>157.8842941215892</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.2111427250267</v>
+        <v>158.2059724608917</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.2586713698626</v>
+        <v>158.2535418631684</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.5024039451527</v>
+        <v>159.4975886312281</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.3942261308089</v>
+        <v>158.3921722413747</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7523264906702</v>
+        <v>155.7542162308965</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.8986830048259</v>
+        <v>155.9007015943088</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.676662470657</v>
+        <v>156.677504896477</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.395161882966</v>
+        <v>156.4000559469667</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.1668153621615</v>
+        <v>156.171971771325</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>156.0095645469281</v>
+        <v>156.0151496704676</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.226249431044</v>
+        <v>157.2295574753322</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6422371845803</v>
+        <v>158.6413708061129</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1281010120873</v>
+        <v>159.1267250403521</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.7114231523283</v>
+        <v>159.7095567028915</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.6007304068979</v>
+        <v>159.6004180713818</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1704942496064</v>
+        <v>160.1699807101745</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.0764273605009</v>
+        <v>160.0777787494523</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.8799765232667</v>
+        <v>159.8825035385737</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.3535763654007</v>
+        <v>160.3557224854549</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.0831098415963</v>
+        <v>161.0862776551311</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.7700284700534</v>
+        <v>161.5497637261365</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.5980948141653</v>
+        <v>161.4833740651769</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.4767169116795</v>
+        <v>160.4947903753597</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.167035369552</v>
+        <v>160.1441836373511</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>160.256020605646</v>
+        <v>160.1927890067244</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>160.4521863311602</v>
+        <v>160.3845443884506</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>160.7501444838249</v>
+        <v>160.7476450421007</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>160.9956111094804</v>
+        <v>160.95400175552</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>161.4931884637834</v>
+        <v>161.3605163474972</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>161.8982785394013</v>
+        <v>161.6705511443925</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>162.1418898146459</v>
+        <v>161.9744143411146</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>162.2868550811129</v>
+        <v>162.2482176421008</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>162.0541096457406</v>
+        <v>161.4636683677413</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>161.1443722724775</v>
+        <v>160.3649381346913</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>159.6164419859208</v>
+        <v>159.6851961391527</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>157.1013628790889</v>
+        <v>157.3900067538307</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>157.9025749887685</v>
+        <v>159.9436749130264</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.3406817593913</v>
+        <v>139.3374379143773</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.525339420237</v>
+        <v>142.5206012981496</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.8087373295515</v>
+        <v>143.8036146979781</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.4885420414328</v>
+        <v>144.4832897349084</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.4158972215765</v>
+        <v>144.4105548707055</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.3383963972523</v>
+        <v>144.332978239251</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.295139407544</v>
+        <v>144.2896911328504</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.3344535600911</v>
+        <v>144.3290150041977</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>145.0046543630207</v>
+        <v>144.9992116724504</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0360365227803</v>
+        <v>148.0361228057737</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4313629909705</v>
+        <v>148.4313821800814</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535286090534</v>
+        <v>148.8535301725755</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9162517908228</v>
+        <v>148.9168872069349</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2924949020314</v>
+        <v>149.2926883355257</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.415246968833</v>
+        <v>150.4143916359128</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.8813958952596</v>
+        <v>151.8791575906969</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2716521296115</v>
+        <v>152.2692725982086</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.6008173902464</v>
+        <v>152.5985213143143</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.1925323812489</v>
+        <v>153.1910690178105</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4124289515949</v>
+        <v>152.4120612901897</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.9422754473474</v>
+        <v>152.9387067090216</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.736996406179</v>
+        <v>152.7320906482028</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.7719113264653</v>
+        <v>152.7655053935032</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.4730957941263</v>
+        <v>154.4653255617857</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.43003927431</v>
+        <v>155.4223188159231</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.4261989472217</v>
+        <v>156.4177661280954</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>158.0898098170667</v>
+        <v>158.0805705916407</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.6907768165584</v>
+        <v>159.683064172084</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.5041643330519</v>
+        <v>161.4991494812741</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.8766426282516</v>
+        <v>159.8796532759435</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.6100916985476</v>
+        <v>159.6116074531058</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.1272084913369</v>
+        <v>159.1362060827794</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.3521021597729</v>
+        <v>157.3637482761816</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.8842941215892</v>
+        <v>157.8954207396659</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.2059724608917</v>
+        <v>158.2161719354814</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.2535418631684</v>
+        <v>158.2636677358802</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.4975886312281</v>
+        <v>159.5070965182089</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.3921722413747</v>
+        <v>158.3962323923233</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7542162308965</v>
+        <v>155.7504924275786</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.9007015943088</v>
+        <v>155.8967239996835</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.677504896477</v>
+        <v>156.6758480962146</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.4000559469667</v>
+        <v>156.3904001761082</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.171971771325</v>
+        <v>156.161796645519</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>156.0151496704676</v>
+        <v>156.0041245319609</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.2295574753322</v>
+        <v>157.2230262097049</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6413708061129</v>
+        <v>158.6430819070356</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1267250403521</v>
+        <v>159.1294430609564</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.7095567028915</v>
+        <v>159.7132439792765</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.6004180713818</v>
+        <v>159.6010375132894</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1699807101745</v>
+        <v>160.170999012808</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.0777787494523</v>
+        <v>160.0751157940385</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.8825035385737</v>
+        <v>159.8775187569452</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.3557224854549</v>
+        <v>160.3514891710877</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.0862776551311</v>
+        <v>161.080026776323</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.5497637261365</v>
+        <v>161.7656622191794</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.4833740651769</v>
+        <v>161.5951476852876</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.4947903753597</v>
+        <v>160.4785591342692</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.1441836373511</v>
+        <v>160.1336934221117</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>160.1927890067244</v>
+        <v>160.2072099040754</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>160.3845443884506</v>
+        <v>160.3999909474903</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>160.7476450421007</v>
+        <v>160.6914686882826</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>160.95400175552</v>
+        <v>160.9024944265906</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>161.3605163474972</v>
+        <v>161.3783426840824</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>161.6705511443925</v>
+        <v>161.7626585438172</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>161.9744143411146</v>
+        <v>161.9965531006816</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>162.2482176421008</v>
+        <v>162.1397003708814</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>161.4636683677413</v>
+        <v>161.9432399226762</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>160.3649381346913</v>
+        <v>161.0921310966578</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>159.6851961391527</v>
+        <v>159.6914482112689</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>157.3900067538307</v>
+        <v>157.5173941776417</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>159.9436749130264</v>
+        <v>157.8836044658523</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.3374379143773</v>
+        <v>139.3358826334763</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.5206012981496</v>
+        <v>142.5183291751752</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.8036146979781</v>
+        <v>143.8011575665396</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.4832897349084</v>
+        <v>144.4807697661775</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.4105548707055</v>
+        <v>144.4079917412968</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.332978239251</v>
+        <v>144.3303787783537</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.2896911328504</v>
+        <v>144.2870772423715</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.3290150041977</v>
+        <v>144.3264057788103</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>144.9992116724504</v>
+        <v>144.9965997949005</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0361228057737</v>
+        <v>148.0361641397898</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4313821800814</v>
+        <v>148.4313913573099</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535301725755</v>
+        <v>148.8535309013393</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9168872069349</v>
+        <v>148.9171916330787</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2926883355257</v>
+        <v>149.2927813657974</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4143916359128</v>
+        <v>150.4139817299878</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.8791575906969</v>
+        <v>151.8780838173633</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2692725982086</v>
+        <v>152.2681309150229</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.5985213143143</v>
+        <v>152.5974192797132</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.1910690178105</v>
+        <v>153.1903665735096</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4120612901897</v>
+        <v>152.4118850698952</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.9387067090216</v>
+        <v>152.9369968562273</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.7320906482028</v>
+        <v>152.7297394488946</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.7655053935032</v>
+        <v>152.7624334856496</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.4653255617857</v>
+        <v>154.461598702111</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.4223188159231</v>
+        <v>155.4186143517086</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.4177661280954</v>
+        <v>156.4137187384617</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>158.0805705916407</v>
+        <v>158.0761342704143</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.683064172084</v>
+        <v>159.679356294266</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.4991494812741</v>
+        <v>161.4967356393883</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.8796532759435</v>
+        <v>159.8810880015803</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.6116074531058</v>
+        <v>159.6123268445729</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.1362060827794</v>
+        <v>159.140514810566</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.3637482761816</v>
+        <v>157.3693289151309</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.8954207396659</v>
+        <v>157.9007554765597</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.2161719354814</v>
+        <v>158.2210657553281</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.2636677358802</v>
+        <v>158.2685360410777</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.5070965182089</v>
+        <v>159.5116709371516</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.3962323923233</v>
+        <v>158.3981925998672</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7504924275786</v>
+        <v>155.7487116304065</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.8967239996835</v>
+        <v>155.8948219961264</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6758480962146</v>
+        <v>156.6750604402479</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.3904001761082</v>
+        <v>156.3857655469195</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.161796645519</v>
+        <v>156.1569102043432</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>156.0041245319609</v>
+        <v>155.9988240770654</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.2230262097049</v>
+        <v>157.2198846114583</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6430819070356</v>
+        <v>158.6439057649586</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1294430609564</v>
+        <v>159.130752407452</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.7132439792765</v>
+        <v>159.7150208061231</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.6010375132894</v>
+        <v>159.6013394674413</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.170999012808</v>
+        <v>160.1714951447798</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.0751157940385</v>
+        <v>160.0738423322587</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.8775187569452</v>
+        <v>159.8751274414532</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.3514891710877</v>
+        <v>160.3494585197903</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.080026776323</v>
+        <v>161.0770251276335</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.7656622191794</v>
+        <v>161.7614106104078</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.5951476852876</v>
+        <v>161.5922688319913</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.4785591342692</v>
+        <v>160.4803307461051</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.1336934221117</v>
+        <v>160.0917141334569</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>160.2072099040754</v>
+        <v>160.1504475773353</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>160.3999909474903</v>
+        <v>160.3402231257216</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>160.6914686882826</v>
+        <v>160.6265663080806</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>160.9024944265906</v>
+        <v>160.803794367426</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>161.3783426840824</v>
+        <v>161.2590466934882</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>161.7626585438172</v>
+        <v>161.6233344666409</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>161.9965531006816</v>
+        <v>161.8473076136228</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>162.1397003708814</v>
+        <v>161.987633049029</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>161.9432399226762</v>
+        <v>161.8246360461597</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>161.0921310966578</v>
+        <v>161.0235994105581</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>159.6914482112689</v>
+        <v>159.7251760500323</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>157.5173941776417</v>
+        <v>157.5118793749476</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>157.8836044658523</v>
+        <v>157.7458453241549</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.3358826334763</v>
+        <v>139.3343693794124</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.5183291751752</v>
+        <v>142.5161181996885</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.8011575665396</v>
+        <v>143.7987661758469</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.4807697661775</v>
+        <v>144.4783168233726</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.4079917412968</v>
+        <v>144.4054968113472</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.3303787783537</v>
+        <v>144.327848507818</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.2870772423715</v>
+        <v>144.284532938424</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.3264057788103</v>
+        <v>144.3238660172219</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>144.9965997949005</v>
+        <v>144.994057036302</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0361641397898</v>
+        <v>148.0362043351418</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4313913573099</v>
+        <v>148.4314002721514</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535309013393</v>
+        <v>148.8535315973976</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9171916330787</v>
+        <v>148.9174876910594</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2927813657974</v>
+        <v>149.2928720606001</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4139817299878</v>
+        <v>150.4135830184762</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.8780838173633</v>
+        <v>151.8770386844004</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2681309150229</v>
+        <v>152.2670195842753</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.5974192797132</v>
+        <v>152.5963462994364</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.1903665735096</v>
+        <v>153.1896825972388</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4118850698952</v>
+        <v>152.4117136469358</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.9369968562273</v>
+        <v>152.9353339565861</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.7297394488946</v>
+        <v>152.7274523469714</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.7624334856496</v>
+        <v>152.7594442551228</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.461598702111</v>
+        <v>154.45797170407</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.4186143517086</v>
+        <v>155.4150082326828</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.4137187384617</v>
+        <v>156.4097781056921</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>158.0761342704143</v>
+        <v>158.0718137920733</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.679356294266</v>
+        <v>159.6757424074638</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.4967356393883</v>
+        <v>161.4943811562651</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.8810880015803</v>
+        <v>159.8824785080839</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.6123268445729</v>
+        <v>159.6130222215831</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.140514810566</v>
+        <v>159.1447038406261</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.3693289151309</v>
+        <v>157.3747567611551</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.9007554765597</v>
+        <v>157.9059460339661</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.2210657553281</v>
+        <v>158.22582955018</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.2685360410777</v>
+        <v>158.2732811122139</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.5116709371516</v>
+        <v>159.5161315656604</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.3981925998672</v>
+        <v>158.4001082627398</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7487116304065</v>
+        <v>155.7469818244949</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.8948219961264</v>
+        <v>155.8929745576858</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6750604402479</v>
+        <v>156.6742982510314</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.3857655469195</v>
+        <v>156.3812529920619</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.1569102043432</v>
+        <v>156.1521509006853</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>155.9988240770654</v>
+        <v>155.9936579111921</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.2198846114583</v>
+        <v>157.2168215942424</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6439057649586</v>
+        <v>158.6447095123207</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.130752407452</v>
+        <v>159.1320302152819</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.7150208061231</v>
+        <v>159.7167551809739</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.6013394674413</v>
+        <v>159.6016363493119</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1714951447798</v>
+        <v>160.1719827937749</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.0738423322587</v>
+        <v>160.0726053539329</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.8751274414532</v>
+        <v>159.8727999268631</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.3494585197903</v>
+        <v>160.347482154946</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.0770251276335</v>
+        <v>161.0741017349357</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.7614106104078</v>
+        <v>161.7572692271546</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.5922688319913</v>
+        <v>161.5894560181995</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.4803307461051</v>
+        <v>160.4820353491306</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.0917141334569</v>
+        <v>160.0524081712629</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>160.1504475773353</v>
+        <v>160.0954315565094</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>160.3402231257216</v>
+        <v>160.2793151228065</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>160.6265663080806</v>
+        <v>160.5492184071646</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>160.803794367426</v>
+        <v>160.6953333776956</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>161.2590466934882</v>
+        <v>161.1282047571331</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>161.6233344666409</v>
+        <v>161.4672598314876</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>161.8473076136228</v>
+        <v>161.6717640778646</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>161.987633049029</v>
+        <v>161.79428390333</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>161.8246360461597</v>
+        <v>161.6276923827647</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>161.0235994105581</v>
+        <v>160.8312863569165</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>159.7251760500323</v>
+        <v>159.5593813148583</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>157.5118793749476</v>
+        <v>157.4978855662478</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>157.7458453241549</v>
+        <v>157.6337683341818</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.3343693794124</v>
+        <v>139.3328964715188</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.5161181996885</v>
+        <v>142.5139659363865</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.7987661758469</v>
+        <v>143.7964379231074</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.4783168233726</v>
+        <v>144.4759282687261</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.4054968113472</v>
+        <v>144.4030673958825</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.327848507818</v>
+        <v>144.3253847026893</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.284532938424</v>
+        <v>144.2820554799655</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.3238660172219</v>
+        <v>144.3213929831648</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>144.994057036302</v>
+        <v>144.9915806907236</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0362043351418</v>
+        <v>148.0362434381989</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4314002721514</v>
+        <v>148.4314089356502</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535315973976</v>
+        <v>148.8535322625548</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9174876910594</v>
+        <v>148.9177757210127</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2928720606001</v>
+        <v>149.2929605060071</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4135830184762</v>
+        <v>150.4131950494775</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.8770386844004</v>
+        <v>151.8760210620325</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2670195842753</v>
+        <v>152.265937412619</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.5963462994364</v>
+        <v>152.5953012410795</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.1896825972388</v>
+        <v>153.1890163709895</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4117136469358</v>
+        <v>152.4115468280238</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.9353339565861</v>
+        <v>152.9337161047815</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.7274523469714</v>
+        <v>152.7252267610106</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.7594442551228</v>
+        <v>152.7565344136305</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.45797170407</v>
+        <v>154.4544406143125</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.4150082326828</v>
+        <v>155.4114966038729</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.4097781056921</v>
+        <v>156.4059400745825</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>158.0718137920733</v>
+        <v>158.0676046971429</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.6757424074638</v>
+        <v>159.6722190117821</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.4943811562651</v>
+        <v>161.4920838934225</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.8824785080839</v>
+        <v>159.8838267734349</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.6130222215831</v>
+        <v>159.6136947217288</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.1447038406261</v>
+        <v>159.148778075752</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.3747567611551</v>
+        <v>157.380037985358</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.9059460339661</v>
+        <v>157.9109981565594</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.22582955018</v>
+        <v>158.2304684073571</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.2732811122139</v>
+        <v>158.2779075383756</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.5161315656604</v>
+        <v>159.5204825575525</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.4001082627398</v>
+        <v>158.4019808285621</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7469818244949</v>
+        <v>155.7453008622533</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.8929745576858</v>
+        <v>155.8911793840203</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6742982510314</v>
+        <v>156.6735603520376</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.3812529920619</v>
+        <v>156.3768577665755</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.1521509006853</v>
+        <v>156.1475138580458</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>155.9936579111921</v>
+        <v>155.9886210237406</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.2168215942424</v>
+        <v>157.2138342642595</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6447095123207</v>
+        <v>158.6454938677388</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1320302152819</v>
+        <v>159.1332775945567</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.7167551809739</v>
+        <v>159.7184485817306</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.6016363493119</v>
+        <v>159.6019282412638</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1719827937749</v>
+        <v>160.1724621103818</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.0726053539329</v>
+        <v>160.0714033277674</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.8727999268631</v>
+        <v>159.870533701823</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.347482154946</v>
+        <v>160.3455579379532</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.0741017349357</v>
+        <v>161.0712535979654</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.7572692271546</v>
+        <v>161.7532338747383</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.5894560181995</v>
+        <v>161.5867070977773</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.4820353491306</v>
+        <v>160.4836763184709</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.0524081712629</v>
+        <v>160.0255980868267</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>160.0954315565094</v>
+        <v>160.0571150331307</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>160.2793151228065</v>
+        <v>160.2374237732238</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>160.5492184071646</v>
+        <v>160.4951187177249</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>160.6953333776956</v>
+        <v>160.6111488028721</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>161.1282047571331</v>
+        <v>161.0237663705902</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>161.4672598314876</v>
+        <v>161.3414673197086</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>161.6717640778646</v>
+        <v>161.5293651599008</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>161.79428390333</v>
+        <v>161.6371730329474</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>161.6276923827647</v>
+        <v>161.4710562695673</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>160.8312863569165</v>
+        <v>160.6884429235185</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>159.5593813148583</v>
+        <v>159.4565074418933</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>157.4978855662478</v>
+        <v>157.5417562813258</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>157.6337683341818</v>
+        <v>157.6674221351991</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B112"/>
+  <dimension ref="A1:B113"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.3328964715188</v>
+        <v>139.3374379143773</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.5139659363865</v>
+        <v>142.5206012981496</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.7964379231074</v>
+        <v>143.8036146979781</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.4759282687261</v>
+        <v>144.4832897349084</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.4030673958825</v>
+        <v>144.4105548707055</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.3253847026893</v>
+        <v>144.332978239251</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.2820554799655</v>
+        <v>144.2896911328504</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.3213929831648</v>
+        <v>144.3290150041977</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>144.9915806907236</v>
+        <v>144.9992116724504</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0362434381989</v>
+        <v>148.0361228057737</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4314089356502</v>
+        <v>148.4313821800814</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535322625548</v>
+        <v>148.8535301725755</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9177757210127</v>
+        <v>148.9168872069349</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2929605060071</v>
+        <v>149.2926883355257</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4131950494775</v>
+        <v>150.4143916359128</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.8760210620325</v>
+        <v>151.8791575906969</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.265937412619</v>
+        <v>152.2692725982086</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.5953012410795</v>
+        <v>152.5985213143143</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.1890163709895</v>
+        <v>153.1910690178105</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4115468280238</v>
+        <v>152.4120612901897</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.9337161047815</v>
+        <v>152.9387067090216</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.7252267610106</v>
+        <v>152.7320906482028</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.7565344136305</v>
+        <v>152.7655053935032</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.4544406143125</v>
+        <v>154.4653255617857</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.4114966038729</v>
+        <v>155.4223188159231</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.4059400745825</v>
+        <v>156.4177661280954</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>158.0676046971429</v>
+        <v>158.0805705916407</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.6722190117821</v>
+        <v>159.683064172084</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.4920838934225</v>
+        <v>161.4991494812741</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.8838267734349</v>
+        <v>159.8796532759435</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.6136947217288</v>
+        <v>159.6116074531058</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.148778075752</v>
+        <v>159.1362060827794</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.380037985358</v>
+        <v>157.3637482761816</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.9109981565594</v>
+        <v>157.8954207396659</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.2304684073571</v>
+        <v>158.2161719354814</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.2779075383756</v>
+        <v>158.2636677358802</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.5204825575525</v>
+        <v>159.5070965182089</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.4019808285621</v>
+        <v>158.3962323923233</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7453008622533</v>
+        <v>155.7504924275786</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.8911793840203</v>
+        <v>155.8967239996835</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6735603520376</v>
+        <v>156.6758480962146</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.3768577665755</v>
+        <v>156.3904001761082</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.1475138580458</v>
+        <v>156.161796645519</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>155.9886210237406</v>
+        <v>156.0041245319609</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.2138342642595</v>
+        <v>157.2230262097049</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6454938677388</v>
+        <v>158.6430819070356</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1332775945567</v>
+        <v>159.1294430609564</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.7184485817306</v>
+        <v>159.7132439792765</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.6019282412638</v>
+        <v>159.6010375132894</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1724621103818</v>
+        <v>160.170999012808</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.0714033277674</v>
+        <v>160.0751157940385</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.870533701823</v>
+        <v>159.8775187569452</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.3455579379532</v>
+        <v>160.3514891710877</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.0712535979654</v>
+        <v>161.080026776323</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.7532338747383</v>
+        <v>161.5420374344422</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.5867070977773</v>
+        <v>161.4778793345826</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.4836763184709</v>
+        <v>160.4975535671301</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.0255980868267</v>
+        <v>160.1021177697384</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>160.0571150331307</v>
+        <v>160.1157290455186</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>160.2374237732238</v>
+        <v>160.3028271674399</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>160.4951187177249</v>
+        <v>160.69530356863</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>160.6111488028721</v>
+        <v>160.8991238188074</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>161.0237663705902</v>
+        <v>161.3375518176431</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>161.3414673197086</v>
+        <v>161.6041020212998</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>161.5293651599008</v>
+        <v>161.8941233299211</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>161.6371730329474</v>
+        <v>162.1542379296322</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>161.4710562695673</v>
+        <v>161.2323431662005</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>160.6884429235185</v>
+        <v>160.2197244311746</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>159.4565074418933</v>
+        <v>159.6052086493274</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>157.5417562813258</v>
+        <v>157.7668553137088</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,15 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>157.6674221351991</v>
+        <v>159.6073688422771</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113" s="3">
+        <v>46346</v>
+      </c>
+      <c r="B113">
+        <v>158.8660059446379</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.3374379143773</v>
+        <v>139.3314623175588</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.5206012981496</v>
+        <v>142.5118700775752</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.8036146979781</v>
+        <v>143.7941703411007</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.4832897349084</v>
+        <v>144.4736016010233</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.4105548707055</v>
+        <v>144.4007009489791</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.332978239251</v>
+        <v>144.3229847791858</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.2896911328504</v>
+        <v>144.2796422679853</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.3290150041977</v>
+        <v>144.3189840821589</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>144.9992116724504</v>
+        <v>144.9891681915612</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0361228057737</v>
+        <v>148.0362814928485</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4313821800814</v>
+        <v>148.4314173582411</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535301725755</v>
+        <v>148.8535328984952</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9168872069349</v>
+        <v>148.9180560448983</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2926883355257</v>
+        <v>149.2930467839573</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4143916359128</v>
+        <v>150.4128173950662</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.8791575906969</v>
+        <v>151.8750298790816</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2692725982086</v>
+        <v>152.2648832683945</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.5985213143143</v>
+        <v>152.594283030246</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.1910690178105</v>
+        <v>153.1883672134523</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4120612901897</v>
+        <v>152.4113844301183</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.9387067090216</v>
+        <v>152.9321414970819</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.7320906482028</v>
+        <v>152.7230602461459</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.7655053935032</v>
+        <v>152.7537008447129</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.4653255617857</v>
+        <v>154.4510016850715</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.4223188159231</v>
+        <v>155.4080758086684</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.4177661280954</v>
+        <v>156.4022007020947</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>158.0805705916407</v>
+        <v>158.0635027511204</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.683064172084</v>
+        <v>159.668782777371</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.4991494812741</v>
+        <v>161.4898418125199</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.8796532759435</v>
+        <v>159.8851346609667</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.6116074531058</v>
+        <v>159.6143454137407</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.1362060827794</v>
+        <v>159.152742155421</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.3637482761816</v>
+        <v>157.3851784319057</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.8954207396659</v>
+        <v>157.9159172889755</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.2161719354814</v>
+        <v>158.2349871535964</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.2636677358802</v>
+        <v>158.2824196853003</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.5070965182089</v>
+        <v>159.5247278690827</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.3962323923233</v>
+        <v>158.4038116861186</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7504924275786</v>
+        <v>155.7436667144471</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.8967239996835</v>
+        <v>155.8894343015884</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6758480962146</v>
+        <v>156.6728456364706</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.3904001761082</v>
+        <v>156.3725753674697</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.161796645519</v>
+        <v>156.1429944450356</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>156.0041245319609</v>
+        <v>155.9837086487832</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.2230262097049</v>
+        <v>157.210919867121</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6430819070356</v>
+        <v>158.6462595164853</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1294430609564</v>
+        <v>159.1344956047723</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.7132439792765</v>
+        <v>159.7201024199125</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.6010375132894</v>
+        <v>159.6022152274824</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.170999012808</v>
+        <v>160.1729332467325</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.0751157940385</v>
+        <v>160.0702348062977</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.8775187569452</v>
+        <v>159.8683263846457</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.3514891710877</v>
+        <v>160.3436838405966</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.080026776323</v>
+        <v>161.0684778668236</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.5420374344422</v>
+        <v>161.7493005667505</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.4778793345826</v>
+        <v>161.5840200105775</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.4975535671301</v>
+        <v>160.4852568192991</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.1021177697384</v>
+        <v>160.0284192113095</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>160.1157290455186</v>
+        <v>160.0449144769182</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>160.3028271674399</v>
+        <v>160.2103786666208</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>160.69530356863</v>
+        <v>160.4654895830405</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>160.8991238188074</v>
+        <v>160.5884462467288</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>161.3375518176431</v>
+        <v>161.00233856548</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>161.6041020212998</v>
+        <v>161.2783352339771</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>161.8941233299211</v>
+        <v>161.4589370051788</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>162.1542379296322</v>
+        <v>161.5622111424029</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>161.2323431662005</v>
+        <v>161.4000101726697</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>160.2197244311746</v>
+        <v>160.6688031003371</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>159.6052086493274</v>
+        <v>159.5025149729654</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>157.7668553137088</v>
+        <v>157.7521618094396</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>159.6073688422771</v>
+        <v>157.5778357493909</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>158.8660059446379</v>
+        <v>156.8343296984752</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.3314623175588</v>
+        <v>139.3358826334763</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.5118700775752</v>
+        <v>142.5183291751752</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.7941703411007</v>
+        <v>143.8011575665396</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.4736016010233</v>
+        <v>144.4807697661775</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.4007009489791</v>
+        <v>144.4079917412968</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.3229847791858</v>
+        <v>144.3303787783537</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.2796422679853</v>
+        <v>144.2870772423715</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.3189840821589</v>
+        <v>144.3264057788103</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>144.9891681915612</v>
+        <v>144.9965997949005</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0362814928485</v>
+        <v>148.0361641397898</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4314173582411</v>
+        <v>148.4313913573099</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535328984952</v>
+        <v>148.8535309013393</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9180560448983</v>
+        <v>148.9171916330787</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2930467839573</v>
+        <v>149.2927813657974</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4128173950662</v>
+        <v>150.4139817299878</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.8750298790816</v>
+        <v>151.8780838173633</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2648832683945</v>
+        <v>152.2681309150229</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.594283030246</v>
+        <v>152.5974192797132</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.1883672134523</v>
+        <v>153.1903665735096</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4113844301183</v>
+        <v>152.4118850698952</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.9321414970819</v>
+        <v>152.9369968562273</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.7230602461459</v>
+        <v>152.7297394488946</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.7537008447129</v>
+        <v>152.7624334856496</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.4510016850715</v>
+        <v>154.461598702111</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.4080758086684</v>
+        <v>155.4186143517086</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.4022007020947</v>
+        <v>156.4137187384617</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>158.0635027511204</v>
+        <v>158.0761342704143</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.668782777371</v>
+        <v>159.679356294266</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.4898418125199</v>
+        <v>161.4967356393883</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.8851346609667</v>
+        <v>159.8810880015803</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.6143454137407</v>
+        <v>159.6123268445729</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.152742155421</v>
+        <v>159.140514810566</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.3851784319057</v>
+        <v>157.3693289151309</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.9159172889755</v>
+        <v>157.9007554765597</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.2349871535964</v>
+        <v>158.2210657553281</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.2824196853003</v>
+        <v>158.2685360410777</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.5247278690827</v>
+        <v>159.5116709371516</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.4038116861186</v>
+        <v>158.3981925998672</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7436667144471</v>
+        <v>155.7487116304065</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.8894343015884</v>
+        <v>155.8948219961264</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6728456364706</v>
+        <v>156.6750604402479</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.3725753674697</v>
+        <v>156.3857655469195</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.1429944450356</v>
+        <v>156.1569102043432</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>155.9837086487832</v>
+        <v>155.9988240770654</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.210919867121</v>
+        <v>157.2198846114583</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6462595164853</v>
+        <v>158.6439057649586</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1344956047723</v>
+        <v>159.130752407452</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.7201024199125</v>
+        <v>159.7150208061231</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.6022152274824</v>
+        <v>159.6013394674413</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1729332467325</v>
+        <v>160.1714951447798</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.0702348062977</v>
+        <v>160.0738423322587</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.8683263846457</v>
+        <v>159.8751274414532</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.3436838405966</v>
+        <v>160.3494585197903</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.0684778668236</v>
+        <v>161.0770251276335</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.7493005667505</v>
+        <v>161.5383267353901</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.5840200105775</v>
+        <v>161.4752274685611</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.4852568192991</v>
+        <v>160.4988499010135</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.0284192113095</v>
+        <v>160.104602731234</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>160.0449144769182</v>
+        <v>160.0757324098171</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>160.2103786666208</v>
+        <v>160.2501586494819</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>160.4654895830405</v>
+        <v>160.6401151829847</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>160.5884462467288</v>
+        <v>160.8666945223046</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>161.00233856548</v>
+        <v>161.3468073525613</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>161.2783352339771</v>
+        <v>161.5503274190967</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>161.4589370051788</v>
+        <v>161.8272036383109</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>161.5622111424029</v>
+        <v>162.0743262428754</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>161.4000101726697</v>
+        <v>161.0824121218853</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>160.6688031003371</v>
+        <v>160.0922471284927</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>159.5025149729654</v>
+        <v>159.4856034629022</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>157.7521618094396</v>
+        <v>157.7726403128951</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>157.5778357493909</v>
+        <v>159.2814394746917</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>156.8343296984752</v>
+        <v>158.2480275050713</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.3358826334763</v>
+        <v>139.3300654079851</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.5183291751752</v>
+        <v>142.5098284349203</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.8011575665396</v>
+        <v>143.7919610894668</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.4807697661775</v>
+        <v>144.4713344468836</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.4079917412968</v>
+        <v>144.3983950548822</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.3303787783537</v>
+        <v>144.3206462856763</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.2870772423715</v>
+        <v>144.2772908364264</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.3264057788103</v>
+        <v>144.3166368524486</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>144.9965997949005</v>
+        <v>144.9868171026904</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0361641397898</v>
+        <v>148.0363185406601</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4313913573099</v>
+        <v>148.4314255497919</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535309013393</v>
+        <v>148.8535335067926</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9171916330787</v>
+        <v>148.9183289676974</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2927813657974</v>
+        <v>149.2931309724977</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4139817299878</v>
+        <v>150.4124496497246</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.8780838173633</v>
+        <v>151.8740641192206</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2681309150229</v>
+        <v>152.2638560776976</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.5974192797132</v>
+        <v>152.5932906468858</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.1903665735096</v>
+        <v>153.1877344777049</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4118850698952</v>
+        <v>152.4112262797547</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.9369968562273</v>
+        <v>152.9306084246675</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.7297394488946</v>
+        <v>152.7209504851691</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.7624334856496</v>
+        <v>152.7509405926808</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.461598702111</v>
+        <v>154.4476513609943</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.4186143517086</v>
+        <v>155.4047423762574</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.4137187384617</v>
+        <v>156.3985562440304</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>158.0761342704143</v>
+        <v>158.0595039305315</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.679356294266</v>
+        <v>159.6654305343299</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.4967356393883</v>
+        <v>161.4876529696589</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.8810880015803</v>
+        <v>159.8864039274628</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.6123268445729</v>
+        <v>159.6149753025206</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.140514810566</v>
+        <v>159.1566004731873</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.3693289151309</v>
+        <v>157.3901836393339</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.9007554765597</v>
+        <v>157.920708595075</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.2210657553281</v>
+        <v>158.2393903714359</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.2685360410777</v>
+        <v>158.2868217086853</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.5116709371516</v>
+        <v>159.5288712704028</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.3981925998672</v>
+        <v>158.4056021680702</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7487116304065</v>
+        <v>155.7420774621906</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.8948219961264</v>
+        <v>155.8877372550734</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6750604402479</v>
+        <v>156.6721530622642</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.3857655469195</v>
+        <v>156.368401518544</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.1569102043432</v>
+        <v>156.13858826024</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>155.9988240770654</v>
+        <v>155.9789162504114</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.2198846114583</v>
+        <v>157.2080757796158</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6439057649586</v>
+        <v>158.6470071123661</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.130752407452</v>
+        <v>159.1356852576011</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.7150208061231</v>
+        <v>159.7217180442422</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.6013394674413</v>
+        <v>159.6024973934711</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1714951447798</v>
+        <v>160.1733963558188</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.0738423322587</v>
+        <v>160.0690984202697</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.8751274414532</v>
+        <v>159.8661757150743</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.3494585197903</v>
+        <v>160.3418579380474</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.0770251276335</v>
+        <v>161.0657718327421</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.5383267353901</v>
+        <v>161.7454655124103</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.4752274685611</v>
+        <v>161.5813927786399</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.4988499010135</v>
+        <v>160.4867798222635</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.104602731234</v>
+        <v>160.0311578048909</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>160.0757324098171</v>
+        <v>160.0112567568793</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>160.2501586494819</v>
+        <v>160.1621668228622</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>160.6401151829847</v>
+        <v>160.4127406406135</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>160.8666945223046</v>
+        <v>160.5353143485634</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>161.3468073525613</v>
+        <v>160.9216846914005</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>161.5503274190967</v>
+        <v>161.1834793616821</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>161.8272036383109</v>
+        <v>161.354463477332</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>162.0743262428754</v>
+        <v>161.4499766062977</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>161.0824121218853</v>
+        <v>161.2866245001244</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>160.0922471284927</v>
+        <v>160.591654780731</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>159.4856034629022</v>
+        <v>159.4650975843971</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>157.7726403128951</v>
+        <v>157.6173367796736</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>159.2814394746917</v>
+        <v>157.3443691955804</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>158.2480275050713</v>
+        <v>156.1861646883575</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.3300654079851</v>
+        <v>139.3343693794124</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.5098284349203</v>
+        <v>142.5161181996885</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.7919610894668</v>
+        <v>143.7987661758469</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.4713344468836</v>
+        <v>144.4783168233726</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.3983950548822</v>
+        <v>144.4054968113472</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.3206462856763</v>
+        <v>144.327848507818</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.2772908364264</v>
+        <v>144.284532938424</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.3166368524486</v>
+        <v>144.3238660172219</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>144.9868171026904</v>
+        <v>144.994057036302</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0363185406601</v>
+        <v>148.0362043351418</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4314255497919</v>
+        <v>148.4314002721514</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535335067926</v>
+        <v>148.8535315973976</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9183289676974</v>
+        <v>148.9174876910594</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2931309724977</v>
+        <v>149.2928720606001</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4124496497246</v>
+        <v>150.4135830184762</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.8740641192206</v>
+        <v>151.8770386844004</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2638560776976</v>
+        <v>152.2670195842753</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.5932906468858</v>
+        <v>152.5963462994364</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.1877344777049</v>
+        <v>153.1896825972388</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4112262797547</v>
+        <v>152.4117136469358</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.9306084246675</v>
+        <v>152.9353339565861</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.7209504851691</v>
+        <v>152.7274523469714</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.7509405926808</v>
+        <v>152.7594442551228</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.4476513609943</v>
+        <v>154.45797170407</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.4047423762574</v>
+        <v>155.4150082326828</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.3985562440304</v>
+        <v>156.4097781056921</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>158.0595039305315</v>
+        <v>158.0718137920733</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.6654305343299</v>
+        <v>159.6757424074638</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.4876529696589</v>
+        <v>161.4943811562651</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.8864039274628</v>
+        <v>159.8824785080839</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.6149753025206</v>
+        <v>159.6130222215831</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.1566004731873</v>
+        <v>159.1447038406261</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.3901836393339</v>
+        <v>157.3747567611551</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.920708595075</v>
+        <v>157.9059460339661</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.2393903714359</v>
+        <v>158.22582955018</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.2868217086853</v>
+        <v>158.2732811122139</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.5288712704028</v>
+        <v>159.5161315656604</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.4056021680702</v>
+        <v>158.4001082627398</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7420774621906</v>
+        <v>155.7469818244949</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.8877372550734</v>
+        <v>155.8929745576858</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6721530622642</v>
+        <v>156.6742982510314</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.368401518544</v>
+        <v>156.3812529920619</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.13858826024</v>
+        <v>156.1521509006853</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>155.9789162504114</v>
+        <v>155.9936579111921</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.2080757796158</v>
+        <v>157.2168215942424</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6470071123661</v>
+        <v>158.6447095123207</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1356852576011</v>
+        <v>159.1320302152819</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.7217180442422</v>
+        <v>159.7167551809739</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.6024973934711</v>
+        <v>159.6016363493119</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1733963558188</v>
+        <v>160.1719827937749</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.0690984202697</v>
+        <v>160.0726053539329</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.8661757150743</v>
+        <v>159.8727999268631</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.3418579380474</v>
+        <v>160.347482154946</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.0657718327421</v>
+        <v>161.0741017349357</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.7454655124103</v>
+        <v>161.5347124304139</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.5813927786399</v>
+        <v>161.4726364850015</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.4867798222635</v>
+        <v>160.5000934194893</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.0311578048909</v>
+        <v>160.1070079086913</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>160.0112567568793</v>
+        <v>160.0221830570792</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>160.1621668228622</v>
+        <v>160.1829335659932</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>160.4127406406135</v>
+        <v>160.5681434592494</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>160.5353143485634</v>
+        <v>160.7976062782067</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>160.9216846914005</v>
+        <v>161.3380590101303</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>161.1834793616821</v>
+        <v>161.4640356563515</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>161.354463477332</v>
+        <v>161.7282393695061</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>161.4499766062977</v>
+        <v>161.9620179585098</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>161.2866245001244</v>
+        <v>160.9062917712016</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>160.591654780731</v>
+        <v>159.9296833484765</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>159.4650975843971</v>
+        <v>159.3216012095365</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>157.6173367796736</v>
+        <v>157.6953427295818</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>157.3443691955804</v>
+        <v>158.9113255714181</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>156.1861646883575</v>
+        <v>157.7231621246471</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.3343693794124</v>
+        <v>139.3287043106415</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.5161181996885</v>
+        <v>142.5078389318296</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.7987661758469</v>
+        <v>143.7898079466581</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.4783168233726</v>
+        <v>144.4691245526999</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.4054968113472</v>
+        <v>144.3961474197947</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.327848507818</v>
+        <v>144.3183668943429</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.284532938424</v>
+        <v>144.2749988437949</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.3238660172219</v>
+        <v>144.3143489566272</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>144.994057036302</v>
+        <v>144.9845251102853</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0362043351418</v>
+        <v>148.0363546210359</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4314002721514</v>
+        <v>148.4314335196405</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535315973976</v>
+        <v>148.853534088919</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9174876910594</v>
+        <v>148.918594778517</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2928720606001</v>
+        <v>149.2932131460088</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4135830184762</v>
+        <v>150.4120914288962</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.8770386844004</v>
+        <v>151.87312281751</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2670195842753</v>
+        <v>152.2628548207458</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.5963462994364</v>
+        <v>152.5923231219067</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.1896825972388</v>
+        <v>153.1871175490725</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4117136469358</v>
+        <v>152.4110722124269</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.9353339565861</v>
+        <v>152.9291152674752</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.7274523469714</v>
+        <v>152.7188952803187</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.7594442551228</v>
+        <v>152.7482508523952</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.45797170407</v>
+        <v>154.4443862669726</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.4150082326828</v>
+        <v>155.4014930100035</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.4097781056921</v>
+        <v>156.3950031426957</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>158.0718137920733</v>
+        <v>158.0556044100063</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.6757424074638</v>
+        <v>159.6621592633139</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.4943811562651</v>
+        <v>161.4855155100605</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.8824785080839</v>
+        <v>159.8876362305838</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.6130222215831</v>
+        <v>159.6155853337453</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.1447038406261</v>
+        <v>159.1603571927161</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.3747567611551</v>
+        <v>157.3950588602144</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.9059460339661</v>
+        <v>157.9253769757462</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.22582955018</v>
+        <v>158.2436824143836</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.2732811122139</v>
+        <v>158.2911175665665</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.5161315656604</v>
+        <v>159.5329163562436</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.4001082627398</v>
+        <v>158.4073535535413</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7469818244949</v>
+        <v>155.7405312895784</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.8929745576858</v>
+        <v>155.8860862994919</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6742982510314</v>
+        <v>156.6714816474981</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.3812529920619</v>
+        <v>156.3643321563337</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.1521509006853</v>
+        <v>156.1342911181853</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>155.9936579111921</v>
+        <v>155.974239509116</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.2168215942424</v>
+        <v>157.205299502048</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6447095123207</v>
+        <v>158.647737279476</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1320302152819</v>
+        <v>159.1368475195054</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.7167551809739</v>
+        <v>159.7232967440087</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.6016363493119</v>
+        <v>159.6027748256143</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1719827937749</v>
+        <v>160.1738515909043</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.0726053539329</v>
+        <v>160.0679928734647</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.8727999268631</v>
+        <v>159.8640795466661</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.347482154946</v>
+        <v>160.3400784023865</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.0741017349357</v>
+        <v>161.0631329195154</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.5347124304139</v>
+        <v>161.7417251048176</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.4726364850015</v>
+        <v>161.5788235025458</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.5000934194893</v>
+        <v>160.4882481176165</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.1070079086913</v>
+        <v>160.0338172815847</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>160.0221830570792</v>
+        <v>159.9646676785028</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>160.1829335659932</v>
+        <v>160.1004703551036</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>160.5681434592494</v>
+        <v>160.3439576098601</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>160.7976062782067</v>
+        <v>160.4667299555686</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>161.3380590101303</v>
+        <v>160.8257197692318</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>161.4640356563515</v>
+        <v>161.0721752893002</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>161.7282393695061</v>
+        <v>161.2320231365966</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>161.9620179585098</v>
+        <v>161.3176797940775</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>160.9062917712016</v>
+        <v>161.150003366523</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>159.9296833484765</v>
+        <v>160.4819711749276</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>159.3216012095365</v>
+        <v>159.2265855772023</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>157.6953427295818</v>
+        <v>157.439880662266</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>158.9113255714181</v>
+        <v>157.062783960738</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>157.7231621246471</v>
+        <v>155.6742991786141</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.3287043106415</v>
+        <v>139.3273776658662</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.5078389318296</v>
+        <v>142.5058995964118</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.7898079466581</v>
+        <v>143.7877088024965</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.4691245526999</v>
+        <v>144.4669697771809</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.3961474197947</v>
+        <v>144.3939558642809</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.3183668943429</v>
+        <v>144.3161443934647</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.2749988437949</v>
+        <v>144.2727640653966</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.3143489566272</v>
+        <v>144.3121181738862</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>144.9845251102853</v>
+        <v>144.9822900152436</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0363546210359</v>
+        <v>148.0363897713501</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4314335196405</v>
+        <v>148.4314412766302</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.853534088919</v>
+        <v>148.853534646252</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.918594778517</v>
+        <v>148.9188537516082</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2932131460088</v>
+        <v>149.2932933754151</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4120914288962</v>
+        <v>150.4117423676501</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.87312281751</v>
+        <v>151.8722050571928</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2628548207458</v>
+        <v>152.2618785285139</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.5923231219067</v>
+        <v>152.5913795340354</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.1871175490725</v>
+        <v>153.1865158431448</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4110722124269</v>
+        <v>152.4109220720158</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.9291152674752</v>
+        <v>152.9276604885172</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.7188952803187</v>
+        <v>152.716892545692</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.7482508523952</v>
+        <v>152.7456289598157</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.4443862669726</v>
+        <v>154.4412031968819</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.4014930100035</v>
+        <v>155.3983245766822</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.3950031426957</v>
+        <v>156.3915380154679</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>158.0556044100063</v>
+        <v>158.0518005502891</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.6621592633139</v>
+        <v>159.658966086787</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.4855155100605</v>
+        <v>161.483427663092</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.8876362305838</v>
+        <v>159.8888331356879</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.6155853337453</v>
+        <v>159.6161763980844</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.1603571927161</v>
+        <v>159.1640162625845</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.3950588602144</v>
+        <v>157.399809079326</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.9253769757462</v>
+        <v>157.9299270853758</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.2436824143836</v>
+        <v>158.2478674209766</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.2911175665665</v>
+        <v>158.2953110308392</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.5329163562436</v>
+        <v>159.5368665558807</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.4073535535413</v>
+        <v>158.4090670705865</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7405312895784</v>
+        <v>155.7390264768968</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.8860862994919</v>
+        <v>155.884479592924</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6714816474981</v>
+        <v>156.6708304661935</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.3643321563337</v>
+        <v>156.3603634170845</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.1342911181853</v>
+        <v>156.1300990363158</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>155.974239509116</v>
+        <v>155.9696743091163</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.205299502048</v>
+        <v>157.2025886511033</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.647737279476</v>
+        <v>158.6484506138403</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1368475195054</v>
+        <v>159.1379833141859</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.7232967440087</v>
+        <v>159.7248397522251</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.6027748256143</v>
+        <v>159.6030476107993</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1738515909043</v>
+        <v>160.1742991050178</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.0679928734647</v>
+        <v>160.066916937927</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.8640795466661</v>
+        <v>159.8620358397393</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.3400784023865</v>
+        <v>160.3383434966063</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.0631329195154</v>
+        <v>161.0605586755456</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.7417251048176</v>
+        <v>161.7380759100369</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.5788235025458</v>
+        <v>161.5763103579255</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.4882481176165</v>
+        <v>160.4896643281651</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.0338172815847</v>
+        <v>160.0364008762868</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>159.9646676785028</v>
+        <v>159.9188605017725</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>160.1004703551036</v>
+        <v>160.0392595010618</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>160.3439576098601</v>
+        <v>160.2735917244012</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>160.4667299555686</v>
+        <v>160.3949940115982</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>160.8257197692318</v>
+        <v>160.7281635231434</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>161.0721752893002</v>
+        <v>160.9597775387562</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>161.2320231365966</v>
+        <v>161.1088176361672</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>161.3176797940775</v>
+        <v>161.1850411792092</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>161.150003366523</v>
+        <v>161.0134108718737</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>160.4819711749276</v>
+        <v>160.3702417065842</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>159.2265855772023</v>
+        <v>159.0070382044549</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>157.439880662266</v>
+        <v>157.2786082467047</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>157.062783960738</v>
+        <v>156.8291821800696</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>155.6742991786141</v>
+        <v>155.4001308113118</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.3273776658662</v>
+        <v>139.326084181962</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.5058995964118</v>
+        <v>142.5040085549601</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.7877088024965</v>
+        <v>143.7856616512825</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.4669697771809</v>
+        <v>144.4648680844431</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.3939558642809</v>
+        <v>144.3918183162297</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.3161443934647</v>
+        <v>144.313976680273</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.2727640653966</v>
+        <v>144.2705843861466</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.3121181738862</v>
+        <v>144.3099423928375</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>144.9822900152436</v>
+        <v>144.9801097261682</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0363897713501</v>
+        <v>148.0364240270779</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4314412766302</v>
+        <v>148.4314488291417</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.853534646252</v>
+        <v>148.8535351800818</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9188537516082</v>
+        <v>148.9191061473084</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2932933754151</v>
+        <v>149.293371728381</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4117423676501</v>
+        <v>150.4114021194459</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.8722050571928</v>
+        <v>151.871309966727</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2618785285139</v>
+        <v>152.2609262796176</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.5913795340354</v>
+        <v>152.5904590069088</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.1865158431448</v>
+        <v>153.185928803939</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4109220720158</v>
+        <v>152.4107757102624</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.9276604885172</v>
+        <v>152.9262426286286</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.716892545692</v>
+        <v>152.7149403002291</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.7456289598157</v>
+        <v>152.7430723832517</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.4412031968819</v>
+        <v>154.4380991031543</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.3983245766822</v>
+        <v>155.3952340965041</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.3915380154679</v>
+        <v>156.3881576441912</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>158.0518005502891</v>
+        <v>158.0480888871037</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.658966086787</v>
+        <v>159.6558482608706</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.483427663092</v>
+        <v>161.4813877376167</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.8888331356879</v>
+        <v>159.8899961220994</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.6161763980844</v>
+        <v>159.6167493350669</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.1640162625845</v>
+        <v>159.1675814299546</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.399809079326</v>
+        <v>157.4044390304622</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.9299270853758</v>
+        <v>157.934363347101</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.2478674209766</v>
+        <v>158.2519493278224</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.2953110308392</v>
+        <v>158.2994056979898</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.5368665558807</v>
+        <v>159.5407251424389</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.4090670705865</v>
+        <v>158.4107438985394</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7390264768968</v>
+        <v>155.737561394364</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.884479592924</v>
+        <v>155.8829153898069</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6708304661935</v>
+        <v>156.670198644451</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.3603634170845</v>
+        <v>156.3564916246699</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.1300990363158</v>
+        <v>156.1260082228974</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>155.9696743091163</v>
+        <v>155.9652167265628</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.2025886511033</v>
+        <v>157.1999409531989</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6484506138403</v>
+        <v>158.6491476849502</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1379833141859</v>
+        <v>159.1390935248768</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.7248397522251</v>
+        <v>159.7263482485932</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.6030476107993</v>
+        <v>159.6033158360892</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1742991050178</v>
+        <v>160.1747390505212</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.066916937927</v>
+        <v>160.0658694495587</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.8620358397393</v>
+        <v>159.8600426548378</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.3383434966063</v>
+        <v>160.3366515690514</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.0605586755456</v>
+        <v>161.0580467664479</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.7380759100369</v>
+        <v>161.7345146569401</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.5763103579255</v>
+        <v>161.5738515921152</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.4896643281651</v>
+        <v>160.4910309211552</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.0364008762868</v>
+        <v>160.0389116560029</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>159.9188605017725</v>
+        <v>159.8756965471156</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>160.0392595010618</v>
+        <v>159.9796108542219</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>160.2735917244012</v>
+        <v>160.2066758410106</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>160.3949940115982</v>
+        <v>160.3312996055245</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>160.7281635231434</v>
+        <v>160.6442324534562</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>160.9597775387562</v>
+        <v>160.8674854229901</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>161.1088176361672</v>
+        <v>161.0123941959981</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>161.1850411792092</v>
+        <v>161.0864329941409</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>161.0134108718737</v>
+        <v>160.921087179631</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>160.3702417065842</v>
+        <v>160.1958464526754</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>159.0070382044549</v>
+        <v>158.8638605568332</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>157.2786082467047</v>
+        <v>157.2123382336959</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>156.8291821800696</v>
+        <v>156.7540616736771</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>155.4001308113118</v>
+        <v>155.467823058871</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.326084181962</v>
+        <v>139.3248226310032</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.5040085549601</v>
+        <v>142.5021640259179</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.7856616512825</v>
+        <v>143.7836645854096</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.4648680844431</v>
+        <v>144.4628175376064</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.3918183162297</v>
+        <v>144.3897328043316</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.313976680273</v>
+        <v>144.3118617543261</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.2705843861466</v>
+        <v>144.2684577939041</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.3099423928375</v>
+        <v>144.3078196048589</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>144.9801097261682</v>
+        <v>144.9779822528576</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0364240270779</v>
+        <v>148.0364574219145</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4314488291417</v>
+        <v>148.431456185123</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535351800818</v>
+        <v>148.8535356916182</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9191061473084</v>
+        <v>148.919352212912</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.293371728381</v>
+        <v>149.2934482694945</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4114021194459</v>
+        <v>150.4110703549904</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.871309966727</v>
+        <v>151.870436717034</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2609262796176</v>
+        <v>152.2599971974242</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.5904590069088</v>
+        <v>152.5895607063733</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.185928803939</v>
+        <v>153.185355902193</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4107757102624</v>
+        <v>152.4106329862781</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.9262426286286</v>
+        <v>152.9248603016089</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.7149403002291</v>
+        <v>152.7130366612163</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.7430723832517</v>
+        <v>152.7405787152551</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.4380991031543</v>
+        <v>154.4350710871121</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.3952340965041</v>
+        <v>155.3922187338577</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.3881576441912</v>
+        <v>156.3848589653309</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>158.0480888871037</v>
+        <v>158.0444661208064</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.6558482608706</v>
+        <v>159.6528031677429</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.4813877376167</v>
+        <v>161.4793941176432</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.8899961220994</v>
+        <v>159.891126588879</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.6167493350669</v>
+        <v>159.6173049366315</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.1675814299546</v>
+        <v>159.1710562532204</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.4044390304622</v>
+        <v>157.40895321199</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.934363347101</v>
+        <v>157.9386899669468</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.2519493278224</v>
+        <v>158.255931881707</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.2994056979898</v>
+        <v>158.303404999101</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.5407251424389</v>
+        <v>159.5444952415818</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.4107438985394</v>
+        <v>158.412385170249</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.737561394364</v>
+        <v>155.7361344963501</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.8829153898069</v>
+        <v>155.8813920347447</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.670198644451</v>
+        <v>156.6695853569011</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.3564916246699</v>
+        <v>156.3527132793718</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.1260082228974</v>
+        <v>156.1220150657721</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>155.9652167265628</v>
+        <v>155.960863018545</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.1999409531989</v>
+        <v>157.1973542382814</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6491476849502</v>
+        <v>158.6498290372019</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1390935248768</v>
+        <v>159.1401789964982</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.7263482485932</v>
+        <v>159.727823362289</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.6033158360892</v>
+        <v>159.6035795884424</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1747390505212</v>
+        <v>160.1751715787394</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.0658694495587</v>
+        <v>160.064849304049</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.8600426548378</v>
+        <v>159.8580981466673</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.3366515690514</v>
+        <v>160.3350010482599</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.0580467664479</v>
+        <v>161.0555949681747</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.7345146569401</v>
+        <v>161.7310382277521</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.5738515921152</v>
+        <v>161.5714455209624</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.4910309211552</v>
+        <v>160.4923502191871</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.0389116560029</v>
+        <v>160.0413525302679</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>159.8756965471156</v>
+        <v>159.8473690763474</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>159.9796108542219</v>
+        <v>159.9381521507565</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>160.2066758410106</v>
+        <v>160.1616971913298</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>160.3312996055245</v>
+        <v>160.2800946850435</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>160.6442324534562</v>
+        <v>160.5845094577823</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>160.8674854229901</v>
+        <v>160.8017872488093</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>161.0123941959981</v>
+        <v>160.9440412746357</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>161.0864329941409</v>
+        <v>161.0174117436482</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>160.921087179631</v>
+        <v>160.8603202567384</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>160.1958464526754</v>
+        <v>160.0610935472991</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>158.8638605568332</v>
+        <v>158.7664178638037</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>157.2123382336959</v>
+        <v>157.1924261750218</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>156.7540616736771</v>
+        <v>156.7482522089206</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>155.467823058871</v>
+        <v>155.6232286354773</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B113"/>
+  <dimension ref="A1:B114"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.3248226310032</v>
+        <v>139.3300654079851</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.5021640259179</v>
+        <v>142.5098284349203</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.7836645854096</v>
+        <v>143.7919610894668</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.4628175376064</v>
+        <v>144.4713344468836</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.3897328043316</v>
+        <v>144.3983950548822</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.3118617543261</v>
+        <v>144.3206462856763</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.2684577939041</v>
+        <v>144.2772908364264</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.3078196048589</v>
+        <v>144.3166368524486</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>144.9779822528576</v>
+        <v>144.9868171026904</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0364574219145</v>
+        <v>148.0363185406601</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.431456185123</v>
+        <v>148.4314255497919</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535356916182</v>
+        <v>148.8535335067926</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.919352212912</v>
+        <v>148.9183289676974</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2934482694945</v>
+        <v>149.2931309724977</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4110703549904</v>
+        <v>150.4124496497246</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.870436717034</v>
+        <v>151.8740641192206</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2599971974242</v>
+        <v>152.2638560776976</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.5895607063733</v>
+        <v>152.5932906468858</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.185355902193</v>
+        <v>153.1877344777049</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4106329862781</v>
+        <v>152.4112262797547</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.9248603016089</v>
+        <v>152.9306084246675</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.7130366612163</v>
+        <v>152.7209504851691</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.7405787152551</v>
+        <v>152.7509405926808</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.4350710871121</v>
+        <v>154.4476513609943</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.3922187338577</v>
+        <v>155.4047423762574</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.3848589653309</v>
+        <v>156.3985562440304</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>158.0444661208064</v>
+        <v>158.0595039305315</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.6528031677429</v>
+        <v>159.6654305343299</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.4793941176432</v>
+        <v>161.4876529696589</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.891126588879</v>
+        <v>159.8864039274628</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.6173049366315</v>
+        <v>159.6149753025206</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.1710562532204</v>
+        <v>159.1566004731873</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.40895321199</v>
+        <v>157.3901836393339</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.9386899669468</v>
+        <v>157.920708595075</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.255931881707</v>
+        <v>158.2393903714359</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.303404999101</v>
+        <v>158.2868217086853</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.5444952415818</v>
+        <v>159.5288712704028</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.412385170249</v>
+        <v>158.4056021680702</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7361344963501</v>
+        <v>155.7420774621906</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.8813920347447</v>
+        <v>155.8877372550734</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6695853569011</v>
+        <v>156.6721530622642</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.3527132793718</v>
+        <v>156.368401518544</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.1220150657721</v>
+        <v>156.13858826024</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>155.960863018545</v>
+        <v>155.9789162504114</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.1973542382814</v>
+        <v>157.2080757796158</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6498290372019</v>
+        <v>158.6470071123661</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1401789964982</v>
+        <v>159.1356852576011</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.727823362289</v>
+        <v>159.7217180442422</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.6035795884424</v>
+        <v>159.6024973934711</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1751715787394</v>
+        <v>160.1733963558188</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.064849304049</v>
+        <v>160.0690984202697</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.8580981466673</v>
+        <v>159.8661757150743</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.3350010482599</v>
+        <v>160.3418579380474</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.0555949681747</v>
+        <v>161.0657718327421</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.7310382277521</v>
+        <v>161.5244119859503</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.5714455209624</v>
+        <v>161.4652093991232</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.4923502191871</v>
+        <v>160.5035339549346</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.0413525302679</v>
+        <v>160.1137796783553</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>159.8473690763474</v>
+        <v>159.9375964830153</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>159.9381521507565</v>
+        <v>160.0441570127407</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>160.1616971913298</v>
+        <v>160.4203001539187</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>160.2800946850435</v>
+        <v>160.6782348649582</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>160.5845094577823</v>
+        <v>161.2072967085607</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>160.8017872488093</v>
+        <v>161.3656379421664</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>160.9440412746357</v>
+        <v>161.6173279719683</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>161.0174117436482</v>
+        <v>161.8423687432839</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>160.8603202567384</v>
+        <v>160.7638703844199</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>160.0610935472991</v>
+        <v>159.9294566898047</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>158.7664178638037</v>
+        <v>159.4865935663331</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>157.1924261750218</v>
+        <v>158.2850779074161</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>156.7482522089206</v>
+        <v>159.4126046465085</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,15 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>155.6232286354773</v>
+        <v>159.181850762589</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114" s="3">
+        <v>46353</v>
+      </c>
+      <c r="B114">
+        <v>160.927100762589</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.3300654079851</v>
+        <v>139.3235918449471</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.5098284349203</v>
+        <v>142.5003643142825</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.7919610894668</v>
+        <v>143.7817157894413</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.4713344468836</v>
+        <v>144.4608162928507</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.3983950548822</v>
+        <v>144.3876974520249</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.3206462856763</v>
+        <v>144.3097977113623</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.2772908364264</v>
+        <v>144.2663823732868</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.3166368524486</v>
+        <v>144.30574789792</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>144.9868171026904</v>
+        <v>144.9759057002619</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0363185406601</v>
+        <v>148.0364899878847</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4314255497919</v>
+        <v>148.4314633521172</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535335067926</v>
+        <v>148.853536181996</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9183289676974</v>
+        <v>148.9195921834763</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2931309724977</v>
+        <v>149.2935230604377</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4124496497246</v>
+        <v>150.4107467611792</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.8740641192206</v>
+        <v>151.8695845189461</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2638560776976</v>
+        <v>152.2590904473703</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.5932906468858</v>
+        <v>152.5886838379774</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.1877344777049</v>
+        <v>153.1847966337816</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4112262797547</v>
+        <v>152.4104937660933</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.9306084246675</v>
+        <v>152.9235121897225</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.7209504851691</v>
+        <v>152.7111798382668</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.7509405926808</v>
+        <v>152.7381456651011</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.4476513609943</v>
+        <v>154.432116389999</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.4047423762574</v>
+        <v>155.3892757887136</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.3985562440304</v>
+        <v>156.3816390608252</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>158.0595039305315</v>
+        <v>158.0409291067599</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.6654305343299</v>
+        <v>159.6498283085447</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.4876529696589</v>
+        <v>161.4774452582527</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.8864039274628</v>
+        <v>159.892225860139</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.6149753025206</v>
+        <v>159.6178439503896</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.1566004731873</v>
+        <v>159.174444113716</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.3901836393339</v>
+        <v>157.4133559012701</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.920708595075</v>
+        <v>157.9429109469426</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.2393903714359</v>
+        <v>158.2598186508462</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.2868217086853</v>
+        <v>158.3073122091837</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.5288712704028</v>
+        <v>159.5481798396379</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.4056021680702</v>
+        <v>158.4139919742078</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7420774621906</v>
+        <v>155.7347443160362</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.8877372550734</v>
+        <v>155.8799079567868</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6721530622642</v>
+        <v>156.668989823436</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.368401518544</v>
+        <v>156.3490250474549</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.13858826024</v>
+        <v>156.1181161218956</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>155.9789162504114</v>
+        <v>155.9566096128411</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.2080757796158</v>
+        <v>157.1948264340375</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6470071123661</v>
+        <v>158.6504951912435</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1356852576011</v>
+        <v>159.1412405376756</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.7217180442422</v>
+        <v>159.7292661745797</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.6024973934711</v>
+        <v>159.6038389544705</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1733963558188</v>
+        <v>160.1755968396463</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.0690984202697</v>
+        <v>160.0638554531097</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.8661757150743</v>
+        <v>159.8562005584661</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.3418579380474</v>
+        <v>160.3333904381737</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.0657718327421</v>
+        <v>161.0532011606128</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.5244119859503</v>
+        <v>161.7276436492405</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.4652093991232</v>
+        <v>161.5690905257726</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.5035339549346</v>
+        <v>160.4936244102522</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.1137796783553</v>
+        <v>160.0437262608206</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>159.9375964830153</v>
+        <v>159.8505537637925</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>160.0441570127407</v>
+        <v>159.9157644682031</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>160.4203001539187</v>
+        <v>160.144922273563</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>160.6782348649582</v>
+        <v>160.2641224268563</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>161.2072967085607</v>
+        <v>160.6010983779279</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>161.3656379421664</v>
+        <v>160.8465369307027</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>161.6173279719683</v>
+        <v>161.0167639025863</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>161.8423687432839</v>
+        <v>161.1221333338084</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>160.7638703844199</v>
+        <v>161.0122169919619</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>159.9294566898047</v>
+        <v>160.313945446306</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>159.4865935663331</v>
+        <v>159.2397668734828</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>158.2850779074161</v>
+        <v>157.8991522489289</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>159.4126046465085</v>
+        <v>157.840099054384</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>159.181850762589</v>
+        <v>157.8047235630532</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>160.927100762589</v>
+        <v>159.5499735630532</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.3235918449471</v>
+        <v>139.3287043106415</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.5003643142825</v>
+        <v>142.5078389318296</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.7817157894413</v>
+        <v>143.7898079466581</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.4608162928507</v>
+        <v>144.4691245526999</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.3876974520249</v>
+        <v>144.3961474197947</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.3097977113623</v>
+        <v>144.3183668943429</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.2663823732868</v>
+        <v>144.2749988437949</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.30574789792</v>
+        <v>144.3143489566272</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>144.9759057002619</v>
+        <v>144.9845251102853</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0364899878847</v>
+        <v>148.0363546210359</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4314633521172</v>
+        <v>148.4314335196405</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.853536181996</v>
+        <v>148.853534088919</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9195921834763</v>
+        <v>148.918594778517</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2935230604377</v>
+        <v>149.2932131460088</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4107467611792</v>
+        <v>150.4120914288962</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.8695845189461</v>
+        <v>151.87312281751</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2590904473703</v>
+        <v>152.2628548207458</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.5886838379774</v>
+        <v>152.5923231219067</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.1847966337816</v>
+        <v>153.1871175490725</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4104937660933</v>
+        <v>152.4110722124269</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.9235121897225</v>
+        <v>152.9291152674752</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.7111798382668</v>
+        <v>152.7188952803187</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.7381456651011</v>
+        <v>152.7482508523952</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.432116389999</v>
+        <v>154.4443862669726</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.3892757887136</v>
+        <v>155.4014930100035</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.3816390608252</v>
+        <v>156.3950031426957</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>158.0409291067599</v>
+        <v>158.0556044100063</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.6498283085447</v>
+        <v>159.6621592633139</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.4774452582527</v>
+        <v>161.4855155100605</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.892225860139</v>
+        <v>159.8876362305838</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.6178439503896</v>
+        <v>159.6155853337453</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.174444113716</v>
+        <v>159.1603571927161</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.4133559012701</v>
+        <v>157.3950588602144</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.9429109469426</v>
+        <v>157.9253769757462</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.2598186508462</v>
+        <v>158.2436824143836</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.3073122091837</v>
+        <v>158.2911175665665</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.5481798396379</v>
+        <v>159.5329163562436</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.4139919742078</v>
+        <v>158.4073535535413</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7347443160362</v>
+        <v>155.7405312895784</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.8799079567868</v>
+        <v>155.8860862994919</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.668989823436</v>
+        <v>156.6714816474981</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.3490250474549</v>
+        <v>156.3643321563337</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.1181161218956</v>
+        <v>156.1342911181853</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>155.9566096128411</v>
+        <v>155.974239509116</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.1948264340375</v>
+        <v>157.205299502048</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6504951912435</v>
+        <v>158.647737279476</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1412405376756</v>
+        <v>159.1368475195054</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.7292661745797</v>
+        <v>159.7232967440087</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.6038389544705</v>
+        <v>159.6027748256143</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1755968396463</v>
+        <v>160.1738515909043</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.0638554531097</v>
+        <v>160.0679928734647</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.8562005584661</v>
+        <v>159.8640795466661</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.3333904381737</v>
+        <v>160.3400784023865</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.0532011606128</v>
+        <v>161.0631329195154</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.7276436492405</v>
+        <v>161.5211482369423</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.5690905257726</v>
+        <v>161.4628429001149</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.4936244102522</v>
+        <v>160.5045922475155</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.0437262608206</v>
+        <v>160.1158996912567</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>159.8505537637925</v>
+        <v>159.9405237649204</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>159.9157644682031</v>
+        <v>160.0091967658833</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>160.144922273563</v>
+        <v>160.3864350837569</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>160.2641224268563</v>
+        <v>160.6375500823564</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>160.6010983779279</v>
+        <v>161.1917124399486</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>160.8465369307027</v>
+        <v>161.3820187463211</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>161.0167639025863</v>
+        <v>161.6458547837026</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>161.1221333338084</v>
+        <v>161.8860743973643</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>161.0122169919619</v>
+        <v>160.88509672609</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>160.313945446306</v>
+        <v>160.1428880922556</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>159.2397668734828</v>
+        <v>159.8322958976536</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>157.8991522489289</v>
+        <v>158.8418546092803</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>157.840099054384</v>
+        <v>160.1352201793495</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>157.8047235630532</v>
+        <v>160.3855453004008</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>159.5499735630532</v>
+        <v>162.1307953004008</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.3287043106415</v>
+        <v>139.3223907120286</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.5078389318296</v>
+        <v>142.4986078064126</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.7898079466581</v>
+        <v>143.7798135346123</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.4691245526999</v>
+        <v>144.4588625938956</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.3961474197947</v>
+        <v>144.3857104718734</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.3183668943429</v>
+        <v>144.3077827375909</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.2749988437949</v>
+        <v>144.2643562999262</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.3143489566272</v>
+        <v>144.3037254508463</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>144.9845251102853</v>
+        <v>144.9738782628671</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0363546210359</v>
+        <v>148.036521755446</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4314335196405</v>
+        <v>148.4314703372871</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.853534088919</v>
+        <v>148.8535366522806</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.918594778517</v>
+        <v>148.9198262825694</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2932131460088</v>
+        <v>149.2935961601473</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4120914288962</v>
+        <v>150.4104310401146</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.87312281751</v>
+        <v>151.8687526208344</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2628548207458</v>
+        <v>152.2582052344704</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.5923231219067</v>
+        <v>152.58782764464</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.1871175490725</v>
+        <v>153.184250518243</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4110722124269</v>
+        <v>152.4103579222373</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.9291152674752</v>
+        <v>152.9221970395275</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.7188952803187</v>
+        <v>152.7093681277375</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.7482508523952</v>
+        <v>152.7357710518079</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.4443862669726</v>
+        <v>154.4292323846509</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.4014930100035</v>
+        <v>155.3864026886346</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.3950031426957</v>
+        <v>156.378495149576</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>158.0556044100063</v>
+        <v>158.037474846373</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.6621592633139</v>
+        <v>159.646921296755</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.4855155100605</v>
+        <v>161.4755396817836</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.8876362305838</v>
+        <v>159.8932951899454</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.6155853337453</v>
+        <v>159.6183670826269</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.1603571927161</v>
+        <v>159.1777482265646</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.3950588602144</v>
+        <v>157.4176511680312</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.9253769757462</v>
+        <v>157.9470300973019</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.2436824143836</v>
+        <v>158.2636130353505</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.2911175665665</v>
+        <v>158.3111304558906</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.5329163562436</v>
+        <v>159.5517817911989</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.4073535535413</v>
+        <v>158.4155653565762</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7405312895784</v>
+        <v>155.7333894604741</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.8860862994919</v>
+        <v>155.8784616641342</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6714816474981</v>
+        <v>156.6684113061999</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.3643321563337</v>
+        <v>156.3454237514692</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.1342911181853</v>
+        <v>156.114308107594</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>155.974239509116</v>
+        <v>155.952453098352</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.205299502048</v>
+        <v>157.1923555604861</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.647737279476</v>
+        <v>158.6511466452383</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1368475195054</v>
+        <v>159.1422789226356</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.7232967440087</v>
+        <v>159.7306777212858</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.6027748256143</v>
+        <v>159.6040940202312</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1738515909043</v>
+        <v>160.1760149816</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.0679928734647</v>
+        <v>160.0628869009888</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.8640795466661</v>
+        <v>159.8543482167735</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.3400784023865</v>
+        <v>160.3318183136858</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.0631329195154</v>
+        <v>161.0508633216197</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.5211482369423</v>
+        <v>161.7243280845018</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.4628429001149</v>
+        <v>161.5667850503956</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.5045922475155</v>
+        <v>160.4948555569689</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.1158996912567</v>
+        <v>160.0460354705944</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>159.9405237649204</v>
+        <v>159.8536593233922</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>160.0091967658833</v>
+        <v>159.8891149285019</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>160.3864350837569</v>
+        <v>160.1231705321524</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>160.6375500823564</v>
+        <v>160.2413004180097</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>161.1917124399486</v>
+        <v>160.6118650769167</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>161.3820187463211</v>
+        <v>160.8813460331113</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>161.6458547837026</v>
+        <v>161.0753585590338</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>161.8860743973643</v>
+        <v>161.2083476988277</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>160.88509672609</v>
+        <v>161.1399040843279</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>160.1428880922556</v>
+        <v>160.5297350903192</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>159.8322958976536</v>
+        <v>159.6455524429905</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>158.8418546092803</v>
+        <v>158.4999559650939</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>160.1352201793495</v>
+        <v>158.7268704397864</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>160.3855453004008</v>
+        <v>159.3589877858241</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>162.1307953004008</v>
+        <v>161.1042377858242</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.3223907120286</v>
+        <v>139.3212181734108</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.4986078064126</v>
+        <v>142.4968929652051</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.7798135346123</v>
+        <v>143.7779561737184</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.4588625938956</v>
+        <v>144.4569547668684</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.3857104718734</v>
+        <v>144.3837701603394</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.3077827375909</v>
+        <v>144.3058151043837</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.2643562999262</v>
+        <v>144.2623778351269</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.3037254508463</v>
+        <v>144.3017505279886</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>144.9738782628671</v>
+        <v>144.9718982194719</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.036521755446</v>
+        <v>148.0365527535824</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4314703372871</v>
+        <v>148.4314771474395</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535366522806</v>
+        <v>148.8535371034729</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9198262825694</v>
+        <v>148.9200547229628</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2935961601473</v>
+        <v>149.293667624964</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4104310401146</v>
+        <v>150.410122908194</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.8687526208344</v>
+        <v>151.8679403064055</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2582052344704</v>
+        <v>152.2573408009998</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.58782764464</v>
+        <v>152.5869914044819</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.184250518243</v>
+        <v>153.1837170974077</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4103579222373</v>
+        <v>152.4102253333489</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.9221970395275</v>
+        <v>152.9209136580059</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.7093681277375</v>
+        <v>152.7075999075452</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.7357710518079</v>
+        <v>152.7334527976513</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.4292323846509</v>
+        <v>154.4264165677541</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.3864026886346</v>
+        <v>155.3835969813431</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.378495149576</v>
+        <v>156.3754245795289</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>158.037474846373</v>
+        <v>158.0341004787522</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.646921296755</v>
+        <v>159.6440798519996</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.4755396817836</v>
+        <v>161.4736759742565</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.8932951899454</v>
+        <v>159.8943357668435</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.6183670826269</v>
+        <v>159.6188750010679</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.1777482265646</v>
+        <v>159.180971650742</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.4176511680312</v>
+        <v>157.4218428867878</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.9470300973019</v>
+        <v>157.9510510477426</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.2636130353505</v>
+        <v>158.2673182769654</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.3111304558906</v>
+        <v>158.3148627276569</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.5517817911989</v>
+        <v>159.5553038262345</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.4155653565762</v>
+        <v>158.4171063231081</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7333894604741</v>
+        <v>155.7320686060104</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.8784616641342</v>
+        <v>155.8770517392383</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6684113061999</v>
+        <v>156.667849106812</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.3454237514692</v>
+        <v>156.341906361223</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.114308107594</v>
+        <v>156.1105878894843</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>155.952453098352</v>
+        <v>155.9483902161677</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.1923555604861</v>
+        <v>157.1899397249233</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6511466452383</v>
+        <v>158.6517838760491</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1422789226356</v>
+        <v>159.1432948929869</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.7306777212858</v>
+        <v>159.7320589950955</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.6040940202312</v>
+        <v>159.6043448710528</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1760149816</v>
+        <v>160.176426151119</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.0628869009888</v>
+        <v>160.0619427012415</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.8543482167735</v>
+        <v>159.8525395265635</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.3318183136858</v>
+        <v>160.330283316499</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.0508633216197</v>
+        <v>161.0485795214628</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.7243280845018</v>
+        <v>161.7210888252952</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.5667850503956</v>
+        <v>161.5645275984454</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.4948555569689</v>
+        <v>160.4960456050907</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.0460354705944</v>
+        <v>160.0482826520781</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>159.8536593233922</v>
+        <v>159.8566885692856</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>159.8891149285019</v>
+        <v>159.8763613878779</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>160.1231705321524</v>
+        <v>160.1155369002469</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>160.2413004180097</v>
+        <v>160.2360691965432</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>160.6118650769167</v>
+        <v>160.6397353064366</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>160.8813460331113</v>
+        <v>160.9347049167226</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>161.0753585590338</v>
+        <v>161.1544740997881</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>161.2083476988277</v>
+        <v>161.317095270536</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>161.1399040843279</v>
+        <v>161.2919731614362</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>160.5297350903192</v>
+        <v>160.770739848261</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>159.6455524429905</v>
+        <v>160.0725663499486</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>158.4999559650939</v>
+        <v>159.1106178240478</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>158.7268704397864</v>
+        <v>159.5919669190476</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>159.3589877858241</v>
+        <v>160.7309405025269</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>161.1042377858242</v>
+        <v>170.5304481461492</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.3212181734108</v>
+        <v>139.3200732200727</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.4968929652051</v>
+        <v>142.4952183256107</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.7779561737184</v>
+        <v>143.7761421363635</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.4569547668684</v>
+        <v>144.4550912155279</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.3837701603394</v>
+        <v>144.3818748929196</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.3058151043837</v>
+        <v>144.3038931633369</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.2623778351269</v>
+        <v>144.2604453208981</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.3017505279886</v>
+        <v>144.2998214742621</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>144.9718982194719</v>
+        <v>144.9699639283255</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0365527535824</v>
+        <v>148.0365830098929</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4314771474395</v>
+        <v>148.4314837890468</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535371034729</v>
+        <v>148.8535375365141</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9200547229628</v>
+        <v>148.9202777072754</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.293667624964</v>
+        <v>149.2937375087725</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.410122908194</v>
+        <v>150.409822095264</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.8679403064055</v>
+        <v>151.8671468926503</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2573408009998</v>
+        <v>152.2564964243391</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.5869914044819</v>
+        <v>152.5861744288047</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.1837170974077</v>
+        <v>153.183195934122</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4102253333489</v>
+        <v>152.4100958838148</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.9209136580059</v>
+        <v>152.9196609089695</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.7075999075452</v>
+        <v>152.7058736323498</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.7334527976513</v>
+        <v>152.731188922132</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.4264165677541</v>
+        <v>154.4236665526426</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.3835969813431</v>
+        <v>155.3808563278007</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.3754245795289</v>
+        <v>156.372424820295</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>158.0341004787522</v>
+        <v>158.030803272916</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.6440798519996</v>
+        <v>159.6413017942616</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.4736759742565</v>
+        <v>161.4718527820197</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.8943357668435</v>
+        <v>159.8953487180396</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.6188750010679</v>
+        <v>159.6193683374245</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.180971650742</v>
+        <v>159.1841172984188</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.4218428867878</v>
+        <v>157.4259347483793</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.9510510477426</v>
+        <v>157.9549772580175</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.2673182769654</v>
+        <v>158.2709374681456</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.3148627276569</v>
+        <v>158.3185118813105</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.5553038262345</v>
+        <v>159.5587485567549</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.4171063231081</v>
+        <v>158.418615840981</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7320686060104</v>
+        <v>155.7307804940469</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.8770517392383</v>
+        <v>155.8756768342575</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.667849106812</v>
+        <v>156.667302563804</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.341906361223</v>
+        <v>156.3384699853723</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.1105878894843</v>
+        <v>156.1069524760055</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>155.9483902161677</v>
+        <v>155.9444178512186</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.1899397249233</v>
+        <v>157.1875771171936</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6517838760491</v>
+        <v>158.6524073403505</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1432948929869</v>
+        <v>159.1442891593937</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.7320589950955</v>
+        <v>159.7334109477437</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.6043448710528</v>
+        <v>159.6045915913837</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.176426151119</v>
+        <v>160.1768304926973</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.0619427012415</v>
+        <v>160.0610219537334</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.8525395265635</v>
+        <v>159.8507729667155</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.330283316499</v>
+        <v>160.3287841512705</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.0485795214628</v>
+        <v>161.046347917631</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.7210888252952</v>
+        <v>161.7179232848858</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.5645275984454</v>
+        <v>161.5623167306488</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.4960456050907</v>
+        <v>160.4971963913507</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.0482826520781</v>
+        <v>160.0504701750953</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>159.8566885692856</v>
+        <v>159.8596441880068</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>159.8763613878779</v>
+        <v>159.8720201457672</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>160.1155369002469</v>
+        <v>160.1157931756545</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>160.2360691965432</v>
+        <v>160.2406602331266</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>160.6397353064366</v>
+        <v>160.6731536444971</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>160.9347049167226</v>
+        <v>160.992681436115</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>161.1544740997881</v>
+        <v>161.2371524246713</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>161.317095270536</v>
+        <v>161.4282645925232</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>161.2919731614362</v>
+        <v>161.4445290357335</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>160.770739848261</v>
+        <v>161.0065678623337</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>160.0725663499486</v>
+        <v>160.4772497063607</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>159.1106178240478</v>
+        <v>159.6782864316543</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>159.5919669190476</v>
+        <v>160.366957037933</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>160.7309405025269</v>
+        <v>161.8594138839227</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>170.5304481461492</v>
+        <v>170.8100579205136</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.3200732200727</v>
+        <v>139.3189548899138</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.4952183256107</v>
+        <v>142.4935824904614</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.7761421363635</v>
+        <v>143.7743699245353</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.4550912155279</v>
+        <v>144.453270416818</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.3818748929196</v>
+        <v>144.3800231196165</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.3038931633369</v>
+        <v>144.3020153416723</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.2604453208981</v>
+        <v>144.2585571753262</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.2998214742621</v>
+        <v>144.2979367105276</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>144.9699639283255</v>
+        <v>144.9680738225991</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0365830098929</v>
+        <v>148.036612550673</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4314837890468</v>
+        <v>148.431490268267</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535375365141</v>
+        <v>148.8535379522896</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9202777072754</v>
+        <v>148.9204954285715</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2937375087725</v>
+        <v>149.2938058631327</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.409822095264</v>
+        <v>150.4095283438321</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.8671468926503</v>
+        <v>151.8663717279339</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2564964243391</v>
+        <v>152.2556714149655</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.5861744288047</v>
+        <v>152.5853760602095</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.183195934122</v>
+        <v>153.1826866110576</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4100958838148</v>
+        <v>152.4099694634336</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.9196609089695</v>
+        <v>152.9184377097186</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.7058736323498</v>
+        <v>152.7041878290751</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.731188922132</v>
+        <v>152.7289775363617</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.4236665526426</v>
+        <v>154.4209800625914</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.3808563278007</v>
+        <v>155.3781784957602</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.372424820295</v>
+        <v>156.3694934562709</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>158.030803272916</v>
+        <v>158.0275806205308</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.6413017942616</v>
+        <v>159.6385850384623</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.4718527820197</v>
+        <v>161.4700688086039</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.8953487180396</v>
+        <v>159.8963351132698</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.6193683374245</v>
+        <v>159.6198476897484</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.1841172984188</v>
+        <v>159.1871879436421</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.4259347483793</v>
+        <v>157.4299302707018</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.9549772580175</v>
+        <v>157.958812027718</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.2709374681456</v>
+        <v>158.2744735605151</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.3185118813105</v>
+        <v>158.3220806491927</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.5587485567549</v>
+        <v>159.5621184830555</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.418615840981</v>
+        <v>158.4200948405368</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7307804940469</v>
+        <v>155.7295239271063</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.8756768342575</v>
+        <v>155.8743356668427</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.667302563804</v>
+        <v>156.666771050251</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.3384699853723</v>
+        <v>156.3351118635786</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.1069524760055</v>
+        <v>156.1033990095142</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>155.9444178512186</v>
+        <v>155.9405330244658</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.1875771171936</v>
+        <v>157.1852660052631</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6524073403505</v>
+        <v>158.6530174756724</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1442891593937</v>
+        <v>159.1452624031491</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.7334109477437</v>
+        <v>159.734734492063</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.6045915913837</v>
+        <v>159.6048342646669</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1768304926973</v>
+        <v>160.1772281486504</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.0610219537334</v>
+        <v>160.0601238018597</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.8507729667155</v>
+        <v>159.849047085793</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.3287841512705</v>
+        <v>160.3273195820179</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.046347917631</v>
+        <v>161.0441667499892</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.7179232848858</v>
+        <v>161.7148289913545</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.5623167306488</v>
+        <v>161.5601510623179</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.4971963913507</v>
+        <v>160.4983096507004</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.0504701750953</v>
+        <v>160.0526002940489</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>159.8596441880068</v>
+        <v>159.8625287453977</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>159.8720201457672</v>
+        <v>159.8677981167902</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>160.1157931756545</v>
+        <v>160.1156336948737</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>160.2406602331266</v>
+        <v>160.243637349926</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>160.6731536444971</v>
+        <v>160.7003001759573</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>160.992681436115</v>
+        <v>161.0409899688019</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>161.2371524246713</v>
+        <v>161.3073002318578</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>161.4282645925232</v>
+        <v>161.5229551336954</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>161.4445290357335</v>
+        <v>161.5749573901132</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>161.0065678623337</v>
+        <v>161.2086498083028</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>160.4772497063607</v>
+        <v>160.8195585240689</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>159.6782864316543</v>
+        <v>160.1508999457988</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>160.366957037933</v>
+        <v>160.9796047646817</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>161.8594138839227</v>
+        <v>162.6656393864082</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>170.8100579205136</v>
+        <v>170.7271770057783</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.3189548899138</v>
+        <v>139.3178622650579</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.4935824904614</v>
+        <v>142.491984126584</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.7743699245353</v>
+        <v>143.7726381084834</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.453270416818</v>
+        <v>144.4514909167219</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.3800231196165</v>
+        <v>144.3782133607168</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.3020153416723</v>
+        <v>144.300180137951</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.2585571753262</v>
+        <v>144.2567118882623</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.2979367105276</v>
+        <v>144.296094729286</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>144.9680738225991</v>
+        <v>144.9662264061615</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.036612550673</v>
+        <v>148.0366414009908</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.431490268267</v>
+        <v>148.4314965909628</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535379522896</v>
+        <v>148.8535383516328</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9204954285715</v>
+        <v>148.920708070917</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2938058631327</v>
+        <v>149.2938727374029</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4095283438321</v>
+        <v>150.4092414083352</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.8663717279339</v>
+        <v>151.8656141902165</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2556714149655</v>
+        <v>152.2548651145813</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.5853760602095</v>
+        <v>152.5845956708397</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.1826866110576</v>
+        <v>153.1821887296016</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4099694634336</v>
+        <v>152.4098459671019</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.9184377097186</v>
+        <v>152.9172430279349</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.7041878290751</v>
+        <v>152.7025410927379</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.7289775363617</v>
+        <v>152.7268168378326</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.4209800625914</v>
+        <v>154.4183549245672</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.3781784957602</v>
+        <v>155.3755613537516</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.3694934562709</v>
+        <v>156.3666281802206</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>158.0275806205308</v>
+        <v>158.0244300291266</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.6385850384623</v>
+        <v>159.6359275893876</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.4700688086039</v>
+        <v>161.4683228117662</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.8963351132698</v>
+        <v>159.8972959683813</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.6198476897484</v>
+        <v>159.6203136246031</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.1871879436421</v>
+        <v>159.1901862304088</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.4299302707018</v>
+        <v>157.4338328086977</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.958812027718</v>
+        <v>157.9625585054093</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.2744735605151</v>
+        <v>158.2779293727612</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.3220806491927</v>
+        <v>158.3255716458249</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.5621184830555</v>
+        <v>159.5654159995729</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.4200948405368</v>
+        <v>158.4215442169362</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7295239271063</v>
+        <v>155.7282977651802</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.8743356668427</v>
+        <v>155.8730270162227</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.666771050251</v>
+        <v>156.6662539715818</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.3351118635786</v>
+        <v>156.3318293591914</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.1033990095142</v>
+        <v>156.0999247589012</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>155.9405330244658</v>
+        <v>155.9367328855938</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.1852660052631</v>
+        <v>157.1830047310731</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6530174756724</v>
+        <v>158.6536147013811</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1452624031491</v>
+        <v>159.1462152776554</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.734734492063</v>
+        <v>159.7360305039161</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.6048342646669</v>
+        <v>159.6050729732337</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1772281486504</v>
+        <v>160.1776192589913</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.0601238018597</v>
+        <v>160.0592474299603</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.849047085793</v>
+        <v>159.8473604981097</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.3273195820179</v>
+        <v>160.32588842877</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.0441667499892</v>
+        <v>161.0420343362517</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.7148289913545</v>
+        <v>161.7118035813432</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.5601510623179</v>
+        <v>161.5580292609419</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.4983096507004</v>
+        <v>160.4993870229961</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.0526002940489</v>
+        <v>160.0546751546711</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>159.8625287453977</v>
+        <v>159.8653446930939</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>159.8677981167902</v>
+        <v>159.8781024563228</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>160.1156336948737</v>
+        <v>160.1297732154394</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>160.243637349926</v>
+        <v>160.2635759712759</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>160.7003001759573</v>
+        <v>160.7411823993286</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>161.0409899688019</v>
+        <v>161.1037378400292</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>161.3073002318578</v>
+        <v>161.3925712857873</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>161.5229551336954</v>
+        <v>161.6336627293618</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>161.5749573901132</v>
+        <v>161.7220854318044</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>161.2086498083028</v>
+        <v>161.4269973925198</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>160.8195585240689</v>
+        <v>161.1721732854898</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>160.1508999457988</v>
+        <v>160.6261505127037</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>160.9796047646817</v>
+        <v>161.5814687353657</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>162.6656393864082</v>
+        <v>163.4247073401297</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>170.7271770057783</v>
+        <v>170.8486126450723</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B114"/>
+  <dimension ref="A1:B115"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.3178622650579</v>
+        <v>139.3167944693414</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.491984126584</v>
+        <v>142.4904219611785</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.7726381084834</v>
+        <v>143.7709453228758</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.4514909167219</v>
+        <v>144.4497513263955</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.3782133607168</v>
+        <v>144.3764442028532</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.300180137951</v>
+        <v>144.2983861180749</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.2567118882623</v>
+        <v>144.2549080172995</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.296094729286</v>
+        <v>144.2942940906626</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>144.9662264061615</v>
+        <v>144.964420249639</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0366414009908</v>
+        <v>148.0366695847578</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4314965909628</v>
+        <v>148.4315027627187</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535383516328</v>
+        <v>148.8535387353292</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.920708070917</v>
+        <v>148.9209158098979</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2938727374029</v>
+        <v>149.2939381788549</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4092414083352</v>
+        <v>150.4089610544566</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.8656141902165</v>
+        <v>151.8648736853925</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2548651145813</v>
+        <v>152.2540768943673</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.5845956708397</v>
+        <v>152.5838326607424</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.1821887296016</v>
+        <v>153.1817019088195</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4098459671019</v>
+        <v>152.409725294524</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.9172430279349</v>
+        <v>152.9160758787864</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.7025410927379</v>
+        <v>152.7009320825641</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.7268168378326</v>
+        <v>152.7247051055413</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.4183549245672</v>
+        <v>154.4157890633992</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.3755613537516</v>
+        <v>155.3730028654697</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.3666281802206</v>
+        <v>156.3638267872805</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>158.0244300291266</v>
+        <v>158.0213491157559</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.6359275893876</v>
+        <v>159.633327536933</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.4683228117662</v>
+        <v>161.4666136007158</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.8972959683813</v>
+        <v>159.8982322486519</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.6203136246031</v>
+        <v>159.6207666790734</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.1901862304088</v>
+        <v>159.1931146801814</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.4338328086977</v>
+        <v>157.4376455636626</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.9625585054093</v>
+        <v>157.9662196971489</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.2779293727612</v>
+        <v>158.2813075980048</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.3255716458249</v>
+        <v>158.3289873741532</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.5654159995729</v>
+        <v>159.5686434003813</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.4215442169362</v>
+        <v>158.4229648317317</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7282977651802</v>
+        <v>155.7271009223337</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.8730270162227</v>
+        <v>155.8717497195671</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6662539715818</v>
+        <v>156.6657507635499</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.3318293591914</v>
+        <v>156.328619952414</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.0999247589012</v>
+        <v>156.0965271126884</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>155.9367328855938</v>
+        <v>155.9330147061653</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.1830047310731</v>
+        <v>157.1807917066537</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6536147013811</v>
+        <v>158.6541994196008</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1462152776554</v>
+        <v>159.1471484098169</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.7360305039161</v>
+        <v>159.7372998240166</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.6050729732337</v>
+        <v>159.6053077982169</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1776192589913</v>
+        <v>160.1780039613296</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.0592474299603</v>
+        <v>160.0583920609168</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.8473604981097</v>
+        <v>159.8457118800563</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.32588842877</v>
+        <v>160.3244895644392</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.0420343362517</v>
+        <v>161.0399490677472</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.7118035813432</v>
+        <v>161.7088447942006</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.5580292609419</v>
+        <v>161.5559500438923</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.4993870229961</v>
+        <v>160.5004300591793</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.0546751546711</v>
+        <v>160.0566968003174</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>159.8653446930939</v>
+        <v>159.868094374611</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>159.8781024563228</v>
+        <v>159.8812836985946</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>160.1297732154394</v>
+        <v>160.1333253339602</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>160.2635759712759</v>
+        <v>160.2799852538065</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>160.7411823993286</v>
+        <v>160.7506555444772</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>161.1037378400292</v>
+        <v>161.1500006939518</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>161.3925712857873</v>
+        <v>161.45473217663</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>161.6336627293618</v>
+        <v>161.7168176006334</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>161.7220854318044</v>
+        <v>161.8364447910487</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>161.4269973925198</v>
+        <v>161.6023317063266</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>161.1721732854898</v>
+        <v>161.4163192610095</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>160.6261505127037</v>
+        <v>161.0119997378273</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>161.5814687353657</v>
+        <v>162.0508621558621</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>163.4247073401297</v>
+        <v>163.9671732161351</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,15 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>170.8486126450723</v>
+        <v>170.750203025531</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115" s="3">
+        <v>46360</v>
+      </c>
+      <c r="B115">
+        <v>170.6339276789178</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.3167944693414</v>
+        <v>139.3157506659704</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.4904219611785</v>
+        <v>142.4888947784387</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.7709453228758</v>
+        <v>143.7692902632112</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.4497513263955</v>
+        <v>144.4480503185579</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.3764442028532</v>
+        <v>144.3747142953291</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.2983861180749</v>
+        <v>144.2966319115552</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.2549080172995</v>
+        <v>144.2531441840179</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.2942940906626</v>
+        <v>144.2925334186587</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>144.964420249639</v>
+        <v>144.9626539867347</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0366695847578</v>
+        <v>148.0366971247943</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4315027627187</v>
+        <v>148.4315087888577</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535387353292</v>
+        <v>148.853539104119</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9209158098979</v>
+        <v>148.9211188131021</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2939381788549</v>
+        <v>149.2940022327821</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4089610544566</v>
+        <v>150.40868705849</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.8648736853925</v>
+        <v>151.8641496457416</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2540768943673</v>
+        <v>152.253306153352</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.5838326607424</v>
+        <v>152.5830864563367</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.1817019088195</v>
+        <v>153.1812257844875</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.409725294524</v>
+        <v>152.4096073499392</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.9160758787864</v>
+        <v>152.914935322231</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.7009320825641</v>
+        <v>152.6993595183659</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.7247051055413</v>
+        <v>152.7226406954382</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.4157890633992</v>
+        <v>154.4132804963388</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.3730028654697</v>
+        <v>155.3705010845318</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.3638267872805</v>
+        <v>156.3610871693583</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>158.0213491157559</v>
+        <v>158.0183356010638</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.633327536933</v>
+        <v>159.6307830516445</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.4666136007158</v>
+        <v>161.464940033504</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.8982322486519</v>
+        <v>159.8991448718681</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.6207666790734</v>
+        <v>159.6212073626235</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.1931146801814</v>
+        <v>159.1959756988886</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.4376455636626</v>
+        <v>157.4413715919228</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.9662196971489</v>
+        <v>157.9697984744371</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.2813075980048</v>
+        <v>158.2846108106887</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.3289873741532</v>
+        <v>158.3323302314039</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.5686434003813</v>
+        <v>159.5718028843516</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.4229648317317</v>
+        <v>158.4243575143621</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7271009223337</v>
+        <v>155.7259323635479</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.8717497195671</v>
+        <v>155.8705026686024</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6657507635499</v>
+        <v>156.6652608903545</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.328619952414</v>
+        <v>156.3254812339163</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.0965271126884</v>
+        <v>156.0932035725718</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>155.9330147061653</v>
+        <v>155.9293758732061</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.1807917066537</v>
+        <v>157.1786254104772</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6541994196008</v>
+        <v>158.6547720160813</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1471484098169</v>
+        <v>159.1480624013523</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.7372998240166</v>
+        <v>159.7385432596444</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.6053077982169</v>
+        <v>159.6055388194782</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1780039613296</v>
+        <v>160.1783823907932</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.0583920609168</v>
+        <v>160.0575569539157</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.8457118800563</v>
+        <v>159.8440999666718</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.3244895644392</v>
+        <v>160.3231219119018</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.0399490677472</v>
+        <v>161.0379094054578</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.7088447942006</v>
+        <v>161.7059504665006</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.5559500438923</v>
+        <v>161.553912176237</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.5004300591793</v>
+        <v>160.5014402269956</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.0566968003174</v>
+        <v>160.0586671778394</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>159.868094374611</v>
+        <v>159.8707800310592</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>159.8812836985946</v>
+        <v>159.8843987417792</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>160.1333253339602</v>
+        <v>160.1189089100816</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>160.2799852538065</v>
+        <v>160.2758382370202</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>160.7506555444772</v>
+        <v>160.7385871458992</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>161.1500006939518</v>
+        <v>161.1704457813004</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>161.45473217663</v>
+        <v>161.4891083055219</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>161.7168176006334</v>
+        <v>161.7693937475337</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>161.8364447910487</v>
+        <v>161.9157401098903</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>161.6023317063266</v>
+        <v>161.7327925884201</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>161.4163192610095</v>
+        <v>161.6020435737283</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>161.0119997378273</v>
+        <v>161.3182124173545</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>162.0508621558621</v>
+        <v>162.4098533511051</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>163.9671732161351</v>
+        <v>164.3443903441132</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>170.750203025531</v>
+        <v>170.5290144038925</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>170.6339276789178</v>
+        <v>170.0572656833735</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.3157506659704</v>
+        <v>139.3147300553339</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.4888947784387</v>
+        <v>142.487401416398</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.7692902632112</v>
+        <v>143.7676716824704</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.4480503185579</v>
+        <v>144.4463866241186</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.3747142953291</v>
+        <v>144.3730223466838</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.2966319115552</v>
+        <v>144.2949162080245</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.2531441840179</v>
+        <v>144.2514190704767</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.2925334186587</v>
+        <v>144.2908113976494</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>144.9626539867347</v>
+        <v>144.9609263107886</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0366971247943</v>
+        <v>148.0367240428916</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4315087888577</v>
+        <v>148.4315146744561</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.853539104119</v>
+        <v>148.8535394587005</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9211188131021</v>
+        <v>148.92131724057</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2940022327821</v>
+        <v>149.2940649426013</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.40868705849</v>
+        <v>150.4084192067464</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.8641496457416</v>
+        <v>151.8634415284805</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.253306153352</v>
+        <v>152.2525523168881</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.5830864563367</v>
+        <v>152.5823565089821</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.1812257844875</v>
+        <v>153.1807600081862</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4096073499392</v>
+        <v>152.4094920418685</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.914935322231</v>
+        <v>152.9138204605009</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.6993595183659</v>
+        <v>152.6978221771619</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.7226406954382</v>
+        <v>152.720622036179</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.4132804963388</v>
+        <v>154.410827327978</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.3705010845318</v>
+        <v>155.3680541495773</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.3610871693583</v>
+        <v>156.3584073098937</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>158.0183356010638</v>
+        <v>158.0153873037374</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.6307830516445</v>
+        <v>159.6282923805362</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.464940033504</v>
+        <v>161.463301014571</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.8991448718681</v>
+        <v>159.9000347111842</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.6212073626235</v>
+        <v>159.6216361588203</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.1959756988886</v>
+        <v>159.1987715834535</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.4413715919228</v>
+        <v>157.4450138129324</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.9697984744371</v>
+        <v>157.9732975816414</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.2846108106887</v>
+        <v>158.2878414730189</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.3323302314039</v>
+        <v>158.335602514576</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.5718028843516</v>
+        <v>159.5748965600001</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.4243575143621</v>
+        <v>158.425723063574</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7259323635479</v>
+        <v>155.724791101781</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.8705026686024</v>
+        <v>155.8692848064619</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6652608903545</v>
+        <v>156.6647838428977</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.3254812339163</v>
+        <v>156.3224108988609</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.0932035725718</v>
+        <v>156.0899517473773</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>155.9293758732061</v>
+        <v>155.9258138831896</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.1786254104772</v>
+        <v>157.1765043840374</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6547720160813</v>
+        <v>158.655332861014</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1480624013523</v>
+        <v>159.1489578300301</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.7385432596444</v>
+        <v>159.7397615862665</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.6055388194782</v>
+        <v>159.6057661155506</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1783823907932</v>
+        <v>160.1787546799693</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.0575569539157</v>
+        <v>160.0567414023642</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.8440999666718</v>
+        <v>159.8425235484382</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.3231219119018</v>
+        <v>160.3217844412677</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.0379094054578</v>
+        <v>161.035913876308</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.7059504665006</v>
+        <v>161.7031185269051</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.553912176237</v>
+        <v>161.5519144686587</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.5014402269956</v>
+        <v>160.5024189162893</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.0586671778394</v>
+        <v>160.060588143067</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>159.8707800310592</v>
+        <v>159.8734038065104</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>159.8843987417792</v>
+        <v>159.8874495492983</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>160.1189089100816</v>
+        <v>159.9923687069092</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>160.2758382370202</v>
+        <v>160.1325902166592</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>160.7385871458992</v>
+        <v>160.580961594101</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>161.1704457813004</v>
+        <v>160.992621847627</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>161.4891083055219</v>
+        <v>161.3249654489428</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>161.7693937475337</v>
+        <v>161.6072961809041</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>161.9157401098903</v>
+        <v>161.758218360192</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>161.7327925884201</v>
+        <v>161.5827981446975</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>161.6020435737283</v>
+        <v>161.4506091456081</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>161.3182124173545</v>
+        <v>161.2064237241545</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>162.4098533511051</v>
+        <v>162.2334066305626</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>164.3443903441132</v>
+        <v>163.9843128985194</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>170.5290144038925</v>
+        <v>168.9343019587527</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>170.0572656833735</v>
+        <v>165.7148554384553</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.3147300553339</v>
+        <v>139.3137318729615</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.487401416398</v>
+        <v>142.4859407639819</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.7676716824704</v>
+        <v>143.7660883879842</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.4463866241186</v>
+        <v>144.4447590290241</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.3730223466838</v>
+        <v>144.3713671214815</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.2949162080245</v>
+        <v>144.2932377539778</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.2514190704767</v>
+        <v>144.2497314159338</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.2908113976494</v>
+        <v>144.2891267691091</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>144.9609263107886</v>
+        <v>144.959235971561</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0367240428916</v>
+        <v>148.0367503598692</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4315146744561</v>
+        <v>148.4315204243577</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535394587005</v>
+        <v>148.8535397997328</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.92131724057</v>
+        <v>148.9215112452143</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2940649426013</v>
+        <v>149.2941263499484</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4084192067464</v>
+        <v>150.4081572949995</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.8634415284805</v>
+        <v>151.8627488144095</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2525523168881</v>
+        <v>152.2518148352283</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.5823565089821</v>
+        <v>152.5816422936387</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.1807600081862</v>
+        <v>153.1803042464537</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4094920418685</v>
+        <v>152.4093792828786</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.9138204605009</v>
+        <v>152.9127304357548</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.6978221771619</v>
+        <v>152.6963188900207</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.720622036179</v>
+        <v>152.7186476251532</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.410827327978</v>
+        <v>154.4084277454979</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.3680541495773</v>
+        <v>155.3656602796837</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.3584073098937</v>
+        <v>156.3557852789561</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>158.0153873037374</v>
+        <v>158.0125021353072</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.6282923805362</v>
+        <v>159.6258538431614</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.463301014571</v>
+        <v>161.4616954924366</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.9000347111842</v>
+        <v>159.9009025977776</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.6216361588203</v>
+        <v>159.6220535269287</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.1987715834535</v>
+        <v>159.2015045278844</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.4450138129324</v>
+        <v>157.4485750168348</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.9732975816414</v>
+        <v>157.9767196429378</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.2878414730189</v>
+        <v>158.291001940992</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.335602514576</v>
+        <v>158.3388064255962</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.5748965600001</v>
+        <v>159.5779264500459</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.425723063574</v>
+        <v>158.427062248773</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.724791101781</v>
+        <v>155.7236761952283</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.8692848064619</v>
+        <v>155.8680951247504</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6647838428977</v>
+        <v>156.6643191371667</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.3224108988609</v>
+        <v>156.3194067413129</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.0899517473773</v>
+        <v>156.0867693473974</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>155.9258138831896</v>
+        <v>155.9223263363909</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.1765043840374</v>
+        <v>157.1744272286355</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.655332861014</v>
+        <v>158.6558823097997</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1489578300301</v>
+        <v>159.1498352508341</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.7397615862665</v>
+        <v>159.7409555490627</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.6057661155506</v>
+        <v>159.6059897635923</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1787546799693</v>
+        <v>160.1791209588603</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.0567414023642</v>
+        <v>160.0559447319479</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.8425235484382</v>
+        <v>159.840981468283</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.3217844412677</v>
+        <v>160.3204761673281</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.035913876308</v>
+        <v>161.0339610696882</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.7031185269051</v>
+        <v>161.7003469913474</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.5519144686587</v>
+        <v>161.5499557754719</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.5024189162893</v>
+        <v>160.5033674439111</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.060588143067</v>
+        <v>160.0624614659305</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>159.8734038065104</v>
+        <v>159.8759677530431</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>159.8874495492983</v>
+        <v>159.8904380113834</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>159.9923687069092</v>
+        <v>159.8772239420187</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>160.1325902166592</v>
+        <v>160.0022445305138</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>160.580961594101</v>
+        <v>160.4371526402923</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>160.992621847627</v>
+        <v>160.8331866191699</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>161.3249654489428</v>
+        <v>161.1771377394332</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>161.6072961809041</v>
+        <v>161.4621948662242</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>161.758218360192</v>
+        <v>161.6185795685581</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>161.5827981446975</v>
+        <v>161.4527762504769</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>161.4506091456081</v>
+        <v>161.3226580671081</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>161.2064237241545</v>
+        <v>161.118994749287</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>162.2334066305626</v>
+        <v>162.0937270091528</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>163.9843128985194</v>
+        <v>163.6975466592687</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>168.9343019587527</v>
+        <v>167.7027420234791</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>165.7148554384553</v>
+        <v>163.6456454006878</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.3137318729615</v>
+        <v>139.3127553876137</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.4859407639819</v>
+        <v>142.4845117582524</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.7660883879842</v>
+        <v>143.7645392385054</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.4447590290241</v>
+        <v>144.4431663713076</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.3713671214815</v>
+        <v>144.3697474373069</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.2932377539778</v>
+        <v>144.2915953497216</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.2497314159338</v>
+        <v>144.2480800137774</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.2891267691091</v>
+        <v>144.2874783285484</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>144.959235971561</v>
+        <v>144.957581772221</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0367503598692</v>
+        <v>148.0367760956277</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4315204243577</v>
+        <v>148.4315260431867</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535397997328</v>
+        <v>148.8535401278383</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9215112452143</v>
+        <v>148.9217009732125</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2941263499484</v>
+        <v>149.2941864947675</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4081572949995</v>
+        <v>150.4079011279686</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.8627488144095</v>
+        <v>151.8620710066466</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2518148352283</v>
+        <v>152.2510931821908</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.5816422936387</v>
+        <v>152.5809433076131</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.1803042464537</v>
+        <v>153.1798581799919</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4093792828786</v>
+        <v>152.4092689893596</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.9127304357548</v>
+        <v>152.9116644278845</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.6963188900207</v>
+        <v>152.6948485391107</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.7186476251532</v>
+        <v>152.7167160247713</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.4084277454979</v>
+        <v>154.4060800142249</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.3656602796837</v>
+        <v>155.3633177700758</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.3557852789561</v>
+        <v>156.353219228652</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>158.0125021353072</v>
+        <v>158.0096780952751</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.6258538431614</v>
+        <v>159.6234658279242</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.4616954924366</v>
+        <v>161.4601224575259</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.9009025977776</v>
+        <v>159.901749323319</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.6220535269287</v>
+        <v>159.6224599033937</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.2015045278844</v>
+        <v>159.2041766289623</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.4485750168348</v>
+        <v>157.4520578715294</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.9767196429378</v>
+        <v>157.9800671688014</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.291001940992</v>
+        <v>158.2940944700403</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.3388064255962</v>
+        <v>158.3419440761623</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.5779264500459</v>
+        <v>159.5808944956974</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.427062248773</v>
+        <v>158.428375811308</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7236761952283</v>
+        <v>155.7225867447693</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.8680951247504</v>
+        <v>155.8669326608075</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6643191371667</v>
+        <v>156.6638663127301</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.3194067413129</v>
+        <v>156.3164666490021</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.0867693473974</v>
+        <v>156.0836541790827</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>155.9223263363909</v>
+        <v>155.9189109315857</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.1744272286355</v>
+        <v>157.17239260236</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6558823097997</v>
+        <v>158.6564207037731</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1498352508341</v>
+        <v>159.1506951970617</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.7409555490627</v>
+        <v>159.7421258643693</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.6059897635923</v>
+        <v>159.6062098393512</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1791209588603</v>
+        <v>160.1794813548554</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.0559447319479</v>
+        <v>160.0551662988184</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.840981468283</v>
+        <v>159.8394726187731</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.3204761673281</v>
+        <v>160.3191961471653</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.0339610696882</v>
+        <v>161.0320496341945</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.7003469913474</v>
+        <v>161.6976339585123</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.5499557754719</v>
+        <v>161.5480349927355</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.5033674439111</v>
+        <v>160.5042870582687</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.0624614659305</v>
+        <v>160.064288835249</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>159.8759677530431</v>
+        <v>159.8784738354848</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>159.8904380113834</v>
+        <v>159.8933659482391</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>159.8772239420187</v>
+        <v>159.7678638277002</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>160.0022445305138</v>
+        <v>159.8805366531114</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>160.4371526402923</v>
+        <v>160.3032231157904</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>160.8331866191699</v>
+        <v>160.6836230396675</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>161.1771377394332</v>
+        <v>161.0385324952358</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>161.4621948662242</v>
+        <v>161.3247654622302</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>161.6185795685581</v>
+        <v>161.4826864360843</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>161.4527762504769</v>
+        <v>161.3219592201925</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>161.3226580671081</v>
+        <v>161.1901119365295</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>161.118994749287</v>
+        <v>161.0164228597556</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>162.0937270091528</v>
+        <v>161.9359045228093</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>163.6975466592687</v>
+        <v>163.397406502869</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>167.7027420234791</v>
+        <v>166.8686375077299</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>163.6456454006878</v>
+        <v>162.7422622784934</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.3127553876137</v>
+        <v>139.3117998994965</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.4845117582524</v>
+        <v>142.4831133818291</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.7645392385054</v>
+        <v>143.7630231414677</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.4431663713076</v>
+        <v>144.441607538326</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.3697474373069</v>
+        <v>144.368162161952</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.2915953497216</v>
+        <v>144.2899878465177</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.2480800137774</v>
+        <v>144.2464637086525</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.2874783285484</v>
+        <v>144.2858649226454</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>144.957581772221</v>
+        <v>144.955962566526</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0367760956277</v>
+        <v>148.0368012691998</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4315260431867</v>
+        <v>148.4315315353603</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535401278383</v>
+        <v>148.8535404436053</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9217009732125</v>
+        <v>148.921886564373</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2941864947675</v>
+        <v>149.2942454153959</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4079011279686</v>
+        <v>150.4076505188337</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.8620710066466</v>
+        <v>151.8614076294411</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2510931821908</v>
+        <v>152.2503868539122</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.5809433076131</v>
+        <v>152.5802590693829</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.1798581799919</v>
+        <v>153.1794215029233</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4092689893596</v>
+        <v>152.4091610813192</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.9116644278845</v>
+        <v>152.9106216524646</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.6948485391107</v>
+        <v>152.6934100549414</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.7167160247713</v>
+        <v>152.7148258589883</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.4060800142249</v>
+        <v>154.4037824734699</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.3633177700758</v>
+        <v>155.361024988106</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.353219228652</v>
+        <v>156.3507073888223</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>158.0096780952751</v>
+        <v>158.006913266544</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.6234658279242</v>
+        <v>159.6211267886098</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.4601224575259</v>
+        <v>161.4585809401217</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.901749323319</v>
+        <v>159.9025756422714</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.6224599033937</v>
+        <v>159.6228557032165</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.2041766289623</v>
+        <v>159.2067898915569</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.4520578715294</v>
+        <v>157.4554649292807</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.9800671688014</v>
+        <v>157.9833425620836</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.2940944700403</v>
+        <v>158.2971212203221</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.3419440761623</v>
+        <v>158.3450174922935</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.5808944956974</v>
+        <v>159.5838025606872</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.428375811308</v>
+        <v>158.4296644656924</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7225867447693</v>
+        <v>155.7215218915835</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.8669326608075</v>
+        <v>155.8657964951532</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6638663127301</v>
+        <v>156.6634249313409</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.3164666490021</v>
+        <v>156.3135885984155</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.0836541790827</v>
+        <v>156.0806041400619</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>155.9189109315857</v>
+        <v>155.9155654610686</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.17239260236</v>
+        <v>157.1703992172474</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6564207037731</v>
+        <v>158.6569483708846</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1506951970617</v>
+        <v>159.1515381813607</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.7421258643693</v>
+        <v>159.7432732210403</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.6062098393512</v>
+        <v>159.6064264171384</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1794813548554</v>
+        <v>160.1798359927135</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.0551662988184</v>
+        <v>160.0544054879011</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.8394726187731</v>
+        <v>159.8379959394875</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.3191961471653</v>
+        <v>160.3179434779141</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.0320496341945</v>
+        <v>161.030178274569</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.6976339585123</v>
+        <v>161.6949776055926</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.5480349927355</v>
+        <v>161.5461510564538</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.5042870582687</v>
+        <v>160.5051789435512</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.064288835249</v>
+        <v>160.066071863209</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>159.8784738354848</v>
+        <v>159.880923935873</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>159.8933659482391</v>
+        <v>159.8962351130589</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>159.7678638277002</v>
+        <v>159.6638993241156</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>159.8805366531114</v>
+        <v>159.757120031983</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>160.3032231157904</v>
+        <v>160.157490146395</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>160.6836230396675</v>
+        <v>160.5155692369383</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>161.0385324952358</v>
+        <v>160.8574002538374</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>161.3247654622302</v>
+        <v>161.1335171540884</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>161.4826864360843</v>
+        <v>161.2822495226349</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>161.3219592201925</v>
+        <v>161.1105894658347</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>161.1901119365295</v>
+        <v>160.9566929027705</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>161.0164228597556</v>
+        <v>160.7683025178881</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>161.9359045228093</v>
+        <v>161.6067870334289</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>163.397406502869</v>
+        <v>162.8980095715825</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>166.8686375077299</v>
+        <v>165.8589200118303</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>162.7422622784934</v>
+        <v>161.5765982726582</v>
       </c>
     </row>
   </sheetData>
